--- a/comptes_exemple.xlsx
+++ b/comptes_exemple.xlsx
@@ -64,12 +64,12 @@
     <definedName function="false" hidden="false" name="CTRL1montant_ancrage" vbProcedure="false">Contrôles!$E$3:$E$26</definedName>
     <definedName function="false" hidden="false" name="CTRL1montant_releve" vbProcedure="false">Contrôles!$G$3:$G$26</definedName>
     <definedName function="false" hidden="false" name="CTRL1solde_calc" vbProcedure="false">Contrôles!$F$3:$F$26</definedName>
-    <definedName function="false" hidden="false" name="CTRL2affichage" vbProcedure="false">Contrôles!$K$31:$K$48</definedName>
-    <definedName function="false" hidden="false" name="CTRL2drill" vbProcedure="false">Contrôles!$M$31:$M$48</definedName>
-    <definedName function="false" hidden="false" name="CTRL2general" vbProcedure="false">Contrôles!$L$31:$L$48</definedName>
-    <definedName function="false" hidden="false" name="CTRL2type" vbProcedure="false">Contrôles!$J$31:$J$48</definedName>
-    <definedName function="false" hidden="false" name="CTRL2_fonds_en_transit" vbProcedure="false">Contrôles!$L$43</definedName>
-    <definedName function="false" hidden="false" name="CTRL2_synthese" vbProcedure="false">Contrôles!$K$49</definedName>
+    <definedName function="false" hidden="false" name="CTRL2affichage" vbProcedure="false">Contrôles!$K$31:$K$51</definedName>
+    <definedName function="false" hidden="false" name="CTRL2drill" vbProcedure="false">Contrôles!$M$31:$M$51</definedName>
+    <definedName function="false" hidden="false" name="CTRL2general" vbProcedure="false">Contrôles!$L$31:$L$51</definedName>
+    <definedName function="false" hidden="false" name="CTRL2type" vbProcedure="false">Contrôles!$J$31:$J$51</definedName>
+    <definedName function="false" hidden="false" name="CTRL2_fonds_en_transit" vbProcedure="false">Contrôles!$L$46</definedName>
+    <definedName function="false" hidden="false" name="CTRL2_synthese" vbProcedure="false">Contrôles!$K$52</definedName>
     <definedName function="false" hidden="false" name="OPcatégorie" vbProcedure="false">Opérations!$G$4:$G$10000</definedName>
     <definedName function="false" hidden="false" name="OPcommentaire" vbProcedure="false">Opérations!$I$4:$I$10000</definedName>
     <definedName function="false" hidden="false" name="OPcompte" vbProcedure="false">Opérations!$H$4:$H$10000</definedName>
@@ -116,7 +116,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="956" uniqueCount="288">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="959" uniqueCount="290">
   <si>
     <t xml:space="preserve">Patrimoine et répartition</t>
   </si>
@@ -883,7 +883,13 @@
     <t xml:space="preserve">COMPTES (de début #Solde à fin #Solde)</t>
   </si>
   <si>
-    <t xml:space="preserve">CATÉGORIES (année glissante)</t>
+    <t xml:space="preserve">    Manquantes</t>
+  </si>
+  <si>
+    <t xml:space="preserve">    Inconnues</t>
+  </si>
+  <si>
+    <t xml:space="preserve">    Écart Budget € (année glissante)</t>
   </si>
   <si>
     <t xml:space="preserve">    Date hors période</t>
@@ -913,7 +919,7 @@
     <t xml:space="preserve">    Total €</t>
   </si>
   <si>
-    <t xml:space="preserve">INCONNUS (Comptes)</t>
+    <t xml:space="preserve">INCONNUS (Comptes, Devises)</t>
   </si>
   <si>
     <t xml:space="preserve">FORMULES</t>
@@ -986,7 +992,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="42">
+  <numFmts count="41">
     <numFmt numFmtId="164" formatCode="General"/>
     <numFmt numFmtId="165" formatCode="#,##0.00\ [$€-40C];\-#,##0.00\ [$€-40C]"/>
     <numFmt numFmtId="166" formatCode="#,##0.00\ [$XAU]"/>
@@ -1015,20 +1021,19 @@
     <numFmt numFmtId="189" formatCode="\ #,##0.00\ [$€-40C]"/>
     <numFmt numFmtId="190" formatCode="@&quot; ▼&quot;"/>
     <numFmt numFmtId="191" formatCode="#,##0.00000\ [$€-40C];\-#,##0.00000\ [$€-40C]"/>
-    <numFmt numFmtId="192" formatCode="0%"/>
-    <numFmt numFmtId="193" formatCode="#,##0"/>
-    <numFmt numFmtId="194" formatCode="0.00\ %"/>
-    <numFmt numFmtId="195" formatCode="[$-40C]dd/mm/yy"/>
-    <numFmt numFmtId="196" formatCode="0.00000"/>
-    <numFmt numFmtId="197" formatCode="#,##0.00"/>
-    <numFmt numFmtId="198" formatCode="\ 0.00\ [$€-40C]"/>
-    <numFmt numFmtId="199" formatCode="#,##0.000000000\ [$XAU]"/>
-    <numFmt numFmtId="200" formatCode="#,##0.000000000\ [$OrPr]"/>
-    <numFmt numFmtId="201" formatCode="#,##0.000000000\ [$BTC]"/>
-    <numFmt numFmtId="202" formatCode="#,##0.000000000\ [$SAT]"/>
-    <numFmt numFmtId="203" formatCode="#,##0.000000000\ [$XMR]"/>
-    <numFmt numFmtId="204" formatCode="#,##0.000000000\ [$USD]"/>
-    <numFmt numFmtId="205" formatCode="#,##0.000000000\ [$SGD]"/>
+    <numFmt numFmtId="192" formatCode="#,##0"/>
+    <numFmt numFmtId="193" formatCode="0.00\ %"/>
+    <numFmt numFmtId="194" formatCode="[$-40C]dd/mm/yy"/>
+    <numFmt numFmtId="195" formatCode="0.00000"/>
+    <numFmt numFmtId="196" formatCode="#,##0.00"/>
+    <numFmt numFmtId="197" formatCode="\ 0.00\ [$€-40C]"/>
+    <numFmt numFmtId="198" formatCode="#,##0.000000000\ [$XAU]"/>
+    <numFmt numFmtId="199" formatCode="#,##0.000000000\ [$OrPr]"/>
+    <numFmt numFmtId="200" formatCode="#,##0.000000000\ [$BTC]"/>
+    <numFmt numFmtId="201" formatCode="#,##0.000000000\ [$SAT]"/>
+    <numFmt numFmtId="202" formatCode="#,##0.000000000\ [$XMR]"/>
+    <numFmt numFmtId="203" formatCode="#,##0.000000000\ [$USD]"/>
+    <numFmt numFmtId="204" formatCode="#,##0.000000000\ [$SGD]"/>
   </numFmts>
   <fonts count="21">
     <font>
@@ -1578,684 +1583,680 @@
       <protection locked="true" hidden="false"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="170">
+  <cellXfs count="169">
     <xf numFmtId="164" fontId="0" fillId="2" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="2" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="164" fontId="0" fillId="2" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="10" fillId="16" borderId="5" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="164" fontId="10" fillId="16" borderId="5" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="10" fillId="16" borderId="5" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="164" fontId="10" fillId="16" borderId="5" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="left" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="10" fillId="16" borderId="5" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="164" fontId="10" fillId="16" borderId="5" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="left" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="11" fillId="16" borderId="5" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="164" fontId="11" fillId="16" borderId="5" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="left" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="10" fillId="16" borderId="5" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="164" fontId="10" fillId="16" borderId="5" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="178" fontId="10" fillId="16" borderId="5" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="178" fontId="10" fillId="16" borderId="5" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="left" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="179" fontId="11" fillId="16" borderId="5" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="179" fontId="11" fillId="16" borderId="5" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="178" fontId="12" fillId="16" borderId="5" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="178" fontId="12" fillId="16" borderId="5" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="11" fillId="16" borderId="5" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="164" fontId="11" fillId="16" borderId="5" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="180" fontId="11" fillId="17" borderId="5" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="180" fontId="11" fillId="17" borderId="5" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="11" fillId="16" borderId="5" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="164" fontId="11" fillId="16" borderId="5" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="left" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="181" fontId="11" fillId="16" borderId="5" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="181" fontId="11" fillId="16" borderId="5" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="178" fontId="11" fillId="18" borderId="5" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="178" fontId="11" fillId="18" borderId="5" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="left" vertical="top" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="182" fontId="11" fillId="2" borderId="5" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="182" fontId="11" fillId="2" borderId="5" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="center" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="165" fontId="11" fillId="2" borderId="5" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="165" fontId="11" fillId="2" borderId="5" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="right" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="183" fontId="11" fillId="2" borderId="5" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="183" fontId="11" fillId="2" borderId="5" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="right" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="2" borderId="5" xfId="0" applyFont="false" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="164" fontId="0" fillId="2" borderId="5" xfId="0" applyFont="false" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="11" fillId="2" borderId="5" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="164" fontId="11" fillId="2" borderId="5" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="178" fontId="12" fillId="16" borderId="5" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="178" fontId="12" fillId="16" borderId="5" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="left" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="178" fontId="12" fillId="16" borderId="5" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="178" fontId="12" fillId="16" borderId="5" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="left" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="178" fontId="11" fillId="18" borderId="5" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="178" fontId="11" fillId="18" borderId="5" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="center" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="178" fontId="12" fillId="18" borderId="5" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="178" fontId="12" fillId="18" borderId="5" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="center" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="165" fontId="11" fillId="17" borderId="4" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="165" fontId="11" fillId="17" borderId="4" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="right" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="182" fontId="12" fillId="16" borderId="5" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="182" fontId="12" fillId="16" borderId="5" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="178" fontId="11" fillId="16" borderId="5" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="178" fontId="11" fillId="16" borderId="5" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="left" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="12" fillId="16" borderId="5" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="164" fontId="12" fillId="16" borderId="5" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="left" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="182" fontId="12" fillId="16" borderId="5" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="182" fontId="12" fillId="16" borderId="5" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="178" fontId="11" fillId="18" borderId="5" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="178" fontId="11" fillId="18" borderId="5" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="center" vertical="top" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="11" fillId="18" borderId="6" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="164" fontId="11" fillId="18" borderId="6" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="left" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="12" fillId="18" borderId="6" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="164" fontId="12" fillId="18" borderId="6" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="left" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="178" fontId="11" fillId="18" borderId="5" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="178" fontId="11" fillId="18" borderId="5" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="left" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="165" fontId="13" fillId="2" borderId="5" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="165" fontId="13" fillId="2" borderId="5" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="center" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="182" fontId="11" fillId="2" borderId="5" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="182" fontId="11" fillId="2" borderId="5" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="left" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="165" fontId="11" fillId="2" borderId="5" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="165" fontId="11" fillId="2" borderId="5" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="center" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="165" fontId="12" fillId="2" borderId="5" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="165" fontId="12" fillId="2" borderId="5" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="center" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="165" fontId="12" fillId="10" borderId="5" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="165" fontId="12" fillId="10" borderId="5" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="182" fontId="11" fillId="2" borderId="5" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="182" fontId="11" fillId="2" borderId="5" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="left" vertical="top" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="184" fontId="11" fillId="13" borderId="5" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="184" fontId="11" fillId="13" borderId="5" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="center" vertical="top" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="184" fontId="11" fillId="14" borderId="5" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="184" fontId="11" fillId="14" borderId="5" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="center" vertical="top" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="165" fontId="14" fillId="17" borderId="5" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="165" fontId="14" fillId="17" borderId="5" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="center" vertical="top" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="165" fontId="13" fillId="2" borderId="5" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="165" fontId="13" fillId="2" borderId="5" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="center" vertical="top" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="182" fontId="11" fillId="2" borderId="5" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="182" fontId="11" fillId="2" borderId="5" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="center" vertical="top" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="15" fillId="2" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="164" fontId="15" fillId="2" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="15" fillId="2" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="164" fontId="15" fillId="2" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
       <alignment horizontal="center" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="16" fillId="16" borderId="5" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="164" fontId="16" fillId="16" borderId="5" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="178" fontId="11" fillId="16" borderId="5" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="178" fontId="11" fillId="16" borderId="5" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="left" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="180" fontId="11" fillId="16" borderId="5" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="180" fontId="11" fillId="16" borderId="5" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="left" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="178" fontId="11" fillId="16" borderId="5" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="178" fontId="11" fillId="16" borderId="5" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="165" fontId="11" fillId="17" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="165" fontId="11" fillId="17" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
       <alignment horizontal="left" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="178" fontId="11" fillId="16" borderId="5" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="178" fontId="11" fillId="16" borderId="5" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="178" fontId="11" fillId="2" borderId="5" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="178" fontId="11" fillId="2" borderId="5" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="left" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="178" fontId="11" fillId="2" borderId="5" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="178" fontId="11" fillId="2" borderId="5" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="left" vertical="top" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="178" fontId="11" fillId="2" borderId="5" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="178" fontId="11" fillId="2" borderId="5" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="center" vertical="top" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="178" fontId="11" fillId="2" borderId="5" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="178" fontId="11" fillId="2" borderId="5" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="center" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="185" fontId="11" fillId="2" borderId="5" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="185" fontId="11" fillId="2" borderId="5" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="center" vertical="top" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="165" fontId="11" fillId="2" borderId="5" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="165" fontId="11" fillId="2" borderId="5" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="center" vertical="top" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="179" fontId="11" fillId="2" borderId="5" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="179" fontId="11" fillId="2" borderId="5" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="center" vertical="top" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="171" fontId="11" fillId="2" borderId="5" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="171" fontId="11" fillId="2" borderId="5" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="center" vertical="top" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="171" fontId="11" fillId="13" borderId="5" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="171" fontId="11" fillId="13" borderId="5" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="center" vertical="top" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="172" fontId="11" fillId="2" borderId="5" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="172" fontId="11" fillId="2" borderId="5" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="center" vertical="top" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="172" fontId="11" fillId="13" borderId="5" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="172" fontId="11" fillId="13" borderId="5" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="center" vertical="top" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="169" fontId="11" fillId="2" borderId="5" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="169" fontId="11" fillId="2" borderId="5" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="center" vertical="top" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="169" fontId="11" fillId="13" borderId="5" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="169" fontId="11" fillId="13" borderId="5" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="center" vertical="top" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="170" fontId="11" fillId="2" borderId="5" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="170" fontId="11" fillId="2" borderId="5" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="center" vertical="top" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="170" fontId="11" fillId="13" borderId="5" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="170" fontId="11" fillId="13" borderId="5" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="center" vertical="top" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="167" fontId="11" fillId="2" borderId="5" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="167" fontId="11" fillId="2" borderId="5" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="center" vertical="top" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="167" fontId="11" fillId="13" borderId="5" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="167" fontId="11" fillId="13" borderId="5" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="center" vertical="top" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="11" fillId="18" borderId="6" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="164" fontId="11" fillId="18" borderId="6" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="left" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="11" fillId="18" borderId="6" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="164" fontId="11" fillId="18" borderId="6" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="11" fillId="18" borderId="6" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="164" fontId="11" fillId="18" borderId="6" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="165" fontId="11" fillId="18" borderId="6" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="165" fontId="11" fillId="18" borderId="6" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="right" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="186" fontId="11" fillId="2" borderId="5" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="186" fontId="11" fillId="2" borderId="5" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="left" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="17" fillId="2" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="164" fontId="17" fillId="2" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="187" fontId="11" fillId="16" borderId="5" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="187" fontId="11" fillId="16" borderId="5" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="left" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="178" fontId="11" fillId="18" borderId="6" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="178" fontId="11" fillId="18" borderId="6" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="left" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="188" fontId="11" fillId="18" borderId="7" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="188" fontId="11" fillId="18" borderId="7" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="left" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="178" fontId="11" fillId="18" borderId="5" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="178" fontId="11" fillId="18" borderId="5" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="left" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="11" fillId="18" borderId="5" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="164" fontId="11" fillId="18" borderId="5" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="left" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="165" fontId="11" fillId="18" borderId="5" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="165" fontId="11" fillId="18" borderId="5" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="right" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="188" fontId="11" fillId="18" borderId="8" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="188" fontId="11" fillId="18" borderId="8" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="left" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="189" fontId="11" fillId="18" borderId="8" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="189" fontId="11" fillId="18" borderId="8" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="left" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="189" fontId="11" fillId="18" borderId="9" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="189" fontId="11" fillId="18" borderId="9" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="left" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="18" fillId="16" borderId="5" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="164" fontId="18" fillId="16" borderId="5" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="11" fillId="16" borderId="5" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="164" fontId="11" fillId="16" borderId="5" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="190" fontId="11" fillId="16" borderId="5" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="190" fontId="11" fillId="16" borderId="5" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="191" fontId="11" fillId="16" borderId="5" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="191" fontId="11" fillId="16" borderId="5" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="11" fillId="16" borderId="5" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="164" fontId="11" fillId="16" borderId="5" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="right" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="189" fontId="11" fillId="16" borderId="5" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="189" fontId="11" fillId="16" borderId="5" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="left" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="11" fillId="2" borderId="5" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="164" fontId="11" fillId="2" borderId="5" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="right" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="189" fontId="11" fillId="2" borderId="5" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="189" fontId="11" fillId="2" borderId="5" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="left" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="181" fontId="11" fillId="2" borderId="5" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="181" fontId="11" fillId="2" borderId="5" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="right" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="192" fontId="11" fillId="2" borderId="5" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="189" fontId="11" fillId="18" borderId="6" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="189" fontId="11" fillId="18" borderId="5" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="17" fillId="2" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="center" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="179" fontId="11" fillId="17" borderId="5" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="17" fillId="16" borderId="5" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="178" fontId="19" fillId="16" borderId="5" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="178" fontId="12" fillId="16" borderId="5" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="178" fontId="12" fillId="18" borderId="5" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="left" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="180" fontId="11" fillId="2" borderId="5" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="left" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="179" fontId="11" fillId="2" borderId="5" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="left" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="165" fontId="11" fillId="2" borderId="5" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="left" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="180" fontId="11" fillId="18" borderId="5" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="left" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="179" fontId="11" fillId="18" borderId="5" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="left" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="165" fontId="11" fillId="18" borderId="5" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="left" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="184" fontId="11" fillId="2" borderId="5" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="left" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="171" fontId="11" fillId="2" borderId="5" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="left" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="184" fontId="11" fillId="13" borderId="5" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="left" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="171" fontId="11" fillId="13" borderId="5" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="left" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="184" fontId="11" fillId="14" borderId="5" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="left" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="171" fontId="11" fillId="14" borderId="5" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="left" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="178" fontId="12" fillId="2" borderId="5" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="left" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="178" fontId="12" fillId="2" borderId="5" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="center" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="192" fontId="12" fillId="2" borderId="5" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="center" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="179" fontId="11" fillId="2" borderId="5" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="center" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="180" fontId="11" fillId="18" borderId="6" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="right" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="189" fontId="11" fillId="18" borderId="6" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="193" fontId="11" fillId="18" borderId="6" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="center" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="179" fontId="11" fillId="18" borderId="6" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="center" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="165" fontId="11" fillId="18" borderId="6" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="right" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="179" fontId="11" fillId="18" borderId="6" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="right" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="180" fontId="11" fillId="18" borderId="5" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="right" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="193" fontId="11" fillId="18" borderId="5" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="center" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="179" fontId="11" fillId="18" borderId="5" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="center" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="165" fontId="11" fillId="18" borderId="5" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="right" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="194" fontId="16" fillId="2" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="center" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="186" fontId="11" fillId="16" borderId="5" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="185" fontId="11" fillId="16" borderId="5" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="195" fontId="11" fillId="16" borderId="5" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="13" fillId="16" borderId="5" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="194" fontId="16" fillId="18" borderId="5" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="center" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="178" fontId="13" fillId="2" borderId="5" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="left" vertical="top" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="165" fontId="13" fillId="2" borderId="5" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="right" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="178" fontId="13" fillId="2" borderId="5" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="center" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="13" fillId="2" borderId="5" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="center" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="178" fontId="13" fillId="2" borderId="5" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="left" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="169" fontId="13" fillId="13" borderId="5" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="right" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="167" fontId="13" fillId="13" borderId="5" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="right" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="171" fontId="13" fillId="13" borderId="5" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="right" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="18" fillId="16" borderId="5" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="171" fontId="11" fillId="13" borderId="5" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="right" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="172" fontId="11" fillId="13" borderId="5" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="right" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="169" fontId="11" fillId="13" borderId="5" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="right" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="170" fontId="11" fillId="13" borderId="5" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="right" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="11" fillId="18" borderId="5" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="left" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="11" fillId="2" borderId="5" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="center" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="196" fontId="16" fillId="2" borderId="5" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="right" vertical="top" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="192" fontId="11" fillId="2" borderId="5" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="right" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="197" fontId="11" fillId="18" borderId="6" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="left" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="189" fontId="11" fillId="18" borderId="5" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="164" fontId="11" fillId="2" borderId="5" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="left" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="192" fontId="11" fillId="2" borderId="5" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="left" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="178" fontId="11" fillId="18" borderId="5" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="left" vertical="top" textRotation="0" wrapText="true" indent="4" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="11" fillId="18" borderId="5" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="left" vertical="top" textRotation="0" wrapText="true" indent="4" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="12" fillId="18" borderId="5" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="left" vertical="top" textRotation="0" wrapText="true" indent="4" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="12" fillId="18" borderId="6" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="left" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="17" fillId="2" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="center" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="179" fontId="11" fillId="17" borderId="5" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="17" fillId="16" borderId="5" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="178" fontId="19" fillId="16" borderId="5" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="178" fontId="12" fillId="16" borderId="5" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="178" fontId="12" fillId="18" borderId="5" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="178" fontId="14" fillId="18" borderId="5" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="left" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="180" fontId="11" fillId="2" borderId="5" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="178" fontId="14" fillId="2" borderId="5" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="left" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="179" fontId="11" fillId="2" borderId="5" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="left" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="165" fontId="11" fillId="2" borderId="5" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="left" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="180" fontId="11" fillId="18" borderId="5" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="left" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="179" fontId="11" fillId="18" borderId="5" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="left" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="165" fontId="11" fillId="18" borderId="5" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="left" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="184" fontId="11" fillId="2" borderId="5" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="left" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="171" fontId="11" fillId="2" borderId="5" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="left" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="184" fontId="11" fillId="13" borderId="5" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="left" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="171" fontId="11" fillId="13" borderId="5" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="left" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="184" fontId="11" fillId="14" borderId="5" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="left" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="171" fontId="11" fillId="14" borderId="5" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="left" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="178" fontId="12" fillId="2" borderId="5" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="left" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="178" fontId="12" fillId="2" borderId="5" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="center" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="193" fontId="12" fillId="2" borderId="5" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="center" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="179" fontId="11" fillId="2" borderId="5" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="center" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="180" fontId="11" fillId="18" borderId="6" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="176" fontId="11" fillId="2" borderId="5" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="right" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="194" fontId="11" fillId="18" borderId="6" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="center" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="179" fontId="11" fillId="18" borderId="6" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="center" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="165" fontId="11" fillId="18" borderId="6" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="178" fontId="13" fillId="2" borderId="5" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="right" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="179" fontId="11" fillId="18" borderId="6" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="right" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="180" fontId="11" fillId="18" borderId="5" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="198" fontId="11" fillId="13" borderId="5" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="right" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="194" fontId="11" fillId="18" borderId="5" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="center" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="179" fontId="11" fillId="18" borderId="5" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="center" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="165" fontId="11" fillId="18" borderId="5" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="165" fontId="14" fillId="2" borderId="5" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="right" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="195" fontId="16" fillId="2" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="center" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="186" fontId="11" fillId="16" borderId="5" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="185" fontId="11" fillId="16" borderId="5" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="196" fontId="11" fillId="16" borderId="5" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="13" fillId="16" borderId="5" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="195" fontId="16" fillId="18" borderId="5" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="center" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="178" fontId="13" fillId="2" borderId="5" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="left" vertical="top" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="165" fontId="13" fillId="2" borderId="5" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="199" fontId="11" fillId="13" borderId="5" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="right" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="178" fontId="13" fillId="2" borderId="5" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="center" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="13" fillId="2" borderId="5" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="center" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="178" fontId="13" fillId="2" borderId="5" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="left" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="169" fontId="13" fillId="13" borderId="5" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="200" fontId="11" fillId="13" borderId="5" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="right" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="167" fontId="13" fillId="13" borderId="5" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="201" fontId="11" fillId="13" borderId="5" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="right" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="171" fontId="13" fillId="13" borderId="5" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="202" fontId="11" fillId="13" borderId="5" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="right" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="18" fillId="16" borderId="5" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="171" fontId="11" fillId="13" borderId="5" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="203" fontId="11" fillId="13" borderId="5" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="right" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="172" fontId="11" fillId="13" borderId="5" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="204" fontId="11" fillId="13" borderId="5" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="right" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="169" fontId="11" fillId="13" borderId="5" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="right" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="170" fontId="11" fillId="13" borderId="5" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="right" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="11" fillId="18" borderId="5" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="left" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="11" fillId="2" borderId="5" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="center" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="197" fontId="16" fillId="2" borderId="5" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="right" vertical="top" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="193" fontId="11" fillId="2" borderId="5" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="right" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="198" fontId="11" fillId="18" borderId="6" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="11" fillId="2" borderId="5" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="left" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="193" fontId="11" fillId="2" borderId="5" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="left" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="178" fontId="11" fillId="18" borderId="5" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="left" vertical="top" textRotation="0" wrapText="true" indent="4" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="11" fillId="18" borderId="5" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="left" vertical="top" textRotation="0" wrapText="true" indent="4" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="12" fillId="18" borderId="5" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="left" vertical="top" textRotation="0" wrapText="true" indent="4" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="12" fillId="18" borderId="6" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="178" fontId="14" fillId="18" borderId="5" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="left" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="178" fontId="14" fillId="2" borderId="5" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="left" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="176" fontId="11" fillId="2" borderId="5" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="right" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="178" fontId="13" fillId="2" borderId="5" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="right" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="199" fontId="11" fillId="13" borderId="5" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="right" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="165" fontId="14" fillId="2" borderId="5" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="right" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="200" fontId="11" fillId="13" borderId="5" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="right" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="201" fontId="11" fillId="13" borderId="5" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="right" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="202" fontId="11" fillId="13" borderId="5" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="right" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="203" fontId="11" fillId="13" borderId="5" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="right" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="204" fontId="11" fillId="13" borderId="5" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="right" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="205" fontId="11" fillId="13" borderId="5" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="right" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="20" fillId="2" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="164" fontId="20" fillId="2" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -2309,7 +2310,7 @@
     <cellStyle name="Input" xfId="59"/>
     <cellStyle name="Résultat2" xfId="60"/>
   </cellStyles>
-  <dxfs count="29">
+  <dxfs count="30">
     <dxf>
       <font>
         <name val="Arial"/>
@@ -2647,13 +2648,13 @@
       </fill>
     </dxf>
     <dxf>
-      <font>
-        <name val="Arial"/>
-        <charset val="1"/>
-        <family val="2"/>
-        <color rgb="FF000000"/>
-      </font>
-      <numFmt numFmtId="164" formatCode="General"/>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
       <fill>
         <patternFill>
           <bgColor rgb="FFFFFC98"/>
@@ -2661,15 +2662,9 @@
       </fill>
     </dxf>
     <dxf>
-      <font>
-        <name val="Arial"/>
-        <charset val="1"/>
-        <family val="2"/>
-      </font>
-      <numFmt numFmtId="164" formatCode="General"/>
       <fill>
         <patternFill>
-          <bgColor rgb="FFD5D5D5"/>
+          <bgColor rgb="FFFFC7CE"/>
         </patternFill>
       </fill>
     </dxf>
@@ -2872,7 +2867,7 @@
   <sheetData>
     <row r="2" customFormat="false" ht="16.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B2" s="2" t="str">
-        <f aca="false">Contrôles!K$49</f>
+        <f aca="false">Contrôles!K$52</f>
         <v>✓</v>
       </c>
       <c r="C2" s="3" t="s">
@@ -4230,7 +4225,7 @@
     </row>
     <row r="2" customFormat="false" ht="16.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A2" s="49" t="str">
-        <f aca="false">Contrôles!K$49</f>
+        <f aca="false">Contrôles!K$52</f>
         <v>✓</v>
       </c>
       <c r="B2" s="5"/>
@@ -5565,13 +5560,13 @@
   <sheetData>
     <row r="1" customFormat="false" ht="16.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A1" s="51" t="str">
-        <f aca="false">Contrôles!K$49</f>
+        <f aca="false">Contrôles!K$52</f>
         <v>✓</v>
       </c>
       <c r="B1" s="12"/>
       <c r="C1" s="75" t="n">
         <f aca="false">C$2-365</f>
-        <v>45857</v>
+        <v>45913</v>
       </c>
       <c r="D1" s="75"/>
     </row>
@@ -5580,7 +5575,7 @@
       <c r="B2" s="12"/>
       <c r="C2" s="75" t="n">
         <f aca="true">TODAY()</f>
-        <v>46222</v>
+        <v>46278</v>
       </c>
       <c r="D2" s="75"/>
     </row>
@@ -5905,7 +5900,7 @@
         <f aca="false">SUMPRODUCT(SUMIFS(OPmontant,OPcatégorie,$E27,OPdate,"&gt;"&amp;$C$2-365,OPdevise,COTcode)*COTcours)</f>
         <v>-0.65626</v>
       </c>
-      <c r="H27" s="93" t="n">
+      <c r="H27" s="92" t="n">
         <v>1</v>
       </c>
       <c r="I27" s="16" t="n">
@@ -5928,7 +5923,7 @@
         <f aca="false">SUMPRODUCT(SUMIFS(OPmontant,OPcatégorie,$E28,OPdate,"&gt;"&amp;$C$2-365,OPdevise,COTcode)*COTcours)</f>
         <v>9.01494</v>
       </c>
-      <c r="H28" s="93" t="n">
+      <c r="H28" s="92" t="n">
         <v>1</v>
       </c>
       <c r="I28" s="16" t="n">
@@ -5951,7 +5946,7 @@
         <f aca="false">SUMPRODUCT(SUMIFS(OPmontant,OPcatégorie,$E29,OPdate,"&gt;"&amp;$C$2-365,OPdevise,COTcode)*COTcours)</f>
         <v>-8.635</v>
       </c>
-      <c r="H29" s="93" t="n">
+      <c r="H29" s="92" t="n">
         <v>1</v>
       </c>
       <c r="I29" s="16" t="n">
@@ -5974,7 +5969,7 @@
         <f aca="false">SUMPRODUCT(SUMIFS(OPmontant,OPcatégorie,$E30,OPdate,"&gt;"&amp;$C$2-365,OPdevise,COTcode)*COTcours)</f>
         <v>0</v>
       </c>
-      <c r="H30" s="93" t="n">
+      <c r="H30" s="92" t="n">
         <v>1</v>
       </c>
       <c r="I30" s="16" t="n">
@@ -5997,7 +5992,7 @@
         <f aca="false">SUMPRODUCT(SUMIFS(OPmontant,OPcatégorie,$E31,OPdate,"&gt;"&amp;$C$2-365,OPdevise,COTcode)*COTcours)</f>
         <v>-120</v>
       </c>
-      <c r="H31" s="93" t="n">
+      <c r="H31" s="92" t="n">
         <v>1</v>
       </c>
       <c r="I31" s="16" t="n">
@@ -6020,7 +6015,7 @@
         <f aca="false">SUMPRODUCT(SUMIFS(OPmontant,OPcatégorie,$E32,OPdate,"&gt;"&amp;$C$2-365,OPdevise,COTcode)*COTcours)</f>
         <v>-1670</v>
       </c>
-      <c r="H32" s="93" t="n">
+      <c r="H32" s="92" t="n">
         <v>1</v>
       </c>
       <c r="I32" s="16" t="n">
@@ -6043,7 +6038,7 @@
         <f aca="false">SUMPRODUCT(SUMIFS(OPmontant,OPcatégorie,$E33,OPdate,"&gt;"&amp;$C$2-365,OPdevise,COTcode)*COTcours)</f>
         <v>0</v>
       </c>
-      <c r="H33" s="93" t="n">
+      <c r="H33" s="92" t="n">
         <v>1</v>
       </c>
       <c r="I33" s="16" t="n">
@@ -6066,7 +6061,7 @@
         <f aca="false">SUMPRODUCT(SUMIFS(OPmontant,OPcatégorie,$E34,OPdate,"&gt;"&amp;$C$2-365,OPdevise,COTcode)*COTcours)</f>
         <v>0</v>
       </c>
-      <c r="H34" s="93" t="n">
+      <c r="H34" s="92" t="n">
         <v>1</v>
       </c>
       <c r="I34" s="16" t="n">
@@ -6099,9 +6094,9 @@
         <f aca="false">SUM(CATtotal_euro)</f>
         <v>-1781.646185</v>
       </c>
-      <c r="H36" s="94"/>
+      <c r="H36" s="93"/>
       <c r="I36" s="72"/>
-      <c r="J36" s="94"/>
+      <c r="J36" s="93"/>
     </row>
     <row r="37" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="E37" s="78" t="s">
@@ -6115,9 +6110,9 @@
         <f aca="false">SUMPRODUCT(SUMIFS(OPmontant,OPdate,"&gt;"&amp;$C$2-365,OPcatégorie,"&lt;&gt;"&amp;Spéciale,OPdevise,COTcode)*COTcours)</f>
         <v>-1781.646185</v>
       </c>
-      <c r="H37" s="95"/>
+      <c r="H37" s="94"/>
       <c r="I37" s="80"/>
-      <c r="J37" s="95"/>
+      <c r="J37" s="94"/>
     </row>
     <row r="38" customFormat="false" ht="16.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="E38" s="78" t="s">
@@ -6131,9 +6126,9 @@
         <f aca="false">ROUND(G$36-G$37,2)</f>
         <v>0</v>
       </c>
-      <c r="H38" s="95"/>
+      <c r="H38" s="94"/>
       <c r="I38" s="80"/>
-      <c r="J38" s="95"/>
+      <c r="J38" s="94"/>
     </row>
     <row r="39" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="E39" s="78" t="s">
@@ -6147,12 +6142,12 @@
         <f aca="false">SUMIFS(CATtotal_euro,CATnom,"&lt;&gt;@*")</f>
         <v>-1790.27632</v>
       </c>
-      <c r="H39" s="95"/>
+      <c r="H39" s="94"/>
       <c r="I39" s="80" t="n">
         <f aca="false">SUMIFS(CATaffectation,CATnom,"&lt;&gt;@*")</f>
         <v>-1790.27632</v>
       </c>
-      <c r="J39" s="95"/>
+      <c r="J39" s="94"/>
     </row>
     <row r="40" customFormat="false" ht="16.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="E40" s="78" t="s">
@@ -6166,9 +6161,9 @@
         <f aca="false">SUM(F$40)</f>
         <v>-1790</v>
       </c>
-      <c r="H40" s="95"/>
+      <c r="H40" s="94"/>
       <c r="I40" s="80"/>
-      <c r="J40" s="95"/>
+      <c r="J40" s="94"/>
     </row>
     <row r="1048495" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
     <row r="1048496" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
@@ -6362,21 +6357,21 @@
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="74" width="31.42"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="74" width="28.57"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="74" width="15.09"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="96" width="17.62"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="95" width="17.62"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="74" width="13.67"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="7" style="96" width="9.16"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="7" style="95" width="9.16"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="8" min="8" style="74" width="15.66"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="9" min="9" style="74" width="17.74"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="10" min="10" style="74" width="15.66"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="11" min="11" style="96" width="17.74"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="12" min="12" style="96" width="13.67"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="11" min="11" style="95" width="17.74"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="12" min="12" style="95" width="13.67"/>
     <col collapsed="false" customWidth="false" hidden="false" outlineLevel="0" max="16379" min="13" style="74" width="13.16"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="16384" min="16380" style="74" width="11.53"/>
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="16.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A1" s="85" t="str">
-        <f aca="false">Contrôles!$K49</f>
+        <f aca="false">Contrôles!$K52</f>
         <v>✓</v>
       </c>
       <c r="B1" s="47" t="s">
@@ -6420,7 +6415,7 @@
         <v>1455.0077973604</v>
       </c>
       <c r="F3" s="85"/>
-      <c r="G3" s="97" t="n">
+      <c r="G3" s="96" t="n">
         <f aca="false">G53</f>
         <v>44927</v>
       </c>
@@ -6430,7 +6425,7 @@
       <c r="K3" s="12"/>
     </row>
     <row r="4" customFormat="false" ht="24.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A4" s="98" t="s">
+      <c r="A4" s="97" t="s">
         <v>158</v>
       </c>
       <c r="B4" s="26" t="s">
@@ -6442,7 +6437,7 @@
       <c r="D4" s="26" t="s">
         <v>88</v>
       </c>
-      <c r="E4" s="99" t="s">
+      <c r="E4" s="98" t="s">
         <v>160</v>
       </c>
       <c r="F4" s="26" t="s">
@@ -6454,13 +6449,13 @@
       <c r="H4" s="26" t="s">
         <v>163</v>
       </c>
-      <c r="I4" s="100" t="s">
+      <c r="I4" s="99" t="s">
         <v>164</v>
       </c>
       <c r="J4" s="51" t="s">
         <v>165</v>
       </c>
-      <c r="K4" s="100" t="s">
+      <c r="K4" s="99" t="s">
         <v>166</v>
       </c>
     </row>
@@ -6480,7 +6475,7 @@
       <c r="K5" s="52"/>
     </row>
     <row r="6" customFormat="false" ht="16.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A6" s="101" t="s">
+      <c r="A6" s="100" t="s">
         <v>167</v>
       </c>
       <c r="B6" s="52"/>
@@ -6508,7 +6503,7 @@
       <c r="K7" s="52"/>
     </row>
     <row r="8" customFormat="false" ht="16.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A8" s="101" t="s">
+      <c r="A8" s="100" t="s">
         <v>168</v>
       </c>
       <c r="B8" s="52" t="s">
@@ -6518,16 +6513,16 @@
         <v>73</v>
       </c>
       <c r="D8" s="52"/>
-      <c r="E8" s="102"/>
+      <c r="E8" s="101"/>
       <c r="F8" s="52"/>
-      <c r="G8" s="103"/>
-      <c r="H8" s="104"/>
-      <c r="I8" s="104"/>
-      <c r="J8" s="103"/>
-      <c r="K8" s="102"/>
+      <c r="G8" s="102"/>
+      <c r="H8" s="103"/>
+      <c r="I8" s="103"/>
+      <c r="J8" s="102"/>
+      <c r="K8" s="101"/>
     </row>
     <row r="9" customFormat="false" ht="16.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A9" s="101" t="s">
+      <c r="A9" s="100" t="s">
         <v>168</v>
       </c>
       <c r="B9" s="32" t="s">
@@ -6539,27 +6534,27 @@
       <c r="D9" s="32" t="s">
         <v>95</v>
       </c>
-      <c r="E9" s="105" t="n">
+      <c r="E9" s="104" t="n">
         <f aca="false">K9-(H9+I9)</f>
         <v>0</v>
       </c>
       <c r="F9" s="32"/>
-      <c r="G9" s="106" t="n">
-        <v>0</v>
-      </c>
-      <c r="H9" s="107" t="n">
-        <v>0</v>
-      </c>
-      <c r="I9" s="107" t="n">
-        <v>0</v>
-      </c>
-      <c r="J9" s="106"/>
-      <c r="K9" s="105" t="n">
+      <c r="G9" s="105" t="n">
+        <v>0</v>
+      </c>
+      <c r="H9" s="106" t="n">
+        <v>0</v>
+      </c>
+      <c r="I9" s="106" t="n">
+        <v>0</v>
+      </c>
+      <c r="J9" s="105"/>
+      <c r="K9" s="104" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="16.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A10" s="101" t="s">
+      <c r="A10" s="100" t="s">
         <v>168</v>
       </c>
       <c r="B10" s="32" t="s">
@@ -6571,34 +6566,34 @@
       <c r="D10" s="32" t="s">
         <v>95</v>
       </c>
-      <c r="E10" s="105" t="n">
+      <c r="E10" s="104" t="n">
         <f aca="false">K10-(H10+I10)</f>
         <v>0</v>
       </c>
       <c r="F10" s="32"/>
-      <c r="G10" s="106" t="n">
+      <c r="G10" s="105" t="n">
         <f aca="false">_xlfn.MINIFS(OPdate,OPcompte,$B10,OPdevise,D10,OPcatégorie,Solde)</f>
         <v>0</v>
       </c>
-      <c r="H10" s="107" t="n">
+      <c r="H10" s="106" t="n">
         <f aca="false">SUMIFS(OPmontant,OPcompte,$B10,OPdevise,$D10,OPdate,$G10,OPcatégorie,Solde)</f>
         <v>0</v>
       </c>
-      <c r="I10" s="107" t="n">
+      <c r="I10" s="106" t="n">
         <f aca="false">I9</f>
         <v>0</v>
       </c>
-      <c r="J10" s="106" t="n">
+      <c r="J10" s="105" t="n">
         <f aca="false">_xlfn.MAXIFS(OPdate,OPcompte,$B10,OPdevise,$D10,OPcatégorie,Solde)</f>
         <v>0</v>
       </c>
-      <c r="K10" s="105" t="n">
+      <c r="K10" s="104" t="n">
         <f aca="false">SUMIFS(OPmontant,OPcompte,$B10,OPdevise,$D10,OPcatégorie,Solde,OPdate,J10)</f>
         <v>0</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="16.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A11" s="101" t="s">
+      <c r="A11" s="100" t="s">
         <v>168</v>
       </c>
       <c r="B11" s="32" t="s">
@@ -6610,28 +6605,28 @@
       <c r="D11" s="32" t="s">
         <v>95</v>
       </c>
-      <c r="E11" s="105" t="n">
+      <c r="E11" s="104" t="n">
         <f aca="false">K11-(H11+I11)</f>
         <v>0</v>
       </c>
       <c r="F11" s="32"/>
-      <c r="G11" s="106" t="n">
+      <c r="G11" s="105" t="n">
         <f aca="false">G10</f>
         <v>0</v>
       </c>
-      <c r="H11" s="107" t="n">
+      <c r="H11" s="106" t="n">
         <f aca="false">H10</f>
         <v>0</v>
       </c>
-      <c r="I11" s="107" t="n">
+      <c r="I11" s="106" t="n">
         <f aca="false">I10</f>
         <v>0</v>
       </c>
-      <c r="J11" s="106" t="n">
+      <c r="J11" s="105" t="n">
         <f aca="false">IF(J9&gt;J10,J9,J10)</f>
         <v>0</v>
       </c>
-      <c r="K11" s="105" t="n">
+      <c r="K11" s="104" t="n">
         <f aca="false">IF(J9&gt;J10,K9,K10)</f>
         <v>0</v>
       </c>
@@ -6650,7 +6645,7 @@
       <c r="K12" s="52"/>
     </row>
     <row r="13" customFormat="false" ht="16.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A13" s="101" t="s">
+      <c r="A13" s="100" t="s">
         <v>168</v>
       </c>
       <c r="B13" s="52" t="s">
@@ -6660,16 +6655,16 @@
         <v>73</v>
       </c>
       <c r="D13" s="52"/>
-      <c r="E13" s="102"/>
+      <c r="E13" s="101"/>
       <c r="F13" s="52"/>
-      <c r="G13" s="103"/>
-      <c r="H13" s="104"/>
-      <c r="I13" s="104"/>
-      <c r="J13" s="103"/>
-      <c r="K13" s="102"/>
+      <c r="G13" s="102"/>
+      <c r="H13" s="103"/>
+      <c r="I13" s="103"/>
+      <c r="J13" s="102"/>
+      <c r="K13" s="101"/>
     </row>
     <row r="14" customFormat="false" ht="16.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A14" s="101" t="s">
+      <c r="A14" s="100" t="s">
         <v>168</v>
       </c>
       <c r="B14" s="32" t="s">
@@ -6681,27 +6676,27 @@
       <c r="D14" s="32" t="s">
         <v>95</v>
       </c>
-      <c r="E14" s="105" t="n">
+      <c r="E14" s="104" t="n">
         <f aca="false">K14-(H14+I14)</f>
         <v>0</v>
       </c>
       <c r="F14" s="32"/>
-      <c r="G14" s="106" t="n">
-        <v>0</v>
-      </c>
-      <c r="H14" s="107" t="n">
-        <v>0</v>
-      </c>
-      <c r="I14" s="107" t="n">
-        <v>0</v>
-      </c>
-      <c r="J14" s="106"/>
-      <c r="K14" s="105" t="n">
+      <c r="G14" s="105" t="n">
+        <v>0</v>
+      </c>
+      <c r="H14" s="106" t="n">
+        <v>0</v>
+      </c>
+      <c r="I14" s="106" t="n">
+        <v>0</v>
+      </c>
+      <c r="J14" s="105"/>
+      <c r="K14" s="104" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="16.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A15" s="101" t="s">
+      <c r="A15" s="100" t="s">
         <v>168</v>
       </c>
       <c r="B15" s="32" t="s">
@@ -6713,34 +6708,34 @@
       <c r="D15" s="32" t="s">
         <v>95</v>
       </c>
-      <c r="E15" s="105" t="n">
+      <c r="E15" s="104" t="n">
         <f aca="false">K15-(H15+I15)</f>
         <v>0</v>
       </c>
       <c r="F15" s="32"/>
-      <c r="G15" s="106" t="n">
+      <c r="G15" s="105" t="n">
         <f aca="false">_xlfn.MINIFS(OPdate,OPcompte,$B15,OPdevise,D15,OPcatégorie,Solde)</f>
         <v>0</v>
       </c>
-      <c r="H15" s="107" t="n">
+      <c r="H15" s="106" t="n">
         <f aca="false">SUMIFS(OPmontant,OPcompte,$B15,OPdevise,$D15,OPdate,$G15,OPcatégorie,Solde)</f>
         <v>0</v>
       </c>
-      <c r="I15" s="107" t="n">
+      <c r="I15" s="106" t="n">
         <f aca="false">I14</f>
         <v>0</v>
       </c>
-      <c r="J15" s="106" t="n">
+      <c r="J15" s="105" t="n">
         <f aca="false">_xlfn.MAXIFS(OPdate,OPcompte,$B15,OPdevise,$D15,OPcatégorie,Solde)</f>
         <v>0</v>
       </c>
-      <c r="K15" s="105" t="n">
+      <c r="K15" s="104" t="n">
         <f aca="false">SUMIFS(OPmontant,OPcompte,$B15,OPdevise,$D15,OPcatégorie,Solde,OPdate,J15)</f>
         <v>0</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="16.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A16" s="101" t="s">
+      <c r="A16" s="100" t="s">
         <v>168</v>
       </c>
       <c r="B16" s="32" t="s">
@@ -6752,28 +6747,28 @@
       <c r="D16" s="32" t="s">
         <v>95</v>
       </c>
-      <c r="E16" s="105" t="n">
+      <c r="E16" s="104" t="n">
         <f aca="false">K16-(H16+I16)</f>
         <v>0</v>
       </c>
       <c r="F16" s="32"/>
-      <c r="G16" s="106" t="n">
+      <c r="G16" s="105" t="n">
         <f aca="false">G15</f>
         <v>0</v>
       </c>
-      <c r="H16" s="107" t="n">
+      <c r="H16" s="106" t="n">
         <f aca="false">H15</f>
         <v>0</v>
       </c>
-      <c r="I16" s="107" t="n">
+      <c r="I16" s="106" t="n">
         <f aca="false">I15</f>
         <v>0</v>
       </c>
-      <c r="J16" s="106" t="n">
+      <c r="J16" s="105" t="n">
         <f aca="false">IF(J14&gt;J15,J14,J15)</f>
         <v>0</v>
       </c>
-      <c r="K16" s="105" t="n">
+      <c r="K16" s="104" t="n">
         <f aca="false">IF(J14&gt;J15,K14,K15)</f>
         <v>0</v>
       </c>
@@ -6792,7 +6787,7 @@
       <c r="K17" s="52"/>
     </row>
     <row r="18" customFormat="false" ht="16.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A18" s="101" t="s">
+      <c r="A18" s="100" t="s">
         <v>168</v>
       </c>
       <c r="B18" s="52" t="s">
@@ -6802,16 +6797,16 @@
         <v>73</v>
       </c>
       <c r="D18" s="52"/>
-      <c r="E18" s="102"/>
+      <c r="E18" s="101"/>
       <c r="F18" s="52"/>
-      <c r="G18" s="103"/>
-      <c r="H18" s="104"/>
-      <c r="I18" s="104"/>
-      <c r="J18" s="103"/>
-      <c r="K18" s="102"/>
+      <c r="G18" s="102"/>
+      <c r="H18" s="103"/>
+      <c r="I18" s="103"/>
+      <c r="J18" s="102"/>
+      <c r="K18" s="101"/>
     </row>
     <row r="19" customFormat="false" ht="16.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A19" s="101" t="s">
+      <c r="A19" s="100" t="s">
         <v>168</v>
       </c>
       <c r="B19" s="32" t="s">
@@ -6823,27 +6818,27 @@
       <c r="D19" s="32" t="s">
         <v>95</v>
       </c>
-      <c r="E19" s="105" t="n">
+      <c r="E19" s="104" t="n">
         <f aca="false">K19-(H19+I19)</f>
         <v>0</v>
       </c>
       <c r="F19" s="32"/>
-      <c r="G19" s="106" t="n">
-        <v>0</v>
-      </c>
-      <c r="H19" s="107" t="n">
-        <v>0</v>
-      </c>
-      <c r="I19" s="107" t="n">
-        <v>0</v>
-      </c>
-      <c r="J19" s="106"/>
-      <c r="K19" s="105" t="n">
+      <c r="G19" s="105" t="n">
+        <v>0</v>
+      </c>
+      <c r="H19" s="106" t="n">
+        <v>0</v>
+      </c>
+      <c r="I19" s="106" t="n">
+        <v>0</v>
+      </c>
+      <c r="J19" s="105"/>
+      <c r="K19" s="104" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="16.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A20" s="101" t="s">
+      <c r="A20" s="100" t="s">
         <v>168</v>
       </c>
       <c r="B20" s="32" t="s">
@@ -6855,34 +6850,34 @@
       <c r="D20" s="32" t="s">
         <v>95</v>
       </c>
-      <c r="E20" s="105" t="n">
+      <c r="E20" s="104" t="n">
         <f aca="false">K20-(H20+I20)</f>
         <v>0</v>
       </c>
       <c r="F20" s="32"/>
-      <c r="G20" s="106" t="n">
+      <c r="G20" s="105" t="n">
         <f aca="false">_xlfn.MINIFS(OPdate,OPcompte,$B20,OPdevise,D20,OPcatégorie,Solde)</f>
         <v>0</v>
       </c>
-      <c r="H20" s="107" t="n">
+      <c r="H20" s="106" t="n">
         <f aca="false">SUMIFS(OPmontant,OPcompte,$B20,OPdevise,$D20,OPdate,$G20,OPcatégorie,Solde)</f>
         <v>0</v>
       </c>
-      <c r="I20" s="107" t="n">
+      <c r="I20" s="106" t="n">
         <f aca="false">I19</f>
         <v>0</v>
       </c>
-      <c r="J20" s="106" t="n">
+      <c r="J20" s="105" t="n">
         <f aca="false">_xlfn.MAXIFS(OPdate,OPcompte,$B20,OPdevise,$D20,OPcatégorie,Solde)</f>
         <v>0</v>
       </c>
-      <c r="K20" s="105" t="n">
+      <c r="K20" s="104" t="n">
         <f aca="false">SUMIFS(OPmontant,OPcompte,$B20,OPdevise,$D20,OPcatégorie,Solde,OPdate,J20)</f>
         <v>0</v>
       </c>
     </row>
     <row r="21" customFormat="false" ht="16.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A21" s="101" t="s">
+      <c r="A21" s="100" t="s">
         <v>168</v>
       </c>
       <c r="B21" s="32" t="s">
@@ -6894,28 +6889,28 @@
       <c r="D21" s="32" t="s">
         <v>95</v>
       </c>
-      <c r="E21" s="105" t="n">
+      <c r="E21" s="104" t="n">
         <f aca="false">K21-(H21+I21)</f>
         <v>0</v>
       </c>
       <c r="F21" s="32"/>
-      <c r="G21" s="106" t="n">
+      <c r="G21" s="105" t="n">
         <f aca="false">G20</f>
         <v>0</v>
       </c>
-      <c r="H21" s="107" t="n">
+      <c r="H21" s="106" t="n">
         <f aca="false">H20</f>
         <v>0</v>
       </c>
-      <c r="I21" s="107" t="n">
+      <c r="I21" s="106" t="n">
         <f aca="false">I20</f>
         <v>0</v>
       </c>
-      <c r="J21" s="106" t="n">
+      <c r="J21" s="105" t="n">
         <f aca="false">IF(J19&gt;J20,J19,J20)</f>
         <v>0</v>
       </c>
-      <c r="K21" s="105" t="n">
+      <c r="K21" s="104" t="n">
         <f aca="false">IF(J19&gt;J20,K19,K20)</f>
         <v>0</v>
       </c>
@@ -6934,7 +6929,7 @@
       <c r="K22" s="52"/>
     </row>
     <row r="23" customFormat="false" ht="16.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A23" s="101" t="s">
+      <c r="A23" s="100" t="s">
         <v>168</v>
       </c>
       <c r="B23" s="52" t="s">
@@ -6944,16 +6939,16 @@
         <v>73</v>
       </c>
       <c r="D23" s="52"/>
-      <c r="E23" s="102"/>
+      <c r="E23" s="101"/>
       <c r="F23" s="52"/>
-      <c r="G23" s="103"/>
-      <c r="H23" s="104"/>
-      <c r="I23" s="104"/>
-      <c r="J23" s="103"/>
-      <c r="K23" s="102"/>
+      <c r="G23" s="102"/>
+      <c r="H23" s="103"/>
+      <c r="I23" s="103"/>
+      <c r="J23" s="102"/>
+      <c r="K23" s="101"/>
     </row>
     <row r="24" customFormat="false" ht="16.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A24" s="101" t="s">
+      <c r="A24" s="100" t="s">
         <v>168</v>
       </c>
       <c r="B24" s="32" t="s">
@@ -6965,27 +6960,27 @@
       <c r="D24" s="32" t="s">
         <v>95</v>
       </c>
-      <c r="E24" s="105" t="n">
+      <c r="E24" s="104" t="n">
         <f aca="false">K24-(H24+I24)</f>
         <v>0</v>
       </c>
       <c r="F24" s="32"/>
-      <c r="G24" s="106" t="n">
-        <v>0</v>
-      </c>
-      <c r="H24" s="107" t="n">
-        <v>0</v>
-      </c>
-      <c r="I24" s="107" t="n">
-        <v>0</v>
-      </c>
-      <c r="J24" s="106"/>
-      <c r="K24" s="105" t="n">
+      <c r="G24" s="105" t="n">
+        <v>0</v>
+      </c>
+      <c r="H24" s="106" t="n">
+        <v>0</v>
+      </c>
+      <c r="I24" s="106" t="n">
+        <v>0</v>
+      </c>
+      <c r="J24" s="105"/>
+      <c r="K24" s="104" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="25" customFormat="false" ht="16.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A25" s="101" t="s">
+      <c r="A25" s="100" t="s">
         <v>168</v>
       </c>
       <c r="B25" s="32" t="s">
@@ -6997,34 +6992,34 @@
       <c r="D25" s="32" t="s">
         <v>95</v>
       </c>
-      <c r="E25" s="105" t="n">
+      <c r="E25" s="104" t="n">
         <f aca="false">K25-(H25+I25)</f>
         <v>0</v>
       </c>
       <c r="F25" s="32"/>
-      <c r="G25" s="106" t="n">
+      <c r="G25" s="105" t="n">
         <f aca="false">_xlfn.MINIFS(OPdate,OPcompte,$B25,OPdevise,D25,OPcatégorie,Solde)</f>
         <v>0</v>
       </c>
-      <c r="H25" s="107" t="n">
+      <c r="H25" s="106" t="n">
         <f aca="false">SUMIFS(OPmontant,OPcompte,$B25,OPdevise,$D25,OPdate,$G25,OPcatégorie,Solde)</f>
         <v>0</v>
       </c>
-      <c r="I25" s="107" t="n">
+      <c r="I25" s="106" t="n">
         <f aca="false">I24</f>
         <v>0</v>
       </c>
-      <c r="J25" s="106" t="n">
+      <c r="J25" s="105" t="n">
         <f aca="false">_xlfn.MAXIFS(OPdate,OPcompte,$B25,OPdevise,$D25,OPcatégorie,Solde)</f>
         <v>0</v>
       </c>
-      <c r="K25" s="105" t="n">
+      <c r="K25" s="104" t="n">
         <f aca="false">SUMIFS(OPmontant,OPcompte,$B25,OPdevise,$D25,OPcatégorie,Solde,OPdate,J25)</f>
         <v>0</v>
       </c>
     </row>
     <row r="26" customFormat="false" ht="16.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A26" s="101" t="s">
+      <c r="A26" s="100" t="s">
         <v>168</v>
       </c>
       <c r="B26" s="32" t="s">
@@ -7036,28 +7031,28 @@
       <c r="D26" s="32" t="s">
         <v>95</v>
       </c>
-      <c r="E26" s="105" t="n">
+      <c r="E26" s="104" t="n">
         <f aca="false">K26-(H26+I26)</f>
         <v>0</v>
       </c>
       <c r="F26" s="32"/>
-      <c r="G26" s="106" t="n">
+      <c r="G26" s="105" t="n">
         <f aca="false">G25</f>
         <v>0</v>
       </c>
-      <c r="H26" s="107" t="n">
+      <c r="H26" s="106" t="n">
         <f aca="false">H25</f>
         <v>0</v>
       </c>
-      <c r="I26" s="107" t="n">
+      <c r="I26" s="106" t="n">
         <f aca="false">I25</f>
         <v>0</v>
       </c>
-      <c r="J26" s="106" t="n">
+      <c r="J26" s="105" t="n">
         <f aca="false">IF(J24&gt;J25,J24,J25)</f>
         <v>0</v>
       </c>
-      <c r="K26" s="105" t="n">
+      <c r="K26" s="104" t="n">
         <f aca="false">IF(J24&gt;J25,K24,K25)</f>
         <v>0</v>
       </c>
@@ -7076,7 +7071,7 @@
       <c r="K27" s="52"/>
     </row>
     <row r="28" customFormat="false" ht="16.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A28" s="101" t="s">
+      <c r="A28" s="100" t="s">
         <v>168</v>
       </c>
       <c r="B28" s="52" t="s">
@@ -7086,16 +7081,16 @@
         <v>73</v>
       </c>
       <c r="D28" s="52"/>
-      <c r="E28" s="108"/>
+      <c r="E28" s="107"/>
       <c r="F28" s="52"/>
-      <c r="G28" s="103"/>
-      <c r="H28" s="109"/>
-      <c r="I28" s="109"/>
-      <c r="J28" s="103"/>
-      <c r="K28" s="108"/>
+      <c r="G28" s="102"/>
+      <c r="H28" s="108"/>
+      <c r="I28" s="108"/>
+      <c r="J28" s="102"/>
+      <c r="K28" s="107"/>
     </row>
     <row r="29" customFormat="false" ht="16.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A29" s="101" t="s">
+      <c r="A29" s="100" t="s">
         <v>168</v>
       </c>
       <c r="B29" s="52" t="s">
@@ -7107,30 +7102,30 @@
       <c r="D29" s="52" t="s">
         <v>100</v>
       </c>
-      <c r="E29" s="110" t="n">
+      <c r="E29" s="109" t="n">
         <f aca="false">K29-(H29+I29)</f>
         <v>2.62</v>
       </c>
       <c r="F29" s="52"/>
-      <c r="G29" s="103" t="n">
-        <v>0</v>
-      </c>
-      <c r="H29" s="111" t="n">
+      <c r="G29" s="102" t="n">
+        <v>0</v>
+      </c>
+      <c r="H29" s="110" t="n">
         <v>10</v>
       </c>
-      <c r="I29" s="111" t="n">
+      <c r="I29" s="110" t="n">
         <f aca="false">SUMIFS(OPmontant,OPcompte,$B29,OPdevise,$D29,OPcatégorie,"&lt;&gt;"&amp;Spéciale,OPlibellé,$C29,OPdate,"&gt;="&amp;$G29)</f>
         <v>0</v>
       </c>
-      <c r="J29" s="103" t="n">
+      <c r="J29" s="102" t="n">
         <v>46083</v>
       </c>
-      <c r="K29" s="110" t="n">
+      <c r="K29" s="109" t="n">
         <v>12.62</v>
       </c>
     </row>
     <row r="30" customFormat="false" ht="16.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A30" s="101" t="s">
+      <c r="A30" s="100" t="s">
         <v>168</v>
       </c>
       <c r="B30" s="52" t="s">
@@ -7142,30 +7137,30 @@
       <c r="D30" s="52" t="s">
         <v>100</v>
       </c>
-      <c r="E30" s="110" t="n">
+      <c r="E30" s="109" t="n">
         <f aca="false">K30-(H30+I30)</f>
         <v>-30.03</v>
       </c>
       <c r="F30" s="52"/>
-      <c r="G30" s="103" t="n">
+      <c r="G30" s="102" t="n">
         <v>45715</v>
       </c>
-      <c r="H30" s="111" t="n">
-        <v>0</v>
-      </c>
-      <c r="I30" s="111" t="n">
+      <c r="H30" s="110" t="n">
+        <v>0</v>
+      </c>
+      <c r="I30" s="110" t="n">
         <f aca="false">SUMIFS(OPmontant,OPcompte,$B30,OPdevise,$D30,OPcatégorie,"&lt;&gt;"&amp;Spéciale,OPlibellé,$C30,OPdate,"&gt;="&amp;$G30)</f>
         <v>30.03</v>
       </c>
-      <c r="J30" s="103" t="n">
+      <c r="J30" s="102" t="n">
         <v>45924</v>
       </c>
-      <c r="K30" s="110" t="n">
+      <c r="K30" s="109" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="31" customFormat="false" ht="16.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A31" s="101" t="s">
+      <c r="A31" s="100" t="s">
         <v>168</v>
       </c>
       <c r="B31" s="52" t="s">
@@ -7177,30 +7172,30 @@
       <c r="D31" s="52" t="s">
         <v>100</v>
       </c>
-      <c r="E31" s="110" t="n">
+      <c r="E31" s="109" t="n">
         <f aca="false">K31-(H31+I31)</f>
         <v>-413.02</v>
       </c>
       <c r="F31" s="52"/>
-      <c r="G31" s="103" t="n">
+      <c r="G31" s="102" t="n">
         <v>45924</v>
       </c>
-      <c r="H31" s="111" t="n">
-        <v>0</v>
-      </c>
-      <c r="I31" s="111" t="n">
+      <c r="H31" s="110" t="n">
+        <v>0</v>
+      </c>
+      <c r="I31" s="110" t="n">
         <f aca="false">SUMIFS(OPmontant,OPcompte,$B31,OPdevise,$D31,OPcatégorie,"&lt;&gt;"&amp;Spéciale,OPlibellé,$C31,OPdate,"&gt;="&amp;$G31)</f>
         <v>1000</v>
       </c>
-      <c r="J31" s="103" t="n">
+      <c r="J31" s="102" t="n">
         <v>46083</v>
       </c>
-      <c r="K31" s="110" t="n">
+      <c r="K31" s="109" t="n">
         <v>586.98</v>
       </c>
     </row>
     <row r="32" customFormat="false" ht="16.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A32" s="101" t="s">
+      <c r="A32" s="100" t="s">
         <v>168</v>
       </c>
       <c r="B32" s="52" t="s">
@@ -7212,30 +7207,30 @@
       <c r="D32" s="52" t="s">
         <v>100</v>
       </c>
-      <c r="E32" s="110" t="n">
+      <c r="E32" s="109" t="n">
         <f aca="false">K32-(H32+I32)</f>
         <v>115.15</v>
       </c>
       <c r="F32" s="52"/>
-      <c r="G32" s="103" t="n">
+      <c r="G32" s="102" t="n">
         <v>46048</v>
       </c>
-      <c r="H32" s="111" t="n">
-        <v>0</v>
-      </c>
-      <c r="I32" s="111" t="n">
+      <c r="H32" s="110" t="n">
+        <v>0</v>
+      </c>
+      <c r="I32" s="110" t="n">
         <f aca="false">SUMIFS(OPmontant,OPcompte,$B32,OPdevise,$D32,OPcatégorie,"&lt;&gt;"&amp;Spéciale,OPlibellé,$C32,OPdate,"&gt;="&amp;$G32)</f>
         <v>2491.99</v>
       </c>
-      <c r="J32" s="103" t="n">
+      <c r="J32" s="102" t="n">
         <v>46083</v>
       </c>
-      <c r="K32" s="110" t="n">
+      <c r="K32" s="109" t="n">
         <v>2607.14</v>
       </c>
     </row>
     <row r="33" customFormat="false" ht="16.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A33" s="101" t="s">
+      <c r="A33" s="100" t="s">
         <v>168</v>
       </c>
       <c r="B33" s="52" t="s">
@@ -7247,30 +7242,30 @@
       <c r="D33" s="52" t="s">
         <v>100</v>
       </c>
-      <c r="E33" s="110" t="n">
+      <c r="E33" s="109" t="n">
         <f aca="false">K33-(H33+I33)</f>
         <v>-18.01</v>
       </c>
       <c r="F33" s="52"/>
-      <c r="G33" s="103" t="n">
+      <c r="G33" s="102" t="n">
         <v>45783</v>
       </c>
-      <c r="H33" s="111" t="n">
-        <v>0</v>
-      </c>
-      <c r="I33" s="111" t="n">
+      <c r="H33" s="110" t="n">
+        <v>0</v>
+      </c>
+      <c r="I33" s="110" t="n">
         <f aca="false">SUMIFS(OPmontant,OPcompte,$B33,OPdevise,$D33,OPcatégorie,"&lt;&gt;"&amp;Spéciale,OPlibellé,$C33,OPdate,"&gt;="&amp;$G33)</f>
         <v>200</v>
       </c>
-      <c r="J33" s="103" t="n">
+      <c r="J33" s="102" t="n">
         <v>46083</v>
       </c>
-      <c r="K33" s="110" t="n">
+      <c r="K33" s="109" t="n">
         <v>181.99</v>
       </c>
     </row>
     <row r="34" customFormat="false" ht="16.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A34" s="101" t="s">
+      <c r="A34" s="100" t="s">
         <v>168</v>
       </c>
       <c r="B34" s="32" t="s">
@@ -7282,34 +7277,34 @@
       <c r="D34" s="32" t="s">
         <v>100</v>
       </c>
-      <c r="E34" s="112" t="n">
+      <c r="E34" s="111" t="n">
         <f aca="false">K34-(H34+I34)</f>
         <v>-343.29</v>
       </c>
       <c r="F34" s="32"/>
-      <c r="G34" s="106" t="n">
+      <c r="G34" s="105" t="n">
         <f aca="false">MIN(G29:G33)</f>
         <v>0</v>
       </c>
-      <c r="H34" s="113" t="n">
+      <c r="H34" s="112" t="n">
         <f aca="false">SUMPRODUCT(H29:H33*IFERROR(INDEX(COTcours,MATCH(D29:D33,COTcode,0)),1))/IFERROR(INDEX(COTcours,MATCH(D34,COTcode,0)),1)</f>
         <v>10</v>
       </c>
-      <c r="I34" s="113" t="n">
+      <c r="I34" s="112" t="n">
         <f aca="false">SUMPRODUCT(I29:I33*IFERROR(INDEX(COTcours,MATCH(D29:D33,COTcode,0)),1))/IFERROR(INDEX(COTcours,MATCH(D34,COTcode,0)),1)</f>
         <v>3722.02</v>
       </c>
-      <c r="J34" s="106" t="n">
+      <c r="J34" s="105" t="n">
         <f aca="false">J33</f>
         <v>46083</v>
       </c>
-      <c r="K34" s="112" t="n">
+      <c r="K34" s="111" t="n">
         <f aca="false">SUMPRODUCT(K29:K33*IFERROR(INDEX(COTcours,MATCH(D29:D33,COTcode,0)),1))/IFERROR(INDEX(COTcours,MATCH(D34,COTcode,0)),1)</f>
         <v>3388.73</v>
       </c>
     </row>
     <row r="35" customFormat="false" ht="16.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A35" s="101" t="s">
+      <c r="A35" s="100" t="s">
         <v>168</v>
       </c>
       <c r="B35" s="32" t="s">
@@ -7321,34 +7316,34 @@
       <c r="D35" s="32" t="s">
         <v>100</v>
       </c>
-      <c r="E35" s="112" t="n">
+      <c r="E35" s="111" t="n">
         <f aca="false">K35-(H35+I35)</f>
         <v>-3722.02</v>
       </c>
       <c r="F35" s="32"/>
-      <c r="G35" s="106" t="n">
+      <c r="G35" s="105" t="n">
         <f aca="false">_xlfn.MINIFS(OPdate,OPcompte,$B35,OPdevise,D35,OPcatégorie,Solde)</f>
         <v>46050</v>
       </c>
-      <c r="H35" s="113" t="n">
+      <c r="H35" s="112" t="n">
         <f aca="false">SUMIFS(OPmontant,OPcompte,$B35,OPdevise,$D35,OPdate,$G35,OPcatégorie,Solde)</f>
         <v>3549.43</v>
       </c>
-      <c r="I35" s="113" t="n">
+      <c r="I35" s="112" t="n">
         <f aca="false">I34</f>
         <v>3722.02</v>
       </c>
-      <c r="J35" s="106" t="n">
+      <c r="J35" s="105" t="n">
         <f aca="false">_xlfn.MAXIFS(OPdate,OPcompte,$B35,OPdevise,$D35,OPcatégorie,Solde)</f>
         <v>46050</v>
       </c>
-      <c r="K35" s="112" t="n">
+      <c r="K35" s="111" t="n">
         <f aca="false">SUMIFS(OPmontant,OPcompte,$B35,OPdevise,$D35,OPcatégorie,Solde,OPdate,J35)</f>
         <v>3549.43</v>
       </c>
     </row>
     <row r="36" customFormat="false" ht="16.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A36" s="101" t="s">
+      <c r="A36" s="100" t="s">
         <v>168</v>
       </c>
       <c r="B36" s="32" t="s">
@@ -7360,28 +7355,28 @@
       <c r="D36" s="32" t="s">
         <v>100</v>
       </c>
-      <c r="E36" s="112" t="n">
+      <c r="E36" s="111" t="n">
         <f aca="false">K36-(H36+I36)</f>
         <v>-3882.72</v>
       </c>
       <c r="F36" s="32"/>
-      <c r="G36" s="106" t="n">
+      <c r="G36" s="105" t="n">
         <f aca="false">G35</f>
         <v>46050</v>
       </c>
-      <c r="H36" s="113" t="n">
+      <c r="H36" s="112" t="n">
         <f aca="false">H35</f>
         <v>3549.43</v>
       </c>
-      <c r="I36" s="113" t="n">
+      <c r="I36" s="112" t="n">
         <f aca="false">I35</f>
         <v>3722.02</v>
       </c>
-      <c r="J36" s="106" t="n">
+      <c r="J36" s="105" t="n">
         <f aca="false">IF(J34&gt;J35,J34,J35)</f>
         <v>46083</v>
       </c>
-      <c r="K36" s="112" t="n">
+      <c r="K36" s="111" t="n">
         <f aca="false">IF(J34&gt;J35,K34,K35)</f>
         <v>3388.73</v>
       </c>
@@ -7400,7 +7395,7 @@
       <c r="K37" s="52"/>
     </row>
     <row r="38" customFormat="false" ht="16.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A38" s="101" t="s">
+      <c r="A38" s="100" t="s">
         <v>175</v>
       </c>
       <c r="B38" s="52"/>
@@ -7415,7 +7410,7 @@
       <c r="K38" s="52"/>
     </row>
     <row r="39" customFormat="false" ht="16.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A39" s="101" t="s">
+      <c r="A39" s="100" t="s">
         <v>176</v>
       </c>
       <c r="B39" s="52" t="s">
@@ -7425,28 +7420,28 @@
       <c r="D39" s="52" t="s">
         <v>122</v>
       </c>
-      <c r="E39" s="102" t="n">
+      <c r="E39" s="101" t="n">
         <f aca="false">K39-(H39+I39)</f>
         <v>2118.4858754304</v>
       </c>
       <c r="F39" s="52"/>
-      <c r="G39" s="103" t="n">
+      <c r="G39" s="102" t="n">
         <f aca="false">_xlfn.MINIFS(OPdate,OPcompte,B39,OPdevise,D39,OPcatégorie,Solde)</f>
         <v>45457</v>
       </c>
-      <c r="H39" s="104" t="n">
+      <c r="H39" s="103" t="n">
         <f aca="false">SUMIFS(OPequiv_euro,OPcompte,B39,OPdevise,D39,OPcatégorie,Solde,OPdate,G39)</f>
         <v>0</v>
       </c>
-      <c r="I39" s="104" t="n">
+      <c r="I39" s="103" t="n">
         <f aca="false">SUMIFS(OPequiv_euro,OPcompte,B39,OPdevise,D39,OPcatégorie,"&lt;&gt;"&amp;Spéciale,OPdate,"&gt;="&amp;G39)</f>
         <v>0</v>
       </c>
-      <c r="J39" s="103" t="n">
+      <c r="J39" s="102" t="n">
         <f aca="false">SUMIF(AVRintitulé,$B39,AVRdate_solde)</f>
         <v>45457</v>
       </c>
-      <c r="K39" s="102" t="n">
+      <c r="K39" s="101" t="n">
         <f aca="false">SUMIF(AVRintitulé,$B39,AVRmontant_solde_euro)</f>
         <v>2118.4858754304</v>
       </c>
@@ -7465,7 +7460,7 @@
       <c r="K40" s="52"/>
     </row>
     <row r="41" customFormat="false" ht="16.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A41" s="101" t="s">
+      <c r="A41" s="100" t="s">
         <v>177</v>
       </c>
       <c r="B41" s="52"/>
@@ -7480,7 +7475,7 @@
       <c r="K41" s="52"/>
     </row>
     <row r="42" customFormat="false" ht="16.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A42" s="101" t="s">
+      <c r="A42" s="100" t="s">
         <v>178</v>
       </c>
       <c r="B42" s="52" t="s">
@@ -7490,34 +7485,34 @@
       <c r="D42" s="52" t="s">
         <v>116</v>
       </c>
-      <c r="E42" s="102" t="n">
+      <c r="E42" s="101" t="n">
         <f aca="false">K42-(H42+I42)</f>
         <v>100</v>
       </c>
       <c r="F42" s="52"/>
-      <c r="G42" s="103" t="n">
+      <c r="G42" s="102" t="n">
         <f aca="false">_xlfn.MINIFS(OPdate,OPcompte,B42,OPdevise,D42,OPcatégorie,Solde)</f>
         <v>44927</v>
       </c>
-      <c r="H42" s="104" t="n">
+      <c r="H42" s="103" t="n">
         <f aca="false">SUMIFS(OPequiv_euro,OPcompte,B42,OPdevise,D42,OPcatégorie,Solde,OPdate,G42)</f>
         <v>0</v>
       </c>
-      <c r="I42" s="104" t="n">
+      <c r="I42" s="103" t="n">
         <f aca="false">SUMIFS(OPequiv_euro,OPcompte,B42,OPdevise,D42,OPcatégorie,"&lt;&gt;"&amp;Spéciale,OPdate,"&gt;="&amp;G42)</f>
         <v>-100</v>
       </c>
-      <c r="J42" s="103" t="n">
+      <c r="J42" s="102" t="n">
         <f aca="false">SUMIF(AVRintitulé,$B42,AVRdate_solde)</f>
         <v>45292</v>
       </c>
-      <c r="K42" s="102" t="n">
+      <c r="K42" s="101" t="n">
         <f aca="false">SUMIF(AVRintitulé,$B42,AVRmontant_solde_euro)</f>
         <v>0</v>
       </c>
     </row>
     <row r="43" customFormat="false" ht="16.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A43" s="101" t="s">
+      <c r="A43" s="100" t="s">
         <v>178</v>
       </c>
       <c r="B43" s="52" t="s">
@@ -7527,34 +7522,34 @@
       <c r="D43" s="52" t="s">
         <v>116</v>
       </c>
-      <c r="E43" s="102" t="n">
+      <c r="E43" s="101" t="n">
         <f aca="false">K43-(H43+I43)</f>
         <v>170.093092</v>
       </c>
       <c r="F43" s="52"/>
-      <c r="G43" s="103" t="n">
+      <c r="G43" s="102" t="n">
         <f aca="false">_xlfn.MINIFS(OPdate,OPcompte,B43,OPdevise,D43,OPcatégorie,Solde)</f>
         <v>45292</v>
       </c>
-      <c r="H43" s="104" t="n">
+      <c r="H43" s="103" t="n">
         <f aca="false">SUMIFS(OPequiv_euro,OPcompte,B43,OPdevise,D43,OPcatégorie,Solde,OPdate,G43)</f>
         <v>0</v>
       </c>
-      <c r="I43" s="104" t="n">
+      <c r="I43" s="103" t="n">
         <f aca="false">SUMIFS(OPequiv_euro,OPcompte,B43,OPdevise,D43,OPcatégorie,"&lt;&gt;"&amp;Spéciale,OPdate,"&gt;="&amp;G43)</f>
         <v>0</v>
       </c>
-      <c r="J43" s="103" t="n">
+      <c r="J43" s="102" t="n">
         <f aca="false">SUMIF(AVRintitulé,$B43,AVRdate_solde)</f>
         <v>45292</v>
       </c>
-      <c r="K43" s="102" t="n">
+      <c r="K43" s="101" t="n">
         <f aca="false">SUMIF(AVRintitulé,$B43,AVRmontant_solde_euro)</f>
         <v>170.093092</v>
       </c>
     </row>
     <row r="44" customFormat="false" ht="16.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A44" s="101" t="s">
+      <c r="A44" s="100" t="s">
         <v>178</v>
       </c>
       <c r="B44" s="52" t="s">
@@ -7564,34 +7559,34 @@
       <c r="D44" s="52" t="s">
         <v>116</v>
       </c>
-      <c r="E44" s="102" t="n">
+      <c r="E44" s="101" t="n">
         <f aca="false">K44-(H44+I44)</f>
         <v>31.28358493</v>
       </c>
       <c r="F44" s="52"/>
-      <c r="G44" s="103" t="n">
+      <c r="G44" s="102" t="n">
         <f aca="false">_xlfn.MINIFS(OPdate,OPcompte,B44,OPdevise,D44,OPcatégorie,Solde)</f>
         <v>45923</v>
       </c>
-      <c r="H44" s="104" t="n">
+      <c r="H44" s="103" t="n">
         <f aca="false">SUMIFS(OPequiv_euro,OPcompte,B44,OPdevise,D44,OPcatégorie,Solde,OPdate,G44)</f>
         <v>0</v>
       </c>
-      <c r="I44" s="104" t="n">
+      <c r="I44" s="103" t="n">
         <f aca="false">SUMIFS(OPequiv_euro,OPcompte,B44,OPdevise,D44,OPcatégorie,"&lt;&gt;"&amp;Spéciale,OPdate,"&gt;="&amp;G44)</f>
         <v>0</v>
       </c>
-      <c r="J44" s="103" t="n">
+      <c r="J44" s="102" t="n">
         <f aca="false">SUMIF(AVRintitulé,$B44,AVRdate_solde)</f>
         <v>45967</v>
       </c>
-      <c r="K44" s="102" t="n">
+      <c r="K44" s="101" t="n">
         <f aca="false">SUMIF(AVRintitulé,$B44,AVRmontant_solde_euro)</f>
         <v>31.28358493</v>
       </c>
     </row>
     <row r="45" customFormat="false" ht="16.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A45" s="101" t="s">
+      <c r="A45" s="100" t="s">
         <v>178</v>
       </c>
       <c r="B45" s="52" t="s">
@@ -7601,28 +7596,28 @@
       <c r="D45" s="52" t="s">
         <v>120</v>
       </c>
-      <c r="E45" s="102" t="n">
+      <c r="E45" s="101" t="n">
         <f aca="false">K45-(H45+I45)</f>
         <v>0</v>
       </c>
       <c r="F45" s="52"/>
-      <c r="G45" s="103" t="n">
+      <c r="G45" s="102" t="n">
         <f aca="false">_xlfn.MINIFS(OPdate,OPcompte,B45,OPdevise,D45,OPcatégorie,Solde)</f>
         <v>0</v>
       </c>
-      <c r="H45" s="104" t="n">
+      <c r="H45" s="103" t="n">
         <f aca="false">SUMIFS(OPequiv_euro,OPcompte,B45,OPdevise,D45,OPcatégorie,Solde,OPdate,G45)</f>
         <v>0</v>
       </c>
-      <c r="I45" s="104" t="n">
+      <c r="I45" s="103" t="n">
         <f aca="false">SUMIFS(OPequiv_euro,OPcompte,B45,OPdevise,D45,OPcatégorie,"&lt;&gt;"&amp;Spéciale,OPdate,"&gt;="&amp;G45)</f>
         <v>0</v>
       </c>
-      <c r="J45" s="103" t="n">
+      <c r="J45" s="102" t="n">
         <f aca="false">SUMIF(AVRintitulé,$B45,AVRdate_solde)</f>
         <v>0</v>
       </c>
-      <c r="K45" s="102" t="n">
+      <c r="K45" s="101" t="n">
         <f aca="false">SUMIF(AVRintitulé,$B45,AVRmontant_solde_euro)</f>
         <v>0</v>
       </c>
@@ -7641,7 +7636,7 @@
       <c r="K46" s="52"/>
     </row>
     <row r="47" customFormat="false" ht="16.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A47" s="101" t="s">
+      <c r="A47" s="100" t="s">
         <v>179</v>
       </c>
       <c r="B47" s="52"/>
@@ -7656,7 +7651,7 @@
       <c r="K47" s="52"/>
     </row>
     <row r="48" customFormat="false" ht="16.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A48" s="101" t="s">
+      <c r="A48" s="100" t="s">
         <v>180</v>
       </c>
       <c r="B48" s="52" t="s">
@@ -7666,34 +7661,34 @@
       <c r="D48" s="52" t="s">
         <v>100</v>
       </c>
-      <c r="E48" s="102" t="n">
+      <c r="E48" s="101" t="n">
         <f aca="false">K48-(H48+I48)</f>
         <v>0</v>
       </c>
       <c r="F48" s="52"/>
-      <c r="G48" s="103" t="n">
+      <c r="G48" s="102" t="n">
         <f aca="false">_xlfn.MINIFS(OPdate,OPcompte,B48,OPdevise,D48,OPcatégorie,Solde)</f>
         <v>0</v>
       </c>
-      <c r="H48" s="104" t="n">
+      <c r="H48" s="103" t="n">
         <f aca="false">SUMIFS(OPequiv_euro,OPcompte,B48,OPdevise,D48,OPcatégorie,Solde,OPdate,G48)</f>
         <v>0</v>
       </c>
-      <c r="I48" s="104" t="n">
+      <c r="I48" s="103" t="n">
         <f aca="false">SUMIFS(OPequiv_euro,OPcompte,B48,OPdevise,D48,OPcatégorie,"&lt;&gt;"&amp;Spéciale,OPdate,"&gt;="&amp;G48)</f>
         <v>0</v>
       </c>
-      <c r="J48" s="103" t="n">
+      <c r="J48" s="102" t="n">
         <f aca="false">SUMIF(AVRintitulé,$B48,AVRdate_solde)</f>
         <v>0</v>
       </c>
-      <c r="K48" s="102" t="n">
+      <c r="K48" s="101" t="n">
         <f aca="false">SUMIF(AVRintitulé,$B48,AVRmontant_solde_euro)</f>
         <v>0</v>
       </c>
     </row>
     <row r="49" customFormat="false" ht="16.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A49" s="101" t="s">
+      <c r="A49" s="100" t="s">
         <v>180</v>
       </c>
       <c r="B49" s="52" t="s">
@@ -7703,34 +7698,34 @@
       <c r="D49" s="52" t="s">
         <v>112</v>
       </c>
-      <c r="E49" s="102" t="n">
+      <c r="E49" s="101" t="n">
         <f aca="false">K49-(H49+I49)</f>
         <v>0</v>
       </c>
       <c r="F49" s="52"/>
-      <c r="G49" s="103" t="n">
+      <c r="G49" s="102" t="n">
         <f aca="false">_xlfn.MINIFS(OPdate,OPcompte,B49,OPdevise,D49,OPcatégorie,Solde)</f>
         <v>0</v>
       </c>
-      <c r="H49" s="104" t="n">
+      <c r="H49" s="103" t="n">
         <f aca="false">SUMIFS(OPequiv_euro,OPcompte,B49,OPdevise,D49,OPcatégorie,Solde,OPdate,G49)</f>
         <v>0</v>
       </c>
-      <c r="I49" s="104" t="n">
+      <c r="I49" s="103" t="n">
         <f aca="false">SUMIFS(OPequiv_euro,OPcompte,B49,OPdevise,D49,OPcatégorie,"&lt;&gt;"&amp;Spéciale,OPdate,"&gt;="&amp;G49)</f>
         <v>0</v>
       </c>
-      <c r="J49" s="103" t="n">
+      <c r="J49" s="102" t="n">
         <f aca="false">SUMIF(AVRintitulé,$B49,AVRdate_solde)</f>
         <v>0</v>
       </c>
-      <c r="K49" s="102" t="n">
+      <c r="K49" s="101" t="n">
         <f aca="false">SUMIF(AVRintitulé,$B49,AVRmontant_solde_euro)</f>
         <v>0</v>
       </c>
     </row>
     <row r="50" customFormat="false" ht="16.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A50" s="101" t="s">
+      <c r="A50" s="100" t="s">
         <v>180</v>
       </c>
       <c r="B50" s="52" t="s">
@@ -7740,28 +7735,28 @@
       <c r="D50" s="52" t="s">
         <v>100</v>
       </c>
-      <c r="E50" s="102" t="n">
+      <c r="E50" s="101" t="n">
         <f aca="false">K50-(H50+I50)</f>
         <v>2387.873965</v>
       </c>
       <c r="F50" s="52"/>
-      <c r="G50" s="103" t="n">
+      <c r="G50" s="102" t="n">
         <f aca="false">_xlfn.MINIFS(OPdate,OPcompte,B50,OPdevise,D50,OPcatégorie,Solde)</f>
         <v>45621</v>
       </c>
-      <c r="H50" s="104" t="n">
+      <c r="H50" s="103" t="n">
         <f aca="false">SUMIFS(OPequiv_euro,OPcompte,B50,OPdevise,D50,OPcatégorie,Solde,OPdate,G50)</f>
         <v>0</v>
       </c>
-      <c r="I50" s="104" t="n">
+      <c r="I50" s="103" t="n">
         <f aca="false">SUMIFS(OPequiv_euro,OPcompte,B50,OPdevise,D50,OPcatégorie,"&lt;&gt;"&amp;Spéciale,OPdate,"&gt;="&amp;G50)</f>
         <v>-1966.84</v>
       </c>
-      <c r="J50" s="103" t="n">
+      <c r="J50" s="102" t="n">
         <f aca="false">SUMIF(AVRintitulé,$B50,AVRdate_solde)</f>
         <v>46050</v>
       </c>
-      <c r="K50" s="102" t="n">
+      <c r="K50" s="101" t="n">
         <f aca="false">SUMIF(AVRintitulé,$B50,AVRmontant_solde_euro)</f>
         <v>421.033965</v>
       </c>
@@ -7780,19 +7775,19 @@
       <c r="K51" s="52"/>
     </row>
     <row r="52" customFormat="false" ht="16.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A52" s="101" t="s">
+      <c r="A52" s="100" t="s">
         <v>4</v>
       </c>
-      <c r="B52" s="114"/>
-      <c r="C52" s="115"/>
-      <c r="D52" s="116"/>
-      <c r="E52" s="115"/>
-      <c r="F52" s="115"/>
-      <c r="G52" s="117"/>
-      <c r="H52" s="115"/>
-      <c r="I52" s="115"/>
-      <c r="J52" s="115"/>
-      <c r="K52" s="115"/>
+      <c r="B52" s="113"/>
+      <c r="C52" s="114"/>
+      <c r="D52" s="115"/>
+      <c r="E52" s="114"/>
+      <c r="F52" s="114"/>
+      <c r="G52" s="116"/>
+      <c r="H52" s="114"/>
+      <c r="I52" s="114"/>
+      <c r="J52" s="114"/>
+      <c r="K52" s="114"/>
     </row>
     <row r="53" customFormat="false" ht="16.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A53" s="69" t="s">
@@ -7803,28 +7798,28 @@
       <c r="D53" s="71" t="s">
         <v>95</v>
       </c>
-      <c r="E53" s="118" t="n">
+      <c r="E53" s="117" t="n">
         <f aca="false">SUM(E54:E57)</f>
         <v>1455.0077973604</v>
       </c>
-      <c r="F53" s="119" t="n">
+      <c r="F53" s="118" t="n">
         <f aca="false">E53/(H53+I53)</f>
         <v>0.345438765774654</v>
       </c>
-      <c r="G53" s="120" t="n">
+      <c r="G53" s="119" t="n">
         <f aca="false">MIN(G54:G57)</f>
         <v>44927</v>
       </c>
-      <c r="H53" s="121" t="n">
+      <c r="H53" s="120" t="n">
         <f aca="false">SUM(H54:H57)</f>
         <v>3064.932805</v>
       </c>
-      <c r="I53" s="121" t="n">
+      <c r="I53" s="120" t="n">
         <f aca="false">SUM(I54:I57)</f>
         <v>1147.12427</v>
       </c>
-      <c r="J53" s="122"/>
-      <c r="K53" s="118" t="n">
+      <c r="J53" s="121"/>
+      <c r="K53" s="117" t="n">
         <f aca="false">SUM(K54:K57)</f>
         <v>5667.0648723604</v>
       </c>
@@ -7838,31 +7833,31 @@
       <c r="D54" s="22" t="s">
         <v>95</v>
       </c>
-      <c r="E54" s="123" t="n">
+      <c r="E54" s="122" t="n">
         <f aca="false">K54-(H54+I54)</f>
         <v>-3352.72872</v>
       </c>
-      <c r="F54" s="124" t="n">
+      <c r="F54" s="123" t="n">
         <f aca="false">E54/(H54+I54)</f>
         <v>-0.533967778091027</v>
       </c>
-      <c r="G54" s="125" t="n">
+      <c r="G54" s="124" t="n">
         <f aca="false">MIN(_xlfn.MINIFS(G:G,A:A,"portefeuilles",C:C,"Retenu",G:G,"&gt;0"))</f>
         <v>46050</v>
       </c>
-      <c r="H54" s="126" t="n">
+      <c r="H54" s="125" t="n">
         <f aca="false">SUMPRODUCT((PVLsection="portefeuilles")*(PVLtitre="Retenu")*PVLmontant_init*IFERROR(INDEX(COTcours,MATCH(PVLdevise,COTcode,0)),1))</f>
         <v>3064.932805</v>
       </c>
-      <c r="I54" s="126" t="n">
+      <c r="I54" s="125" t="n">
         <f aca="false">SUMPRODUCT((PVLsection="portefeuilles")*(PVLtitre="Retenu")*PVLsigma*IFERROR(INDEX(COTcours,MATCH(PVLdevise,COTcode,0)),1))</f>
         <v>3213.96427</v>
       </c>
-      <c r="J54" s="125" t="n">
+      <c r="J54" s="124" t="n">
         <f aca="false">_xlfn.MAXIFS(J:J,A:A,"portefeuilles",C:C,"Retenu")</f>
         <v>46083</v>
       </c>
-      <c r="K54" s="123" t="n">
+      <c r="K54" s="122" t="n">
         <f aca="false">SUMPRODUCT((PVLsection="portefeuilles")*(PVLtitre="Retenu")*PVLmontant*IFERROR(INDEX(COTcours,MATCH(PVLdevise,COTcode,0)),1))</f>
         <v>2926.168355</v>
       </c>
@@ -7876,31 +7871,31 @@
       <c r="D55" s="22" t="s">
         <v>95</v>
       </c>
-      <c r="E55" s="123" t="n">
+      <c r="E55" s="122" t="n">
         <f aca="false">K55-(H55+I55)</f>
         <v>2118.4858754304</v>
       </c>
-      <c r="F55" s="124" t="e">
+      <c r="F55" s="123" t="e">
         <f aca="false">E55/(H55+I55)</f>
         <v>#DIV/0!</v>
       </c>
-      <c r="G55" s="125" t="n">
+      <c r="G55" s="124" t="n">
         <f aca="false">MIN(_xlfn.MINIFS(G:G,A:A,"métaux",G:G,"&gt;0"))</f>
         <v>45457</v>
       </c>
-      <c r="H55" s="126" t="n">
+      <c r="H55" s="125" t="n">
         <f aca="false">SUMIFS(PVLmontant_init,PVLsection,"métaux")</f>
         <v>0</v>
       </c>
-      <c r="I55" s="126" t="n">
+      <c r="I55" s="125" t="n">
         <f aca="false">SUMIFS(PVLsigma,PVLsection,"métaux")</f>
         <v>0</v>
       </c>
-      <c r="J55" s="125" t="n">
+      <c r="J55" s="124" t="n">
         <f aca="false">_xlfn.MAXIFS(J:J,A:A,"métaux")</f>
         <v>45457</v>
       </c>
-      <c r="K55" s="123" t="n">
+      <c r="K55" s="122" t="n">
         <f aca="false">SUMIFS(PVLmontant,PVLsection,"métaux")</f>
         <v>2118.4858754304</v>
       </c>
@@ -7914,31 +7909,31 @@
       <c r="D56" s="22" t="s">
         <v>95</v>
       </c>
-      <c r="E56" s="123" t="n">
+      <c r="E56" s="122" t="n">
         <f aca="false">K56-(H56+I56)</f>
         <v>301.37667693</v>
       </c>
-      <c r="F56" s="124" t="n">
+      <c r="F56" s="123" t="n">
         <f aca="false">E56/(H56+I56)</f>
         <v>-3.0137667693</v>
       </c>
-      <c r="G56" s="125" t="n">
+      <c r="G56" s="124" t="n">
         <f aca="false">MIN(_xlfn.MINIFS(G:G,A:A,"crypto",G:G,"&gt;0"))</f>
         <v>44927</v>
       </c>
-      <c r="H56" s="126" t="n">
+      <c r="H56" s="125" t="n">
         <f aca="false">SUMIFS(PVLmontant_init,PVLsection,"crypto")</f>
         <v>0</v>
       </c>
-      <c r="I56" s="126" t="n">
+      <c r="I56" s="125" t="n">
         <f aca="false">SUMIFS(PVLsigma,PVLsection,"crypto")</f>
         <v>-100</v>
       </c>
-      <c r="J56" s="125" t="n">
+      <c r="J56" s="124" t="n">
         <f aca="false">_xlfn.MAXIFS(J:J,A:A,"crypto")</f>
         <v>45967</v>
       </c>
-      <c r="K56" s="123" t="n">
+      <c r="K56" s="122" t="n">
         <f aca="false">SUMIFS(PVLmontant,PVLsection,"crypto")</f>
         <v>201.37667693</v>
       </c>
@@ -7952,31 +7947,31 @@
       <c r="D57" s="22" t="s">
         <v>95</v>
       </c>
-      <c r="E57" s="123" t="n">
+      <c r="E57" s="122" t="n">
         <f aca="false">K57-(H57+I57)</f>
         <v>2387.873965</v>
       </c>
-      <c r="F57" s="124" t="n">
+      <c r="F57" s="123" t="n">
         <f aca="false">E57/(H57+I57)</f>
         <v>-1.21406620009762</v>
       </c>
-      <c r="G57" s="125" t="n">
+      <c r="G57" s="124" t="n">
         <f aca="false">MIN(_xlfn.MINIFS(G:G,A:A,"devises",G:G,"&gt;0"))</f>
         <v>45621</v>
       </c>
-      <c r="H57" s="126" t="n">
+      <c r="H57" s="125" t="n">
         <f aca="false">SUMIFS(PVLmontant_init,PVLsection,"devises")</f>
         <v>0</v>
       </c>
-      <c r="I57" s="126" t="n">
+      <c r="I57" s="125" t="n">
         <f aca="false">SUMIFS(PVLsigma,PVLsection,"devises")</f>
         <v>-1966.84</v>
       </c>
-      <c r="J57" s="125" t="n">
+      <c r="J57" s="124" t="n">
         <f aca="false">_xlfn.MAXIFS(J:J,A:A,"devises")</f>
         <v>46050</v>
       </c>
-      <c r="K57" s="123" t="n">
+      <c r="K57" s="122" t="n">
         <f aca="false">SUMIFS(PVLmontant,PVLsection,"devises")</f>
         <v>421.033965</v>
       </c>
@@ -8093,7 +8088,7 @@
   <dimension ref="A1:I1048576"/>
   <sheetFormatPr defaultColWidth="6.00390625" defaultRowHeight="13.5" customHeight="true" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="127" width="12.39"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="126" width="12.39"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="44" width="34.31"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="44" width="17"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="44" width="10.33"/>
@@ -8116,7 +8111,7 @@
       <c r="B1" s="5"/>
       <c r="C1" s="5"/>
       <c r="D1" s="5"/>
-      <c r="E1" s="128"/>
+      <c r="E1" s="127"/>
       <c r="F1" s="10" t="s">
         <v>186</v>
       </c>
@@ -8125,18 +8120,18 @@
       <c r="I1" s="5"/>
     </row>
     <row r="2" customFormat="false" ht="16.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A2" s="129" t="n">
+      <c r="A2" s="128" t="n">
         <f aca="true">TODAY()</f>
-        <v>46222</v>
+        <v>46278</v>
       </c>
       <c r="B2" s="49" t="str">
-        <f aca="false">Contrôles!K$49</f>
+        <f aca="false">Contrôles!K$52</f>
         <v>✓</v>
       </c>
-      <c r="C2" s="130"/>
+      <c r="C2" s="129"/>
       <c r="D2" s="5"/>
-      <c r="E2" s="128"/>
-      <c r="F2" s="131" t="s">
+      <c r="E2" s="127"/>
+      <c r="F2" s="130" t="s">
         <v>187</v>
       </c>
       <c r="G2" s="10" t="str">
@@ -8176,1741 +8171,1741 @@
       </c>
     </row>
     <row r="4" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A4" s="132" t="s">
+      <c r="A4" s="131" t="s">
         <v>4</v>
       </c>
-      <c r="B4" s="133"/>
-      <c r="C4" s="134"/>
-      <c r="D4" s="135"/>
-      <c r="E4" s="134"/>
-      <c r="F4" s="136"/>
-      <c r="G4" s="137"/>
-      <c r="H4" s="137"/>
-      <c r="I4" s="133"/>
+      <c r="B4" s="132"/>
+      <c r="C4" s="133"/>
+      <c r="D4" s="134"/>
+      <c r="E4" s="133"/>
+      <c r="F4" s="135"/>
+      <c r="G4" s="136"/>
+      <c r="H4" s="136"/>
+      <c r="I4" s="132"/>
     </row>
     <row r="5" customFormat="false" ht="16.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A5" s="132" t="n">
+      <c r="A5" s="131" t="n">
         <v>44927</v>
       </c>
-      <c r="B5" s="137" t="s">
+      <c r="B5" s="136" t="s">
         <v>58</v>
       </c>
-      <c r="C5" s="138" t="n">
+      <c r="C5" s="137" t="n">
         <v>503110</v>
       </c>
-      <c r="D5" s="135" t="s">
+      <c r="D5" s="134" t="s">
         <v>116</v>
       </c>
-      <c r="E5" s="134"/>
-      <c r="F5" s="136"/>
-      <c r="G5" s="137" t="s">
+      <c r="E5" s="133"/>
+      <c r="F5" s="135"/>
+      <c r="G5" s="136" t="s">
         <v>193</v>
       </c>
-      <c r="H5" s="137" t="s">
+      <c r="H5" s="136" t="s">
         <v>115</v>
       </c>
-      <c r="I5" s="137" t="s">
+      <c r="I5" s="136" t="s">
         <v>194</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="16.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A6" s="132" t="n">
+      <c r="A6" s="131" t="n">
         <v>44927</v>
       </c>
-      <c r="B6" s="137" t="s">
+      <c r="B6" s="136" t="s">
         <v>58</v>
       </c>
-      <c r="C6" s="134" t="n">
+      <c r="C6" s="133" t="n">
         <v>5000</v>
       </c>
-      <c r="D6" s="135" t="s">
+      <c r="D6" s="134" t="s">
         <v>95</v>
       </c>
-      <c r="E6" s="134"/>
-      <c r="F6" s="136"/>
-      <c r="G6" s="137" t="s">
+      <c r="E6" s="133"/>
+      <c r="F6" s="135"/>
+      <c r="G6" s="136" t="s">
         <v>193</v>
       </c>
-      <c r="H6" s="137" t="s">
+      <c r="H6" s="136" t="s">
         <v>103</v>
       </c>
-      <c r="I6" s="137"/>
+      <c r="I6" s="136"/>
     </row>
     <row r="7" customFormat="false" ht="16.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A7" s="132" t="n">
+      <c r="A7" s="131" t="n">
         <v>44968</v>
       </c>
-      <c r="B7" s="137" t="s">
+      <c r="B7" s="136" t="s">
         <v>195</v>
       </c>
-      <c r="C7" s="138" t="n">
+      <c r="C7" s="137" t="n">
         <v>-280000</v>
       </c>
-      <c r="D7" s="135" t="s">
+      <c r="D7" s="134" t="s">
         <v>116</v>
       </c>
-      <c r="E7" s="134" t="n">
+      <c r="E7" s="133" t="n">
         <v>-50</v>
       </c>
-      <c r="F7" s="136" t="s">
+      <c r="F7" s="135" t="s">
         <v>196</v>
       </c>
-      <c r="G7" s="137" t="s">
+      <c r="G7" s="136" t="s">
         <v>142</v>
       </c>
-      <c r="H7" s="137" t="s">
+      <c r="H7" s="136" t="s">
         <v>115</v>
       </c>
-      <c r="I7" s="137"/>
+      <c r="I7" s="136"/>
     </row>
     <row r="8" customFormat="false" ht="16.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A8" s="132" t="n">
+      <c r="A8" s="131" t="n">
         <v>44968</v>
       </c>
-      <c r="B8" s="137" t="s">
+      <c r="B8" s="136" t="s">
         <v>197</v>
       </c>
-      <c r="C8" s="138" t="n">
+      <c r="C8" s="137" t="n">
         <v>-584</v>
       </c>
-      <c r="D8" s="135" t="s">
+      <c r="D8" s="134" t="s">
         <v>116</v>
       </c>
-      <c r="E8" s="134"/>
-      <c r="F8" s="136"/>
-      <c r="G8" s="137" t="s">
+      <c r="E8" s="133"/>
+      <c r="F8" s="135"/>
+      <c r="G8" s="136" t="s">
         <v>148</v>
       </c>
-      <c r="H8" s="137" t="s">
+      <c r="H8" s="136" t="s">
         <v>115</v>
       </c>
-      <c r="I8" s="137"/>
+      <c r="I8" s="136"/>
     </row>
     <row r="9" customFormat="false" ht="16.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A9" s="132" t="n">
+      <c r="A9" s="131" t="n">
         <v>44983</v>
       </c>
-      <c r="B9" s="137" t="s">
+      <c r="B9" s="136" t="s">
         <v>197</v>
       </c>
-      <c r="C9" s="138" t="n">
+      <c r="C9" s="137" t="n">
         <v>280000</v>
       </c>
-      <c r="D9" s="135" t="s">
+      <c r="D9" s="134" t="s">
         <v>116</v>
       </c>
-      <c r="E9" s="134" t="n">
+      <c r="E9" s="133" t="n">
         <v>50</v>
       </c>
-      <c r="F9" s="136" t="s">
+      <c r="F9" s="135" t="s">
         <v>196</v>
       </c>
-      <c r="G9" s="137" t="s">
+      <c r="G9" s="136" t="s">
         <v>142</v>
       </c>
-      <c r="H9" s="137" t="s">
+      <c r="H9" s="136" t="s">
         <v>117</v>
       </c>
-      <c r="I9" s="137"/>
+      <c r="I9" s="136"/>
     </row>
     <row r="10" customFormat="false" ht="16.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A10" s="132" t="n">
+      <c r="A10" s="131" t="n">
         <v>44983</v>
       </c>
-      <c r="B10" s="137" t="s">
+      <c r="B10" s="136" t="s">
         <v>197</v>
       </c>
-      <c r="C10" s="138" t="n">
+      <c r="C10" s="137" t="n">
         <v>-1200</v>
       </c>
-      <c r="D10" s="135" t="s">
+      <c r="D10" s="134" t="s">
         <v>116</v>
       </c>
-      <c r="E10" s="134"/>
-      <c r="F10" s="136"/>
-      <c r="G10" s="137" t="s">
+      <c r="E10" s="133"/>
+      <c r="F10" s="135"/>
+      <c r="G10" s="136" t="s">
         <v>148</v>
       </c>
-      <c r="H10" s="137" t="s">
+      <c r="H10" s="136" t="s">
         <v>117</v>
       </c>
-      <c r="I10" s="137"/>
+      <c r="I10" s="136"/>
     </row>
     <row r="11" customFormat="false" ht="16.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A11" s="132" t="n">
+      <c r="A11" s="131" t="n">
         <v>45000</v>
       </c>
-      <c r="B11" s="137" t="s">
+      <c r="B11" s="136" t="s">
         <v>198</v>
       </c>
-      <c r="C11" s="138" t="n">
+      <c r="C11" s="137" t="n">
         <v>-218292</v>
       </c>
-      <c r="D11" s="135" t="s">
+      <c r="D11" s="134" t="s">
         <v>116</v>
       </c>
-      <c r="E11" s="134" t="n">
+      <c r="E11" s="133" t="n">
         <v>-50</v>
       </c>
-      <c r="F11" s="136" t="s">
+      <c r="F11" s="135" t="s">
         <v>199</v>
       </c>
-      <c r="G11" s="137" t="s">
+      <c r="G11" s="136" t="s">
         <v>140</v>
       </c>
-      <c r="H11" s="137" t="s">
+      <c r="H11" s="136" t="s">
         <v>115</v>
       </c>
-      <c r="I11" s="137"/>
+      <c r="I11" s="136"/>
     </row>
     <row r="12" customFormat="false" ht="16.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A12" s="132" t="n">
+      <c r="A12" s="131" t="n">
         <v>45000</v>
       </c>
-      <c r="B12" s="137" t="s">
+      <c r="B12" s="136" t="s">
         <v>197</v>
       </c>
-      <c r="C12" s="138" t="n">
+      <c r="C12" s="137" t="n">
         <v>-4234</v>
       </c>
-      <c r="D12" s="135" t="s">
+      <c r="D12" s="134" t="s">
         <v>116</v>
       </c>
-      <c r="E12" s="134"/>
-      <c r="F12" s="136"/>
-      <c r="G12" s="137" t="s">
+      <c r="E12" s="133"/>
+      <c r="F12" s="135"/>
+      <c r="G12" s="136" t="s">
         <v>148</v>
       </c>
-      <c r="H12" s="137" t="s">
+      <c r="H12" s="136" t="s">
         <v>115</v>
       </c>
-      <c r="I12" s="137"/>
+      <c r="I12" s="136"/>
     </row>
     <row r="13" customFormat="false" ht="16.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A13" s="132" t="n">
+      <c r="A13" s="131" t="n">
         <v>45000</v>
       </c>
-      <c r="B13" s="137" t="s">
+      <c r="B13" s="136" t="s">
         <v>197</v>
       </c>
-      <c r="C13" s="134" t="n">
+      <c r="C13" s="133" t="n">
         <v>50</v>
       </c>
-      <c r="D13" s="135" t="s">
+      <c r="D13" s="134" t="s">
         <v>95</v>
       </c>
-      <c r="E13" s="134" t="n">
+      <c r="E13" s="133" t="n">
         <v>50</v>
       </c>
-      <c r="F13" s="136" t="s">
+      <c r="F13" s="135" t="s">
         <v>199</v>
       </c>
-      <c r="G13" s="137" t="s">
+      <c r="G13" s="136" t="s">
         <v>140</v>
       </c>
-      <c r="H13" s="137" t="s">
+      <c r="H13" s="136" t="s">
         <v>101</v>
       </c>
-      <c r="I13" s="137"/>
+      <c r="I13" s="136"/>
     </row>
     <row r="14" customFormat="false" ht="16.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A14" s="132" t="n">
+      <c r="A14" s="131" t="n">
         <v>45048</v>
       </c>
-      <c r="B14" s="137" t="s">
+      <c r="B14" s="136" t="s">
         <v>200</v>
       </c>
-      <c r="C14" s="139" t="n">
+      <c r="C14" s="138" t="n">
         <v>14.09344</v>
       </c>
-      <c r="D14" s="135" t="s">
+      <c r="D14" s="134" t="s">
         <v>122</v>
       </c>
-      <c r="E14" s="134" t="n">
+      <c r="E14" s="133" t="n">
         <v>990</v>
       </c>
-      <c r="F14" s="136" t="s">
+      <c r="F14" s="135" t="s">
         <v>201</v>
       </c>
-      <c r="G14" s="137" t="s">
+      <c r="G14" s="136" t="s">
         <v>140</v>
       </c>
-      <c r="H14" s="137" t="s">
+      <c r="H14" s="136" t="s">
         <v>121</v>
       </c>
-      <c r="I14" s="137"/>
+      <c r="I14" s="136"/>
     </row>
     <row r="15" customFormat="false" ht="16.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A15" s="132" t="n">
+      <c r="A15" s="131" t="n">
         <v>45048</v>
       </c>
-      <c r="B15" s="137" t="s">
+      <c r="B15" s="136" t="s">
         <v>202</v>
       </c>
-      <c r="C15" s="134" t="n">
+      <c r="C15" s="133" t="n">
         <v>-39.6</v>
       </c>
-      <c r="D15" s="135" t="s">
+      <c r="D15" s="134" t="s">
         <v>95</v>
       </c>
-      <c r="E15" s="134"/>
-      <c r="F15" s="136"/>
-      <c r="G15" s="137" t="s">
+      <c r="E15" s="133"/>
+      <c r="F15" s="135"/>
+      <c r="G15" s="136" t="s">
         <v>203</v>
       </c>
-      <c r="H15" s="137" t="s">
+      <c r="H15" s="136" t="s">
         <v>121</v>
       </c>
-      <c r="I15" s="137" t="s">
+      <c r="I15" s="136" t="s">
         <v>204</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="16.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A16" s="132" t="n">
+      <c r="A16" s="131" t="n">
         <v>45048</v>
       </c>
-      <c r="B16" s="137" t="s">
+      <c r="B16" s="136" t="s">
         <v>205</v>
       </c>
-      <c r="C16" s="134" t="n">
+      <c r="C16" s="133" t="n">
         <v>-990</v>
       </c>
-      <c r="D16" s="135" t="s">
+      <c r="D16" s="134" t="s">
         <v>95</v>
       </c>
-      <c r="E16" s="134" t="n">
+      <c r="E16" s="133" t="n">
         <v>-990</v>
       </c>
-      <c r="F16" s="136" t="s">
+      <c r="F16" s="135" t="s">
         <v>201</v>
       </c>
-      <c r="G16" s="137" t="s">
+      <c r="G16" s="136" t="s">
         <v>140</v>
       </c>
-      <c r="H16" s="137" t="s">
+      <c r="H16" s="136" t="s">
         <v>103</v>
       </c>
-      <c r="I16" s="137"/>
+      <c r="I16" s="136"/>
     </row>
     <row r="17" customFormat="false" ht="16.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A17" s="132" t="n">
+      <c r="A17" s="131" t="n">
         <v>45292</v>
       </c>
-      <c r="B17" s="137" t="s">
+      <c r="B17" s="136" t="s">
         <v>58</v>
       </c>
-      <c r="C17" s="138" t="n">
-        <v>0</v>
-      </c>
-      <c r="D17" s="135" t="s">
+      <c r="C17" s="137" t="n">
+        <v>0</v>
+      </c>
+      <c r="D17" s="134" t="s">
         <v>116</v>
       </c>
-      <c r="E17" s="134"/>
-      <c r="F17" s="136"/>
-      <c r="G17" s="137" t="s">
+      <c r="E17" s="133"/>
+      <c r="F17" s="135"/>
+      <c r="G17" s="136" t="s">
         <v>193</v>
       </c>
-      <c r="H17" s="137" t="s">
+      <c r="H17" s="136" t="s">
         <v>115</v>
       </c>
-      <c r="I17" s="137"/>
+      <c r="I17" s="136"/>
     </row>
     <row r="18" customFormat="false" ht="16.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A18" s="132" t="n">
+      <c r="A18" s="131" t="n">
         <v>45292</v>
       </c>
-      <c r="B18" s="137" t="s">
+      <c r="B18" s="136" t="s">
         <v>58</v>
       </c>
-      <c r="C18" s="138" t="n">
+      <c r="C18" s="137" t="n">
         <v>278800</v>
       </c>
-      <c r="D18" s="135" t="s">
+      <c r="D18" s="134" t="s">
         <v>116</v>
       </c>
-      <c r="E18" s="134"/>
-      <c r="F18" s="136"/>
-      <c r="G18" s="137" t="s">
+      <c r="E18" s="133"/>
+      <c r="F18" s="135"/>
+      <c r="G18" s="136" t="s">
         <v>193</v>
       </c>
-      <c r="H18" s="137" t="s">
+      <c r="H18" s="136" t="s">
         <v>117</v>
       </c>
-      <c r="I18" s="137"/>
+      <c r="I18" s="136"/>
     </row>
     <row r="19" customFormat="false" ht="16.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A19" s="132" t="n">
+      <c r="A19" s="131" t="n">
         <v>45457</v>
       </c>
-      <c r="B19" s="137" t="s">
+      <c r="B19" s="136" t="s">
         <v>58</v>
       </c>
-      <c r="C19" s="139" t="n">
+      <c r="C19" s="138" t="n">
         <v>14.09344</v>
       </c>
-      <c r="D19" s="135" t="s">
+      <c r="D19" s="134" t="s">
         <v>122</v>
       </c>
-      <c r="E19" s="134"/>
-      <c r="F19" s="136"/>
-      <c r="G19" s="137" t="s">
+      <c r="E19" s="133"/>
+      <c r="F19" s="135"/>
+      <c r="G19" s="136" t="s">
         <v>193</v>
       </c>
-      <c r="H19" s="137" t="s">
+      <c r="H19" s="136" t="s">
         <v>121</v>
       </c>
-      <c r="I19" s="137"/>
+      <c r="I19" s="136"/>
     </row>
     <row r="20" customFormat="false" ht="16.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A20" s="132" t="n">
+      <c r="A20" s="131" t="n">
         <v>45621</v>
       </c>
-      <c r="B20" s="137" t="s">
+      <c r="B20" s="136" t="s">
         <v>58</v>
       </c>
-      <c r="C20" s="140" t="n">
+      <c r="C20" s="139" t="n">
         <v>2500</v>
       </c>
-      <c r="D20" s="135" t="s">
+      <c r="D20" s="134" t="s">
         <v>100</v>
       </c>
-      <c r="E20" s="134"/>
-      <c r="F20" s="136"/>
-      <c r="G20" s="137" t="s">
+      <c r="E20" s="133"/>
+      <c r="F20" s="135"/>
+      <c r="G20" s="136" t="s">
         <v>193</v>
       </c>
-      <c r="H20" s="137" t="s">
+      <c r="H20" s="136" t="s">
         <v>113</v>
       </c>
-      <c r="I20" s="137"/>
+      <c r="I20" s="136"/>
     </row>
     <row r="21" customFormat="false" ht="16.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A21" s="132" t="n">
+      <c r="A21" s="131" t="n">
         <v>45622</v>
       </c>
-      <c r="B21" s="137" t="s">
+      <c r="B21" s="136" t="s">
         <v>206</v>
       </c>
-      <c r="C21" s="140" t="n">
+      <c r="C21" s="139" t="n">
         <v>10</v>
       </c>
-      <c r="D21" s="135" t="s">
+      <c r="D21" s="134" t="s">
         <v>100</v>
       </c>
-      <c r="E21" s="134" t="n">
+      <c r="E21" s="133" t="n">
         <v>9.6</v>
       </c>
-      <c r="F21" s="136"/>
-      <c r="G21" s="137" t="s">
+      <c r="F21" s="135"/>
+      <c r="G21" s="136" t="s">
         <v>149</v>
       </c>
-      <c r="H21" s="137" t="s">
+      <c r="H21" s="136" t="s">
         <v>99</v>
       </c>
-      <c r="I21" s="137"/>
+      <c r="I21" s="136"/>
     </row>
     <row r="22" customFormat="false" ht="16.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A22" s="132" t="n">
+      <c r="A22" s="131" t="n">
         <v>45657</v>
       </c>
-      <c r="B22" s="137" t="s">
+      <c r="B22" s="136" t="s">
         <v>58</v>
       </c>
-      <c r="C22" s="134" t="n">
+      <c r="C22" s="133" t="n">
         <v>50</v>
       </c>
-      <c r="D22" s="135" t="s">
+      <c r="D22" s="134" t="s">
         <v>95</v>
       </c>
-      <c r="E22" s="134"/>
-      <c r="F22" s="136"/>
-      <c r="G22" s="137" t="s">
+      <c r="E22" s="133"/>
+      <c r="F22" s="135"/>
+      <c r="G22" s="136" t="s">
         <v>193</v>
       </c>
-      <c r="H22" s="137" t="s">
+      <c r="H22" s="136" t="s">
         <v>101</v>
       </c>
-      <c r="I22" s="137"/>
+      <c r="I22" s="136"/>
     </row>
     <row r="23" customFormat="false" ht="16.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A23" s="132" t="n">
+      <c r="A23" s="131" t="n">
         <v>45657</v>
       </c>
-      <c r="B23" s="137" t="s">
+      <c r="B23" s="136" t="s">
         <v>58</v>
       </c>
-      <c r="C23" s="134" t="n">
+      <c r="C23" s="133" t="n">
         <v>10965</v>
       </c>
-      <c r="D23" s="135" t="s">
+      <c r="D23" s="134" t="s">
         <v>95</v>
       </c>
-      <c r="E23" s="134"/>
-      <c r="F23" s="136"/>
-      <c r="G23" s="137" t="s">
+      <c r="E23" s="133"/>
+      <c r="F23" s="135"/>
+      <c r="G23" s="136" t="s">
         <v>193</v>
       </c>
-      <c r="H23" s="137" t="s">
+      <c r="H23" s="136" t="s">
         <v>114</v>
       </c>
-      <c r="I23" s="137"/>
+      <c r="I23" s="136"/>
     </row>
     <row r="24" customFormat="false" ht="16.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A24" s="132" t="n">
+      <c r="A24" s="131" t="n">
         <v>45657</v>
       </c>
-      <c r="B24" s="137" t="s">
+      <c r="B24" s="136" t="s">
         <v>58</v>
       </c>
-      <c r="C24" s="134" t="n">
+      <c r="C24" s="133" t="n">
         <v>2500</v>
       </c>
-      <c r="D24" s="135" t="s">
+      <c r="D24" s="134" t="s">
         <v>95</v>
       </c>
-      <c r="E24" s="134"/>
-      <c r="F24" s="136"/>
-      <c r="G24" s="137" t="s">
+      <c r="E24" s="133"/>
+      <c r="F24" s="135"/>
+      <c r="G24" s="136" t="s">
         <v>193</v>
       </c>
-      <c r="H24" s="137" t="s">
+      <c r="H24" s="136" t="s">
         <v>104</v>
       </c>
-      <c r="I24" s="137"/>
+      <c r="I24" s="136"/>
     </row>
     <row r="25" customFormat="false" ht="16.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A25" s="132" t="n">
+      <c r="A25" s="131" t="n">
         <v>45661</v>
       </c>
-      <c r="B25" s="137" t="s">
+      <c r="B25" s="136" t="s">
         <v>207</v>
       </c>
-      <c r="C25" s="134" t="n">
+      <c r="C25" s="133" t="n">
         <v>-1000</v>
       </c>
-      <c r="D25" s="135" t="s">
+      <c r="D25" s="134" t="s">
         <v>95</v>
       </c>
-      <c r="E25" s="134"/>
-      <c r="F25" s="136"/>
-      <c r="G25" s="137" t="s">
+      <c r="E25" s="133"/>
+      <c r="F25" s="135"/>
+      <c r="G25" s="136" t="s">
         <v>31</v>
       </c>
-      <c r="H25" s="137" t="s">
+      <c r="H25" s="136" t="s">
         <v>104</v>
       </c>
-      <c r="I25" s="137"/>
+      <c r="I25" s="136"/>
     </row>
     <row r="26" customFormat="false" ht="16.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A26" s="132" t="n">
+      <c r="A26" s="131" t="n">
         <v>45663</v>
       </c>
-      <c r="B26" s="137" t="s">
+      <c r="B26" s="136" t="s">
         <v>205</v>
       </c>
-      <c r="C26" s="134" t="n">
+      <c r="C26" s="133" t="n">
         <v>500</v>
       </c>
-      <c r="D26" s="135" t="s">
+      <c r="D26" s="134" t="s">
         <v>95</v>
       </c>
-      <c r="E26" s="134"/>
-      <c r="F26" s="136" t="s">
+      <c r="E26" s="133"/>
+      <c r="F26" s="135" t="s">
         <v>208</v>
       </c>
-      <c r="G26" s="137" t="s">
+      <c r="G26" s="136" t="s">
         <v>142</v>
       </c>
-      <c r="H26" s="137" t="s">
+      <c r="H26" s="136" t="s">
         <v>103</v>
       </c>
-      <c r="I26" s="137"/>
+      <c r="I26" s="136"/>
     </row>
     <row r="27" customFormat="false" ht="16.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A27" s="132" t="n">
+      <c r="A27" s="131" t="n">
         <v>45663</v>
       </c>
-      <c r="B27" s="137"/>
-      <c r="C27" s="134" t="n">
+      <c r="B27" s="136"/>
+      <c r="C27" s="133" t="n">
         <v>-500</v>
       </c>
-      <c r="D27" s="135" t="s">
+      <c r="D27" s="134" t="s">
         <v>95</v>
       </c>
-      <c r="E27" s="134"/>
-      <c r="F27" s="136" t="s">
+      <c r="E27" s="133"/>
+      <c r="F27" s="135" t="s">
         <v>208</v>
       </c>
-      <c r="G27" s="137" t="s">
+      <c r="G27" s="136" t="s">
         <v>142</v>
       </c>
-      <c r="H27" s="137" t="s">
+      <c r="H27" s="136" t="s">
         <v>114</v>
       </c>
-      <c r="I27" s="137"/>
+      <c r="I27" s="136"/>
     </row>
     <row r="28" customFormat="false" ht="16.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A28" s="132" t="n">
+      <c r="A28" s="131" t="n">
         <v>45679</v>
       </c>
-      <c r="B28" s="137" t="s">
+      <c r="B28" s="136" t="s">
         <v>209</v>
       </c>
-      <c r="C28" s="134" t="n">
+      <c r="C28" s="133" t="n">
         <v>-180</v>
       </c>
-      <c r="D28" s="135" t="s">
+      <c r="D28" s="134" t="s">
         <v>95</v>
       </c>
-      <c r="E28" s="134"/>
-      <c r="F28" s="136"/>
-      <c r="G28" s="137" t="s">
+      <c r="E28" s="133"/>
+      <c r="F28" s="135"/>
+      <c r="G28" s="136" t="s">
         <v>31</v>
       </c>
-      <c r="H28" s="137" t="s">
+      <c r="H28" s="136" t="s">
         <v>104</v>
       </c>
-      <c r="I28" s="137"/>
+      <c r="I28" s="136"/>
     </row>
     <row r="29" customFormat="false" ht="16.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A29" s="132" t="n">
+      <c r="A29" s="131" t="n">
         <v>45705</v>
       </c>
-      <c r="B29" s="137" t="s">
+      <c r="B29" s="136" t="s">
         <v>210</v>
       </c>
-      <c r="C29" s="134" t="n">
+      <c r="C29" s="133" t="n">
         <v>-300</v>
       </c>
-      <c r="D29" s="135" t="s">
+      <c r="D29" s="134" t="s">
         <v>95</v>
       </c>
-      <c r="E29" s="134"/>
-      <c r="F29" s="136" t="s">
+      <c r="E29" s="133"/>
+      <c r="F29" s="135" t="s">
         <v>211</v>
       </c>
-      <c r="G29" s="137" t="s">
+      <c r="G29" s="136" t="s">
         <v>142</v>
       </c>
-      <c r="H29" s="137" t="s">
+      <c r="H29" s="136" t="s">
         <v>103</v>
       </c>
-      <c r="I29" s="137"/>
+      <c r="I29" s="136"/>
     </row>
     <row r="30" customFormat="false" ht="16.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A30" s="132" t="n">
+      <c r="A30" s="131" t="n">
         <v>45705</v>
       </c>
-      <c r="B30" s="137" t="s">
+      <c r="B30" s="136" t="s">
         <v>210</v>
       </c>
-      <c r="C30" s="134" t="n">
+      <c r="C30" s="133" t="n">
         <v>300</v>
       </c>
-      <c r="D30" s="135" t="s">
+      <c r="D30" s="134" t="s">
         <v>95</v>
       </c>
-      <c r="E30" s="134"/>
-      <c r="F30" s="136" t="s">
+      <c r="E30" s="133"/>
+      <c r="F30" s="135" t="s">
         <v>211</v>
       </c>
-      <c r="G30" s="137" t="s">
+      <c r="G30" s="136" t="s">
         <v>142</v>
       </c>
-      <c r="H30" s="137" t="s">
+      <c r="H30" s="136" t="s">
         <v>104</v>
       </c>
-      <c r="I30" s="137"/>
+      <c r="I30" s="136"/>
     </row>
     <row r="31" customFormat="false" ht="16.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A31" s="132" t="n">
+      <c r="A31" s="131" t="n">
         <v>45715</v>
       </c>
-      <c r="B31" s="137" t="s">
+      <c r="B31" s="136" t="s">
         <v>205</v>
       </c>
-      <c r="C31" s="134" t="n">
+      <c r="C31" s="133" t="n">
         <v>-500</v>
       </c>
-      <c r="D31" s="135" t="s">
+      <c r="D31" s="134" t="s">
         <v>95</v>
       </c>
-      <c r="E31" s="134" t="n">
+      <c r="E31" s="133" t="n">
         <v>-500</v>
       </c>
-      <c r="F31" s="136" t="s">
+      <c r="F31" s="135" t="s">
         <v>212</v>
       </c>
-      <c r="G31" s="137" t="s">
+      <c r="G31" s="136" t="s">
         <v>140</v>
       </c>
-      <c r="H31" s="137" t="s">
+      <c r="H31" s="136" t="s">
         <v>103</v>
       </c>
-      <c r="I31" s="137"/>
+      <c r="I31" s="136"/>
     </row>
     <row r="32" customFormat="false" ht="16.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A32" s="132" t="n">
+      <c r="A32" s="131" t="n">
         <v>45715</v>
       </c>
-      <c r="B32" s="137" t="s">
+      <c r="B32" s="136" t="s">
         <v>213</v>
       </c>
-      <c r="C32" s="140" t="n">
+      <c r="C32" s="139" t="n">
         <v>520.1</v>
       </c>
-      <c r="D32" s="135" t="s">
+      <c r="D32" s="134" t="s">
         <v>100</v>
       </c>
-      <c r="E32" s="134" t="n">
+      <c r="E32" s="133" t="n">
         <v>500</v>
       </c>
-      <c r="F32" s="136" t="s">
+      <c r="F32" s="135" t="s">
         <v>212</v>
       </c>
-      <c r="G32" s="137" t="s">
+      <c r="G32" s="136" t="s">
         <v>140</v>
       </c>
-      <c r="H32" s="137" t="s">
+      <c r="H32" s="136" t="s">
         <v>113</v>
       </c>
-      <c r="I32" s="137"/>
+      <c r="I32" s="136"/>
     </row>
     <row r="33" customFormat="false" ht="16.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A33" s="132" t="n">
+      <c r="A33" s="131" t="n">
         <v>45715</v>
       </c>
-      <c r="B33" s="137" t="s">
+      <c r="B33" s="136" t="s">
         <v>214</v>
       </c>
-      <c r="C33" s="140" t="n">
+      <c r="C33" s="139" t="n">
         <v>60</v>
       </c>
-      <c r="D33" s="135" t="s">
+      <c r="D33" s="134" t="s">
         <v>100</v>
       </c>
-      <c r="E33" s="134" t="n">
+      <c r="E33" s="133" t="n">
         <v>57.25</v>
       </c>
-      <c r="F33" s="136" t="s">
+      <c r="F33" s="135" t="s">
         <v>215</v>
       </c>
-      <c r="G33" s="137" t="s">
+      <c r="G33" s="136" t="s">
         <v>143</v>
       </c>
-      <c r="H33" s="137" t="s">
+      <c r="H33" s="136" t="s">
         <v>99</v>
       </c>
-      <c r="I33" s="137"/>
+      <c r="I33" s="136"/>
     </row>
     <row r="34" customFormat="false" ht="16.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A34" s="132" t="n">
+      <c r="A34" s="131" t="n">
         <v>45715</v>
       </c>
-      <c r="B34" s="137" t="s">
+      <c r="B34" s="136" t="s">
         <v>214</v>
       </c>
-      <c r="C34" s="140" t="n">
+      <c r="C34" s="139" t="n">
         <v>-60</v>
       </c>
-      <c r="D34" s="135" t="s">
+      <c r="D34" s="134" t="s">
         <v>100</v>
       </c>
-      <c r="E34" s="134" t="n">
+      <c r="E34" s="133" t="n">
         <v>-57.25</v>
       </c>
-      <c r="F34" s="136" t="s">
+      <c r="F34" s="135" t="s">
         <v>215</v>
       </c>
-      <c r="G34" s="137" t="s">
+      <c r="G34" s="136" t="s">
         <v>143</v>
       </c>
-      <c r="H34" s="137" t="s">
+      <c r="H34" s="136" t="s">
         <v>113</v>
       </c>
-      <c r="I34" s="137"/>
+      <c r="I34" s="136"/>
     </row>
     <row r="35" customFormat="false" ht="16.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A35" s="132" t="n">
+      <c r="A35" s="131" t="n">
         <v>45716</v>
       </c>
-      <c r="B35" s="137" t="s">
+      <c r="B35" s="136" t="s">
         <v>216</v>
       </c>
-      <c r="C35" s="140" t="n">
+      <c r="C35" s="139" t="n">
         <v>-29.97</v>
       </c>
-      <c r="D35" s="135" t="s">
+      <c r="D35" s="134" t="s">
         <v>100</v>
       </c>
-      <c r="E35" s="134" t="n">
+      <c r="E35" s="133" t="n">
         <v>-28.85</v>
       </c>
-      <c r="F35" s="136" t="s">
+      <c r="F35" s="135" t="s">
         <v>217</v>
       </c>
-      <c r="G35" s="137" t="s">
+      <c r="G35" s="136" t="s">
         <v>144</v>
       </c>
-      <c r="H35" s="137" t="s">
+      <c r="H35" s="136" t="s">
         <v>99</v>
       </c>
-      <c r="I35" s="137"/>
+      <c r="I35" s="136"/>
     </row>
     <row r="36" customFormat="false" ht="16.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A36" s="132" t="n">
+      <c r="A36" s="131" t="n">
         <v>45716</v>
       </c>
-      <c r="B36" s="137" t="s">
+      <c r="B36" s="136" t="s">
         <v>216</v>
       </c>
-      <c r="C36" s="140" t="n">
+      <c r="C36" s="139" t="n">
         <v>29.97</v>
       </c>
-      <c r="D36" s="135" t="s">
+      <c r="D36" s="134" t="s">
         <v>100</v>
       </c>
-      <c r="E36" s="134" t="n">
+      <c r="E36" s="133" t="n">
         <v>28.85</v>
       </c>
-      <c r="F36" s="136" t="s">
+      <c r="F36" s="135" t="s">
         <v>217</v>
       </c>
-      <c r="G36" s="137" t="s">
+      <c r="G36" s="136" t="s">
         <v>144</v>
       </c>
-      <c r="H36" s="137" t="s">
+      <c r="H36" s="136" t="s">
         <v>113</v>
       </c>
-      <c r="I36" s="137"/>
+      <c r="I36" s="136"/>
     </row>
     <row r="37" customFormat="false" ht="16.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A37" s="132" t="n">
+      <c r="A37" s="131" t="n">
         <v>45716</v>
       </c>
-      <c r="B37" s="137" t="s">
+      <c r="B37" s="136" t="s">
         <v>218</v>
       </c>
-      <c r="C37" s="140" t="n">
+      <c r="C37" s="139" t="n">
         <v>0.15</v>
       </c>
-      <c r="D37" s="135" t="s">
+      <c r="D37" s="134" t="s">
         <v>100</v>
       </c>
-      <c r="E37" s="134"/>
-      <c r="F37" s="136"/>
-      <c r="G37" s="137" t="s">
+      <c r="E37" s="133"/>
+      <c r="F37" s="135"/>
+      <c r="G37" s="136" t="s">
         <v>146</v>
       </c>
-      <c r="H37" s="137" t="s">
+      <c r="H37" s="136" t="s">
         <v>113</v>
       </c>
-      <c r="I37" s="137"/>
+      <c r="I37" s="136"/>
     </row>
     <row r="38" customFormat="false" ht="16.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A38" s="132" t="n">
+      <c r="A38" s="131" t="n">
         <v>45715</v>
       </c>
-      <c r="B38" s="137" t="s">
+      <c r="B38" s="136" t="s">
         <v>219</v>
       </c>
-      <c r="C38" s="140" t="n">
+      <c r="C38" s="139" t="n">
         <v>-0.29</v>
       </c>
-      <c r="D38" s="135" t="s">
+      <c r="D38" s="134" t="s">
         <v>100</v>
       </c>
-      <c r="E38" s="134"/>
-      <c r="F38" s="136"/>
-      <c r="G38" s="137" t="s">
+      <c r="E38" s="133"/>
+      <c r="F38" s="135"/>
+      <c r="G38" s="136" t="s">
         <v>148</v>
       </c>
-      <c r="H38" s="137" t="s">
+      <c r="H38" s="136" t="s">
         <v>113</v>
       </c>
-      <c r="I38" s="137"/>
+      <c r="I38" s="136"/>
     </row>
     <row r="39" customFormat="false" ht="16.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A39" s="132" t="n">
+      <c r="A39" s="131" t="n">
         <v>45763</v>
       </c>
-      <c r="B39" s="137"/>
-      <c r="C39" s="134" t="n">
+      <c r="B39" s="136"/>
+      <c r="C39" s="133" t="n">
         <v>-33</v>
       </c>
-      <c r="D39" s="135" t="s">
+      <c r="D39" s="134" t="s">
         <v>95</v>
       </c>
-      <c r="E39" s="134"/>
-      <c r="F39" s="136"/>
-      <c r="G39" s="137" t="s">
+      <c r="E39" s="133"/>
+      <c r="F39" s="135"/>
+      <c r="G39" s="136" t="s">
         <v>151</v>
       </c>
-      <c r="H39" s="137" t="s">
+      <c r="H39" s="136" t="s">
         <v>104</v>
       </c>
-      <c r="I39" s="137"/>
+      <c r="I39" s="136"/>
     </row>
     <row r="40" customFormat="false" ht="16.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A40" s="132" t="n">
+      <c r="A40" s="131" t="n">
         <v>45783</v>
       </c>
-      <c r="B40" s="137" t="s">
+      <c r="B40" s="136" t="s">
         <v>220</v>
       </c>
-      <c r="C40" s="140" t="n">
+      <c r="C40" s="139" t="n">
         <v>200</v>
       </c>
-      <c r="D40" s="135" t="s">
+      <c r="D40" s="134" t="s">
         <v>100</v>
       </c>
-      <c r="E40" s="134" t="n">
+      <c r="E40" s="133" t="n">
         <v>176</v>
       </c>
-      <c r="F40" s="136"/>
-      <c r="G40" s="137" t="s">
+      <c r="F40" s="135"/>
+      <c r="G40" s="136" t="s">
         <v>143</v>
       </c>
-      <c r="H40" s="137" t="s">
+      <c r="H40" s="136" t="s">
         <v>99</v>
       </c>
-      <c r="I40" s="137"/>
+      <c r="I40" s="136"/>
     </row>
     <row r="41" customFormat="false" ht="16.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A41" s="132" t="n">
+      <c r="A41" s="131" t="n">
         <v>45783</v>
       </c>
-      <c r="B41" s="137" t="s">
+      <c r="B41" s="136" t="s">
         <v>220</v>
       </c>
-      <c r="C41" s="140" t="n">
+      <c r="C41" s="139" t="n">
         <v>-200</v>
       </c>
-      <c r="D41" s="135" t="s">
+      <c r="D41" s="134" t="s">
         <v>100</v>
       </c>
-      <c r="E41" s="134" t="n">
+      <c r="E41" s="133" t="n">
         <v>-176</v>
       </c>
-      <c r="F41" s="136"/>
-      <c r="G41" s="137" t="s">
+      <c r="F41" s="135"/>
+      <c r="G41" s="136" t="s">
         <v>143</v>
       </c>
-      <c r="H41" s="137" t="s">
+      <c r="H41" s="136" t="s">
         <v>113</v>
       </c>
-      <c r="I41" s="137"/>
+      <c r="I41" s="136"/>
     </row>
     <row r="42" customFormat="false" ht="16.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A42" s="132" t="n">
+      <c r="A42" s="131" t="n">
         <v>45809</v>
       </c>
-      <c r="B42" s="137" t="s">
+      <c r="B42" s="136" t="s">
         <v>221</v>
       </c>
-      <c r="C42" s="140" t="n">
+      <c r="C42" s="139" t="n">
         <v>0.17</v>
       </c>
-      <c r="D42" s="135" t="s">
+      <c r="D42" s="134" t="s">
         <v>100</v>
       </c>
-      <c r="E42" s="134"/>
-      <c r="F42" s="136"/>
-      <c r="G42" s="137" t="s">
+      <c r="E42" s="133"/>
+      <c r="F42" s="135"/>
+      <c r="G42" s="136" t="s">
         <v>147</v>
       </c>
-      <c r="H42" s="137" t="s">
+      <c r="H42" s="136" t="s">
         <v>113</v>
       </c>
-      <c r="I42" s="137"/>
+      <c r="I42" s="136"/>
     </row>
     <row r="43" customFormat="false" ht="16.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A43" s="132" t="n">
+      <c r="A43" s="131" t="n">
         <v>45809</v>
       </c>
-      <c r="B43" s="137"/>
-      <c r="C43" s="140" t="n">
+      <c r="B43" s="136"/>
+      <c r="C43" s="139" t="n">
         <v>0.79</v>
       </c>
-      <c r="D43" s="135" t="s">
+      <c r="D43" s="134" t="s">
         <v>100</v>
       </c>
-      <c r="E43" s="134"/>
-      <c r="F43" s="136"/>
-      <c r="G43" s="137" t="s">
+      <c r="E43" s="133"/>
+      <c r="F43" s="135"/>
+      <c r="G43" s="136" t="s">
         <v>146</v>
       </c>
-      <c r="H43" s="137" t="s">
+      <c r="H43" s="136" t="s">
         <v>113</v>
       </c>
-      <c r="I43" s="137"/>
+      <c r="I43" s="136"/>
     </row>
     <row r="44" customFormat="false" ht="16.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A44" s="132" t="n">
+      <c r="A44" s="131" t="n">
         <v>45822</v>
       </c>
-      <c r="B44" s="137"/>
-      <c r="C44" s="134" t="n">
+      <c r="B44" s="136"/>
+      <c r="C44" s="133" t="n">
         <v>-90</v>
       </c>
-      <c r="D44" s="135" t="s">
+      <c r="D44" s="134" t="s">
         <v>95</v>
       </c>
-      <c r="E44" s="134"/>
-      <c r="F44" s="136"/>
-      <c r="G44" s="137" t="s">
+      <c r="E44" s="133"/>
+      <c r="F44" s="135"/>
+      <c r="G44" s="136" t="s">
         <v>130</v>
       </c>
-      <c r="H44" s="137" t="s">
+      <c r="H44" s="136" t="s">
         <v>104</v>
       </c>
-      <c r="I44" s="137"/>
+      <c r="I44" s="136"/>
     </row>
     <row r="45" customFormat="false" ht="16.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A45" s="132" t="n">
+      <c r="A45" s="131" t="n">
         <v>45923</v>
       </c>
-      <c r="B45" s="137" t="s">
+      <c r="B45" s="136" t="s">
         <v>58</v>
       </c>
-      <c r="C45" s="138" t="n">
+      <c r="C45" s="137" t="n">
         <v>51277</v>
       </c>
-      <c r="D45" s="135" t="s">
+      <c r="D45" s="134" t="s">
         <v>116</v>
       </c>
-      <c r="E45" s="134"/>
-      <c r="F45" s="136"/>
-      <c r="G45" s="137" t="s">
+      <c r="E45" s="133"/>
+      <c r="F45" s="135"/>
+      <c r="G45" s="136" t="s">
         <v>193</v>
       </c>
-      <c r="H45" s="137" t="s">
+      <c r="H45" s="136" t="s">
         <v>118</v>
       </c>
-      <c r="I45" s="137"/>
+      <c r="I45" s="136"/>
     </row>
     <row r="46" customFormat="false" ht="16.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A46" s="132" t="n">
+      <c r="A46" s="131" t="n">
         <v>45924</v>
       </c>
-      <c r="B46" s="137" t="s">
+      <c r="B46" s="136" t="s">
         <v>205</v>
       </c>
-      <c r="C46" s="134" t="n">
+      <c r="C46" s="133" t="n">
         <v>-900</v>
       </c>
-      <c r="D46" s="135" t="s">
+      <c r="D46" s="134" t="s">
         <v>95</v>
       </c>
-      <c r="E46" s="134" t="n">
+      <c r="E46" s="133" t="n">
         <v>-900</v>
       </c>
-      <c r="F46" s="136" t="s">
+      <c r="F46" s="135" t="s">
         <v>222</v>
       </c>
-      <c r="G46" s="137" t="s">
+      <c r="G46" s="136" t="s">
         <v>140</v>
       </c>
-      <c r="H46" s="137" t="s">
+      <c r="H46" s="136" t="s">
         <v>103</v>
       </c>
-      <c r="I46" s="137"/>
+      <c r="I46" s="136"/>
     </row>
     <row r="47" customFormat="false" ht="16.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A47" s="132" t="n">
+      <c r="A47" s="131" t="n">
         <v>45924</v>
       </c>
-      <c r="B47" s="137" t="s">
+      <c r="B47" s="136" t="s">
         <v>223</v>
       </c>
-      <c r="C47" s="140" t="n">
+      <c r="C47" s="139" t="n">
         <v>1050.06</v>
       </c>
-      <c r="D47" s="135" t="s">
+      <c r="D47" s="134" t="s">
         <v>100</v>
       </c>
-      <c r="E47" s="134" t="n">
+      <c r="E47" s="133" t="n">
         <v>900</v>
       </c>
-      <c r="F47" s="136" t="s">
+      <c r="F47" s="135" t="s">
         <v>222</v>
       </c>
-      <c r="G47" s="137" t="s">
+      <c r="G47" s="136" t="s">
         <v>140</v>
       </c>
-      <c r="H47" s="137" t="s">
+      <c r="H47" s="136" t="s">
         <v>113</v>
       </c>
-      <c r="I47" s="137"/>
+      <c r="I47" s="136"/>
     </row>
     <row r="48" customFormat="false" ht="16.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A48" s="132" t="n">
+      <c r="A48" s="131" t="n">
         <v>45924</v>
       </c>
-      <c r="B48" s="137" t="s">
+      <c r="B48" s="136" t="s">
         <v>224</v>
       </c>
-      <c r="C48" s="140" t="n">
+      <c r="C48" s="139" t="n">
         <v>-0.76</v>
       </c>
-      <c r="D48" s="135" t="s">
+      <c r="D48" s="134" t="s">
         <v>100</v>
       </c>
-      <c r="E48" s="134"/>
-      <c r="F48" s="136" t="s">
+      <c r="E48" s="133"/>
+      <c r="F48" s="135" t="s">
         <v>222</v>
       </c>
-      <c r="G48" s="137" t="s">
+      <c r="G48" s="136" t="s">
         <v>146</v>
       </c>
-      <c r="H48" s="137" t="s">
+      <c r="H48" s="136" t="s">
         <v>113</v>
       </c>
-      <c r="I48" s="137"/>
+      <c r="I48" s="136"/>
     </row>
     <row r="49" customFormat="false" ht="16.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A49" s="132" t="n">
+      <c r="A49" s="131" t="n">
         <v>45924</v>
       </c>
-      <c r="B49" s="137" t="s">
+      <c r="B49" s="136" t="s">
         <v>225</v>
       </c>
-      <c r="C49" s="140" t="n">
+      <c r="C49" s="139" t="n">
         <v>-1000</v>
       </c>
-      <c r="D49" s="135" t="s">
+      <c r="D49" s="134" t="s">
         <v>100</v>
       </c>
-      <c r="E49" s="134" t="n">
+      <c r="E49" s="133" t="n">
         <v>-1175.09</v>
       </c>
-      <c r="F49" s="136" t="s">
+      <c r="F49" s="135" t="s">
         <v>226</v>
       </c>
-      <c r="G49" s="137" t="s">
+      <c r="G49" s="136" t="s">
         <v>143</v>
       </c>
-      <c r="H49" s="137" t="s">
+      <c r="H49" s="136" t="s">
         <v>113</v>
       </c>
-      <c r="I49" s="137"/>
+      <c r="I49" s="136"/>
     </row>
     <row r="50" customFormat="false" ht="16.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A50" s="132" t="n">
+      <c r="A50" s="131" t="n">
         <v>45924</v>
       </c>
-      <c r="B50" s="137" t="s">
+      <c r="B50" s="136" t="s">
         <v>227</v>
       </c>
-      <c r="C50" s="140" t="n">
+      <c r="C50" s="139" t="n">
         <v>-10</v>
       </c>
-      <c r="D50" s="135" t="s">
+      <c r="D50" s="134" t="s">
         <v>100</v>
       </c>
-      <c r="E50" s="134"/>
-      <c r="F50" s="136" t="s">
+      <c r="E50" s="133"/>
+      <c r="F50" s="135" t="s">
         <v>226</v>
       </c>
-      <c r="G50" s="137" t="s">
+      <c r="G50" s="136" t="s">
         <v>148</v>
       </c>
-      <c r="H50" s="137" t="s">
+      <c r="H50" s="136" t="s">
         <v>113</v>
       </c>
-      <c r="I50" s="137"/>
+      <c r="I50" s="136"/>
     </row>
     <row r="51" customFormat="false" ht="16.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A51" s="132" t="n">
+      <c r="A51" s="131" t="n">
         <v>45924</v>
       </c>
-      <c r="B51" s="137" t="s">
+      <c r="B51" s="136" t="s">
         <v>225</v>
       </c>
-      <c r="C51" s="140" t="n">
+      <c r="C51" s="139" t="n">
         <v>1000</v>
       </c>
-      <c r="D51" s="135" t="s">
+      <c r="D51" s="134" t="s">
         <v>100</v>
       </c>
-      <c r="E51" s="134" t="n">
+      <c r="E51" s="133" t="n">
         <v>1175.09</v>
       </c>
-      <c r="F51" s="136" t="s">
+      <c r="F51" s="135" t="s">
         <v>226</v>
       </c>
-      <c r="G51" s="137" t="s">
+      <c r="G51" s="136" t="s">
         <v>143</v>
       </c>
-      <c r="H51" s="137" t="s">
+      <c r="H51" s="136" t="s">
         <v>99</v>
       </c>
-      <c r="I51" s="137"/>
+      <c r="I51" s="136"/>
     </row>
     <row r="52" customFormat="false" ht="16.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A52" s="132" t="n">
+      <c r="A52" s="131" t="n">
         <v>45933</v>
       </c>
-      <c r="B52" s="137" t="s">
+      <c r="B52" s="136" t="s">
         <v>228</v>
       </c>
-      <c r="C52" s="134" t="n">
+      <c r="C52" s="133" t="n">
         <v>-120</v>
       </c>
-      <c r="D52" s="135" t="s">
+      <c r="D52" s="134" t="s">
         <v>95</v>
       </c>
-      <c r="E52" s="134"/>
-      <c r="F52" s="136"/>
-      <c r="G52" s="137" t="s">
+      <c r="E52" s="133"/>
+      <c r="F52" s="135"/>
+      <c r="G52" s="136" t="s">
         <v>150</v>
       </c>
-      <c r="H52" s="137" t="s">
+      <c r="H52" s="136" t="s">
         <v>104</v>
       </c>
-      <c r="I52" s="137"/>
+      <c r="I52" s="136"/>
     </row>
     <row r="53" customFormat="false" ht="16.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A53" s="132" t="n">
+      <c r="A53" s="131" t="n">
         <v>45939</v>
       </c>
-      <c r="B53" s="137" t="s">
+      <c r="B53" s="136" t="s">
         <v>229</v>
       </c>
-      <c r="C53" s="134" t="n">
+      <c r="C53" s="133" t="n">
         <v>-970</v>
       </c>
-      <c r="D53" s="135" t="s">
+      <c r="D53" s="134" t="s">
         <v>95</v>
       </c>
-      <c r="E53" s="134"/>
-      <c r="F53" s="136"/>
-      <c r="G53" s="137" t="s">
+      <c r="E53" s="133"/>
+      <c r="F53" s="135"/>
+      <c r="G53" s="136" t="s">
         <v>31</v>
       </c>
-      <c r="H53" s="137" t="s">
+      <c r="H53" s="136" t="s">
         <v>104</v>
       </c>
-      <c r="I53" s="137"/>
+      <c r="I53" s="136"/>
     </row>
     <row r="54" customFormat="false" ht="16.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A54" s="132" t="n">
+      <c r="A54" s="131" t="n">
         <v>45940</v>
       </c>
-      <c r="B54" s="137" t="s">
+      <c r="B54" s="136" t="s">
         <v>205</v>
       </c>
-      <c r="C54" s="134" t="n">
+      <c r="C54" s="133" t="n">
         <v>500</v>
       </c>
-      <c r="D54" s="135" t="s">
+      <c r="D54" s="134" t="s">
         <v>95</v>
       </c>
-      <c r="E54" s="134"/>
-      <c r="F54" s="136" t="s">
+      <c r="E54" s="133"/>
+      <c r="F54" s="135" t="s">
         <v>230</v>
       </c>
-      <c r="G54" s="137" t="s">
+      <c r="G54" s="136" t="s">
         <v>142</v>
       </c>
-      <c r="H54" s="137" t="s">
+      <c r="H54" s="136" t="s">
         <v>103</v>
       </c>
-      <c r="I54" s="137"/>
+      <c r="I54" s="136"/>
     </row>
     <row r="55" customFormat="false" ht="16.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A55" s="132" t="n">
+      <c r="A55" s="131" t="n">
         <v>45940</v>
       </c>
-      <c r="B55" s="137" t="s">
+      <c r="B55" s="136" t="s">
         <v>231</v>
       </c>
-      <c r="C55" s="134" t="n">
+      <c r="C55" s="133" t="n">
         <v>-500</v>
       </c>
-      <c r="D55" s="135" t="s">
+      <c r="D55" s="134" t="s">
         <v>95</v>
       </c>
-      <c r="E55" s="134"/>
-      <c r="F55" s="136" t="s">
+      <c r="E55" s="133"/>
+      <c r="F55" s="135" t="s">
         <v>230</v>
       </c>
-      <c r="G55" s="137" t="s">
+      <c r="G55" s="136" t="s">
         <v>142</v>
       </c>
-      <c r="H55" s="137" t="s">
+      <c r="H55" s="136" t="s">
         <v>114</v>
       </c>
-      <c r="I55" s="137"/>
+      <c r="I55" s="136"/>
     </row>
     <row r="56" customFormat="false" ht="16.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A56" s="132" t="n">
+      <c r="A56" s="131" t="n">
         <v>45945</v>
       </c>
-      <c r="B56" s="137" t="s">
+      <c r="B56" s="136" t="s">
         <v>205</v>
       </c>
-      <c r="C56" s="134" t="n">
+      <c r="C56" s="133" t="n">
         <v>-300</v>
       </c>
-      <c r="D56" s="135" t="s">
+      <c r="D56" s="134" t="s">
         <v>95</v>
       </c>
-      <c r="E56" s="134"/>
-      <c r="F56" s="136" t="s">
+      <c r="E56" s="133"/>
+      <c r="F56" s="135" t="s">
         <v>232</v>
       </c>
-      <c r="G56" s="137" t="s">
+      <c r="G56" s="136" t="s">
         <v>142</v>
       </c>
-      <c r="H56" s="137" t="s">
+      <c r="H56" s="136" t="s">
         <v>103</v>
       </c>
-      <c r="I56" s="137"/>
+      <c r="I56" s="136"/>
     </row>
     <row r="57" customFormat="false" ht="16.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A57" s="132" t="n">
+      <c r="A57" s="131" t="n">
         <v>45945</v>
       </c>
-      <c r="B57" s="137" t="s">
+      <c r="B57" s="136" t="s">
         <v>210</v>
       </c>
-      <c r="C57" s="134" t="n">
+      <c r="C57" s="133" t="n">
         <v>300</v>
       </c>
-      <c r="D57" s="135" t="s">
+      <c r="D57" s="134" t="s">
         <v>95</v>
       </c>
-      <c r="E57" s="134"/>
-      <c r="F57" s="136" t="s">
+      <c r="E57" s="133"/>
+      <c r="F57" s="135" t="s">
         <v>232</v>
       </c>
-      <c r="G57" s="137" t="s">
+      <c r="G57" s="136" t="s">
         <v>142</v>
       </c>
-      <c r="H57" s="137" t="s">
+      <c r="H57" s="136" t="s">
         <v>104</v>
       </c>
-      <c r="I57" s="137"/>
+      <c r="I57" s="136"/>
     </row>
     <row r="58" customFormat="false" ht="16.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A58" s="132" t="n">
+      <c r="A58" s="131" t="n">
         <v>45951</v>
       </c>
-      <c r="B58" s="137" t="s">
+      <c r="B58" s="136" t="s">
         <v>207</v>
       </c>
-      <c r="C58" s="134" t="n">
+      <c r="C58" s="133" t="n">
         <v>-700</v>
       </c>
-      <c r="D58" s="135" t="s">
+      <c r="D58" s="134" t="s">
         <v>95</v>
       </c>
-      <c r="E58" s="134"/>
-      <c r="F58" s="136"/>
-      <c r="G58" s="137" t="s">
+      <c r="E58" s="133"/>
+      <c r="F58" s="135"/>
+      <c r="G58" s="136" t="s">
         <v>31</v>
       </c>
-      <c r="H58" s="137" t="s">
+      <c r="H58" s="136" t="s">
         <v>104</v>
       </c>
-      <c r="I58" s="137"/>
+      <c r="I58" s="136"/>
     </row>
     <row r="59" customFormat="false" ht="16.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A59" s="132" t="n">
+      <c r="A59" s="131" t="n">
         <v>45967</v>
       </c>
-      <c r="B59" s="137" t="s">
+      <c r="B59" s="136" t="s">
         <v>58</v>
       </c>
-      <c r="C59" s="138" t="n">
+      <c r="C59" s="137" t="n">
         <v>51277</v>
       </c>
-      <c r="D59" s="135" t="s">
+      <c r="D59" s="134" t="s">
         <v>116</v>
       </c>
-      <c r="E59" s="134"/>
-      <c r="F59" s="136"/>
-      <c r="G59" s="137" t="s">
+      <c r="E59" s="133"/>
+      <c r="F59" s="135"/>
+      <c r="G59" s="136" t="s">
         <v>193</v>
       </c>
-      <c r="H59" s="137" t="s">
+      <c r="H59" s="136" t="s">
         <v>118</v>
       </c>
-      <c r="I59" s="137"/>
+      <c r="I59" s="136"/>
     </row>
     <row r="60" customFormat="false" ht="16.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A60" s="132" t="n">
+      <c r="A60" s="131" t="n">
         <v>46014</v>
       </c>
-      <c r="B60" s="137" t="s">
+      <c r="B60" s="136" t="s">
         <v>205</v>
       </c>
-      <c r="C60" s="134" t="n">
+      <c r="C60" s="133" t="n">
         <v>-118.08</v>
       </c>
-      <c r="D60" s="135" t="s">
+      <c r="D60" s="134" t="s">
         <v>95</v>
       </c>
-      <c r="E60" s="134" t="n">
+      <c r="E60" s="133" t="n">
         <v>-118.08</v>
       </c>
-      <c r="F60" s="136" t="s">
+      <c r="F60" s="135" t="s">
         <v>233</v>
       </c>
-      <c r="G60" s="137" t="s">
+      <c r="G60" s="136" t="s">
         <v>140</v>
       </c>
-      <c r="H60" s="137" t="s">
+      <c r="H60" s="136" t="s">
         <v>103</v>
       </c>
-      <c r="I60" s="137"/>
+      <c r="I60" s="136"/>
     </row>
     <row r="61" customFormat="false" ht="16.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A61" s="132" t="n">
+      <c r="A61" s="131" t="n">
         <v>46014</v>
       </c>
-      <c r="B61" s="137" t="s">
+      <c r="B61" s="136" t="s">
         <v>234</v>
       </c>
-      <c r="C61" s="140" t="n">
+      <c r="C61" s="139" t="n">
         <v>10.44</v>
       </c>
-      <c r="D61" s="135" t="s">
+      <c r="D61" s="134" t="s">
         <v>100</v>
       </c>
-      <c r="E61" s="134"/>
-      <c r="F61" s="136"/>
-      <c r="G61" s="137" t="s">
+      <c r="E61" s="133"/>
+      <c r="F61" s="135"/>
+      <c r="G61" s="136" t="s">
         <v>147</v>
       </c>
-      <c r="H61" s="137" t="s">
+      <c r="H61" s="136" t="s">
         <v>113</v>
       </c>
-      <c r="I61" s="137"/>
+      <c r="I61" s="136"/>
     </row>
     <row r="62" customFormat="false" ht="16.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A62" s="132" t="n">
+      <c r="A62" s="131" t="n">
         <v>46048</v>
       </c>
-      <c r="B62" s="137" t="s">
+      <c r="B62" s="136" t="s">
         <v>235</v>
       </c>
-      <c r="C62" s="140" t="n">
+      <c r="C62" s="139" t="n">
         <v>138.95</v>
       </c>
-      <c r="D62" s="135" t="s">
+      <c r="D62" s="134" t="s">
         <v>100</v>
       </c>
-      <c r="E62" s="134" t="n">
+      <c r="E62" s="133" t="n">
         <v>118.08</v>
       </c>
-      <c r="F62" s="136" t="s">
+      <c r="F62" s="135" t="s">
         <v>233</v>
       </c>
-      <c r="G62" s="137" t="s">
+      <c r="G62" s="136" t="s">
         <v>140</v>
       </c>
-      <c r="H62" s="137" t="s">
+      <c r="H62" s="136" t="s">
         <v>113</v>
       </c>
-      <c r="I62" s="137"/>
+      <c r="I62" s="136"/>
     </row>
     <row r="63" customFormat="false" ht="16.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A63" s="132" t="n">
+      <c r="A63" s="131" t="n">
         <v>46048</v>
       </c>
-      <c r="B63" s="137" t="s">
+      <c r="B63" s="136" t="s">
         <v>236</v>
       </c>
-      <c r="C63" s="140" t="n">
+      <c r="C63" s="139" t="n">
         <v>-138.93</v>
       </c>
-      <c r="D63" s="135" t="s">
+      <c r="D63" s="134" t="s">
         <v>100</v>
       </c>
-      <c r="E63" s="134" t="n">
+      <c r="E63" s="133" t="n">
         <v>-117.38</v>
       </c>
-      <c r="F63" s="136" t="s">
+      <c r="F63" s="135" t="s">
         <v>237</v>
       </c>
-      <c r="G63" s="137" t="s">
+      <c r="G63" s="136" t="s">
         <v>143</v>
       </c>
-      <c r="H63" s="137" t="s">
+      <c r="H63" s="136" t="s">
         <v>113</v>
       </c>
-      <c r="I63" s="137"/>
+      <c r="I63" s="136"/>
     </row>
     <row r="64" customFormat="false" ht="16.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A64" s="132" t="n">
+      <c r="A64" s="131" t="n">
         <v>46048</v>
       </c>
-      <c r="B64" s="137" t="s">
+      <c r="B64" s="136" t="s">
         <v>236</v>
       </c>
-      <c r="C64" s="140" t="n">
+      <c r="C64" s="139" t="n">
         <v>138.93</v>
       </c>
-      <c r="D64" s="135" t="s">
+      <c r="D64" s="134" t="s">
         <v>100</v>
       </c>
-      <c r="E64" s="134" t="n">
+      <c r="E64" s="133" t="n">
         <v>117.38</v>
       </c>
-      <c r="F64" s="136" t="s">
+      <c r="F64" s="135" t="s">
         <v>237</v>
       </c>
-      <c r="G64" s="137" t="s">
+      <c r="G64" s="136" t="s">
         <v>143</v>
       </c>
-      <c r="H64" s="137" t="s">
+      <c r="H64" s="136" t="s">
         <v>99</v>
       </c>
-      <c r="I64" s="137"/>
+      <c r="I64" s="136"/>
     </row>
     <row r="65" customFormat="false" ht="16.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A65" s="132" t="n">
+      <c r="A65" s="131" t="n">
         <v>46048</v>
       </c>
-      <c r="B65" s="137" t="s">
+      <c r="B65" s="136" t="s">
         <v>236</v>
       </c>
-      <c r="C65" s="140" t="n">
+      <c r="C65" s="139" t="n">
         <v>-2353.06</v>
       </c>
-      <c r="D65" s="135" t="s">
+      <c r="D65" s="134" t="s">
         <v>100</v>
       </c>
-      <c r="E65" s="134" t="n">
+      <c r="E65" s="133" t="n">
         <v>-1988.05</v>
       </c>
-      <c r="F65" s="136" t="s">
+      <c r="F65" s="135" t="s">
         <v>238</v>
       </c>
-      <c r="G65" s="137" t="s">
+      <c r="G65" s="136" t="s">
         <v>143</v>
       </c>
-      <c r="H65" s="137" t="s">
+      <c r="H65" s="136" t="s">
         <v>113</v>
       </c>
-      <c r="I65" s="137"/>
+      <c r="I65" s="136"/>
     </row>
     <row r="66" customFormat="false" ht="16.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A66" s="132" t="n">
+      <c r="A66" s="131" t="n">
         <v>46048</v>
       </c>
-      <c r="B66" s="137" t="s">
+      <c r="B66" s="136" t="s">
         <v>236</v>
       </c>
-      <c r="C66" s="140" t="n">
+      <c r="C66" s="139" t="n">
         <v>2353.06</v>
       </c>
-      <c r="D66" s="135" t="s">
+      <c r="D66" s="134" t="s">
         <v>100</v>
       </c>
-      <c r="E66" s="134" t="n">
+      <c r="E66" s="133" t="n">
         <v>1988.05</v>
       </c>
-      <c r="F66" s="136" t="s">
+      <c r="F66" s="135" t="s">
         <v>238</v>
       </c>
-      <c r="G66" s="137" t="s">
+      <c r="G66" s="136" t="s">
         <v>143</v>
       </c>
-      <c r="H66" s="137" t="s">
+      <c r="H66" s="136" t="s">
         <v>99</v>
       </c>
-      <c r="I66" s="137"/>
+      <c r="I66" s="136"/>
     </row>
     <row r="67" customFormat="false" ht="16.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A67" s="132" t="n">
+      <c r="A67" s="131" t="n">
         <v>46050</v>
       </c>
-      <c r="B67" s="137" t="s">
+      <c r="B67" s="136" t="s">
         <v>58</v>
       </c>
-      <c r="C67" s="140" t="n">
+      <c r="C67" s="139" t="n">
         <v>487.59</v>
       </c>
-      <c r="D67" s="135" t="s">
+      <c r="D67" s="134" t="s">
         <v>100</v>
       </c>
-      <c r="E67" s="134"/>
-      <c r="F67" s="136"/>
-      <c r="G67" s="137" t="s">
+      <c r="E67" s="133"/>
+      <c r="F67" s="135"/>
+      <c r="G67" s="136" t="s">
         <v>193</v>
       </c>
-      <c r="H67" s="137" t="s">
+      <c r="H67" s="136" t="s">
         <v>113</v>
       </c>
-      <c r="I67" s="137"/>
+      <c r="I67" s="136"/>
     </row>
     <row r="68" customFormat="false" ht="16.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A68" s="132" t="n">
+      <c r="A68" s="131" t="n">
         <v>46050</v>
       </c>
-      <c r="B68" s="137" t="s">
+      <c r="B68" s="136" t="s">
         <v>58</v>
       </c>
-      <c r="C68" s="140" t="n">
+      <c r="C68" s="139" t="n">
         <v>3549.43</v>
       </c>
-      <c r="D68" s="135" t="s">
+      <c r="D68" s="134" t="s">
         <v>100</v>
       </c>
-      <c r="E68" s="134"/>
-      <c r="F68" s="136"/>
-      <c r="G68" s="137" t="s">
+      <c r="E68" s="133"/>
+      <c r="F68" s="135"/>
+      <c r="G68" s="136" t="s">
         <v>193</v>
       </c>
-      <c r="H68" s="137" t="s">
+      <c r="H68" s="136" t="s">
         <v>99</v>
       </c>
-      <c r="I68" s="137"/>
+      <c r="I68" s="136"/>
     </row>
     <row r="69" customFormat="false" ht="16.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A69" s="132" t="n">
+      <c r="A69" s="131" t="n">
         <v>46058</v>
       </c>
-      <c r="B69" s="137" t="s">
+      <c r="B69" s="136" t="s">
         <v>58</v>
       </c>
-      <c r="C69" s="134" t="n">
+      <c r="C69" s="133" t="n">
         <v>9965</v>
       </c>
-      <c r="D69" s="135" t="s">
+      <c r="D69" s="134" t="s">
         <v>95</v>
       </c>
-      <c r="E69" s="134"/>
-      <c r="F69" s="136"/>
-      <c r="G69" s="137" t="s">
+      <c r="E69" s="133"/>
+      <c r="F69" s="135"/>
+      <c r="G69" s="136" t="s">
         <v>193</v>
       </c>
-      <c r="H69" s="137" t="s">
+      <c r="H69" s="136" t="s">
         <v>114</v>
       </c>
-      <c r="I69" s="137"/>
+      <c r="I69" s="136"/>
     </row>
     <row r="70" customFormat="false" ht="16.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A70" s="132" t="n">
+      <c r="A70" s="131" t="n">
         <v>46084</v>
       </c>
-      <c r="B70" s="137" t="s">
+      <c r="B70" s="136" t="s">
         <v>58</v>
       </c>
-      <c r="C70" s="134" t="n">
+      <c r="C70" s="133" t="n">
         <v>7</v>
       </c>
-      <c r="D70" s="135" t="s">
+      <c r="D70" s="134" t="s">
         <v>95</v>
       </c>
-      <c r="E70" s="134"/>
-      <c r="F70" s="136"/>
-      <c r="G70" s="137" t="s">
+      <c r="E70" s="133"/>
+      <c r="F70" s="135"/>
+      <c r="G70" s="136" t="s">
         <v>193</v>
       </c>
-      <c r="H70" s="137" t="s">
+      <c r="H70" s="136" t="s">
         <v>104</v>
       </c>
-      <c r="I70" s="137"/>
+      <c r="I70" s="136"/>
     </row>
     <row r="71" customFormat="false" ht="16.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A71" s="132" t="n">
+      <c r="A71" s="131" t="n">
         <v>46091</v>
       </c>
-      <c r="B71" s="137" t="s">
+      <c r="B71" s="136" t="s">
         <v>205</v>
       </c>
-      <c r="C71" s="134" t="n">
+      <c r="C71" s="133" t="n">
         <v>-10</v>
       </c>
-      <c r="D71" s="135" t="s">
+      <c r="D71" s="134" t="s">
         <v>95</v>
       </c>
-      <c r="E71" s="134"/>
-      <c r="F71" s="136" t="s">
+      <c r="E71" s="133"/>
+      <c r="F71" s="135" t="s">
         <v>239</v>
       </c>
-      <c r="G71" s="137" t="s">
+      <c r="G71" s="136" t="s">
         <v>142</v>
       </c>
-      <c r="H71" s="137" t="s">
+      <c r="H71" s="136" t="s">
         <v>103</v>
       </c>
-      <c r="I71" s="137"/>
+      <c r="I71" s="136"/>
     </row>
     <row r="72" customFormat="false" ht="16.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A72" s="132" t="n">
+      <c r="A72" s="131" t="n">
         <v>46091</v>
       </c>
-      <c r="B72" s="137" t="s">
+      <c r="B72" s="136" t="s">
         <v>240</v>
       </c>
-      <c r="C72" s="134" t="n">
+      <c r="C72" s="133" t="n">
         <v>10</v>
       </c>
-      <c r="D72" s="135" t="s">
+      <c r="D72" s="134" t="s">
         <v>95</v>
       </c>
-      <c r="E72" s="134"/>
-      <c r="F72" s="136" t="s">
+      <c r="E72" s="133"/>
+      <c r="F72" s="135" t="s">
         <v>239</v>
       </c>
-      <c r="G72" s="137" t="s">
+      <c r="G72" s="136" t="s">
         <v>142</v>
       </c>
-      <c r="H72" s="137" t="s">
+      <c r="H72" s="136" t="s">
         <v>106</v>
       </c>
-      <c r="I72" s="137"/>
+      <c r="I72" s="136"/>
     </row>
     <row r="73" customFormat="false" ht="16.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A73" s="132" t="n">
+      <c r="A73" s="131" t="n">
         <v>46091</v>
       </c>
-      <c r="B73" s="137" t="s">
+      <c r="B73" s="136" t="s">
         <v>58</v>
       </c>
-      <c r="C73" s="134" t="n">
+      <c r="C73" s="133" t="n">
         <v>10</v>
       </c>
-      <c r="D73" s="135" t="s">
+      <c r="D73" s="134" t="s">
         <v>95</v>
       </c>
-      <c r="E73" s="134"/>
-      <c r="F73" s="136"/>
-      <c r="G73" s="137" t="s">
+      <c r="E73" s="133"/>
+      <c r="F73" s="135"/>
+      <c r="G73" s="136" t="s">
         <v>193</v>
       </c>
-      <c r="H73" s="137" t="s">
+      <c r="H73" s="136" t="s">
         <v>106</v>
       </c>
-      <c r="I73" s="137"/>
+      <c r="I73" s="136"/>
     </row>
     <row r="74" customFormat="false" ht="16.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A74" s="132" t="n">
+      <c r="A74" s="131" t="n">
         <v>46092</v>
       </c>
-      <c r="B74" s="137" t="s">
+      <c r="B74" s="136" t="s">
         <v>58</v>
       </c>
-      <c r="C74" s="134" t="n">
+      <c r="C74" s="133" t="n">
         <v>2881.92</v>
       </c>
-      <c r="D74" s="135" t="s">
+      <c r="D74" s="134" t="s">
         <v>95</v>
       </c>
-      <c r="E74" s="134"/>
-      <c r="F74" s="136"/>
-      <c r="G74" s="137" t="s">
+      <c r="E74" s="133"/>
+      <c r="F74" s="135"/>
+      <c r="G74" s="136" t="s">
         <v>193</v>
       </c>
-      <c r="H74" s="137" t="s">
+      <c r="H74" s="136" t="s">
         <v>103</v>
       </c>
-      <c r="I74" s="137"/>
+      <c r="I74" s="136"/>
     </row>
     <row r="75" customFormat="false" ht="16.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
     <row r="76" customFormat="false" ht="16.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
@@ -17176,24 +17171,57 @@
     <row r="1048576" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
   </sheetData>
   <autoFilter ref="A3:I4"/>
-  <conditionalFormatting sqref="F1:F642 F647:F677 F679:F774 F776:F781 F783:F895 F897:F898 F900:F3180">
-    <cfRule type="cellIs" priority="2" operator="equal" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="27">
+  <conditionalFormatting sqref="B2">
+    <cfRule type="expression" priority="2" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="1">
+      <formula>NOT(ISERROR(FIND("✗",INDIRECT("RC",0))))</formula>
+    </cfRule>
+    <cfRule type="expression" priority="3" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="2">
+      <formula>NOT(ISERROR(FIND("⚠",INDIRECT("RC",0))))</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="A4:A10000">
+    <cfRule type="expression" priority="4" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="27">
+      <formula>AND(ISNUMBER($A4),OR($A4&lt;DATE(2020,1,1),$A4&gt;DATE(année_courante,12,31)))</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="F4:F10000">
+    <cfRule type="cellIs" priority="5" operator="equal" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="28">
       <formula>"-"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="H1:H3 H628:H631 H779:H782 H821 H1002 H1163:H1164">
-    <cfRule type="cellIs" priority="3" operator="equal" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="28">
-      <formula>"Hors compte"</formula>
+  <conditionalFormatting sqref="G4:G10000">
+    <cfRule type="expression" priority="6" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="27">
+      <formula>AND(ISNUMBER($A4),LEFT($G4,1)&lt;&gt;"#",OR($G4="",COUNTIF(CATnom,$G4)=0))</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B2">
-    <cfRule type="expression" priority="4" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="1">
-      <formula>NOT(ISERROR(FIND("✗",INDIRECT("RC",0))))</formula>
-    </cfRule>
-    <cfRule type="expression" priority="5" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="2">
-      <formula>NOT(ISERROR(FIND("⚠",INDIRECT("RC",0))))</formula>
+  <conditionalFormatting sqref="H4:H10000">
+    <cfRule type="expression" priority="7" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="27">
+      <formula>AND(ISNUMBER($A4),OR(AND($H4="",LEFT($G4,1)&lt;&gt;"#"),AND($H4&lt;&gt;"",COUNTIF(AVRintitulé,$H4)=0)))</formula>
     </cfRule>
   </conditionalFormatting>
+  <conditionalFormatting sqref="D4:D10000">
+    <cfRule type="expression" priority="8" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="29">
+      <formula>AND(ISNUMBER($A4),OR(AND($D4="",LEFT($G4,1)&lt;&gt;"#"),AND($D4&lt;&gt;"",COUNTIF(COTcode,$D4)=0)))</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <dataValidations count="4">
+    <dataValidation allowBlank="true" error="La date doit être comprise entre le 01/01/2020 et le 31/12 de l'année courante (contrôle DIVERS de la feuille Contrôles)." errorStyle="stop" errorTitle="Date hors période" operator="between" showDropDown="false" showErrorMessage="true" showInputMessage="false" sqref="A4:A1074" type="custom">
+      <formula1>AND(ISNUMBER($A4),$A4&gt;=DATE(2020,1,1),$A4&lt;=DATE(année_courante,12,31))</formula1>
+      <formula2>0</formula2>
+    </dataValidation>
+    <dataValidation allowBlank="true" error="Saisis une catégorie de la feuille Budget (colonne Catégories) ou une méta-catégorie #… — ou ajoute-la d'abord dans Budget." errorStyle="stop" errorTitle="Catégorie inconnue" operator="between" showDropDown="false" showErrorMessage="true" showInputMessage="false" sqref="G4:G1074" type="custom">
+      <formula1>OR(LEFT($G4,1)="#",COUNTIF(CATnom,$G4)&gt;0)</formula1>
+      <formula2>0</formula2>
+    </dataValidation>
+    <dataValidation allowBlank="true" error="Saisis un compte suivi (feuille Avoirs, avec devise) — ou crée-le d'abord dans Avoirs." errorStyle="stop" errorTitle="Compte inconnu" operator="between" showDropDown="false" showErrorMessage="true" showInputMessage="false" sqref="H4:H1074" type="custom">
+      <formula1>COUNTIF(CTRL1compte,$H4)&gt;0</formula1>
+      <formula2>0</formula2>
+    </dataValidation>
+    <dataValidation allowBlank="true" error="Saisis un code devise de la feuille Cotations (colonne Code) — ou ajoute la devise d'abord dans Cotations." errorStyle="stop" errorTitle="Devise inconnue" operator="between" showDropDown="false" showErrorMessage="true" showInputMessage="false" sqref="D4:D1074" type="custom">
+      <formula1>COUNTIF(COTcode,$D4)&gt;0</formula1>
+      <formula2>0</formula2>
+    </dataValidation>
+  </dataValidations>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
   <pageMargins left="0.75" right="0.75" top="0.5" bottom="0.5" header="0.511811023622047" footer="0.511811023622047"/>
   <pageSetup paperSize="9" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" horizontalDpi="300" verticalDpi="300" copies="1"/>
@@ -17231,8 +17259,8 @@
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="16.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A1" s="141" t="str">
-        <f aca="false">$K$49</f>
+      <c r="A1" s="140" t="str">
+        <f aca="false">$K$52</f>
         <v>✓</v>
       </c>
       <c r="B1" s="10"/>
@@ -17278,8 +17306,8 @@
         <v>4</v>
       </c>
       <c r="B3" s="55"/>
-      <c r="C3" s="117"/>
-      <c r="D3" s="117"/>
+      <c r="C3" s="116"/>
+      <c r="D3" s="116"/>
       <c r="E3" s="16"/>
       <c r="F3" s="16"/>
       <c r="G3" s="16"/>
@@ -17294,11 +17322,11 @@
       <c r="B4" s="55" t="s">
         <v>95</v>
       </c>
-      <c r="C4" s="117" t="n">
+      <c r="C4" s="116" t="n">
         <f aca="false">IF(COUNTIFS(OPcompte,$A4,OPdevise,$B4,OPcatégorie,Solde)&gt;=2,_xlfn.MINIFS(OPdate,OPcompte,$A4,OPdevise,$B4,OPcatégorie,Solde),0)</f>
         <v>0</v>
       </c>
-      <c r="D4" s="117" t="n">
+      <c r="D4" s="116" t="n">
         <f aca="false">_xlfn.MAXIFS(OPdate,OPcompte,$A4,OPdevise,$B4,OPcatégorie,Solde)</f>
         <v>0</v>
       </c>
@@ -17330,11 +17358,11 @@
       <c r="B5" s="55" t="s">
         <v>95</v>
       </c>
-      <c r="C5" s="117" t="n">
+      <c r="C5" s="116" t="n">
         <f aca="false">IF(COUNTIFS(OPcompte,$A5,OPdevise,$B5,OPcatégorie,Solde)&gt;=2,_xlfn.MINIFS(OPdate,OPcompte,$A5,OPdevise,$B5,OPcatégorie,Solde),0)</f>
         <v>0</v>
       </c>
-      <c r="D5" s="117" t="n">
+      <c r="D5" s="116" t="n">
         <f aca="false">_xlfn.MAXIFS(OPdate,OPcompte,$A5,OPdevise,$B5,OPcatégorie,Solde)</f>
         <v>0</v>
       </c>
@@ -17366,11 +17394,11 @@
       <c r="B6" s="55" t="s">
         <v>95</v>
       </c>
-      <c r="C6" s="117" t="n">
+      <c r="C6" s="116" t="n">
         <f aca="false">IF(COUNTIFS(OPcompte,$A6,OPdevise,$B6,OPcatégorie,Solde)&gt;=2,_xlfn.MINIFS(OPdate,OPcompte,$A6,OPdevise,$B6,OPcatégorie,Solde),0)</f>
         <v>0</v>
       </c>
-      <c r="D6" s="117" t="n">
+      <c r="D6" s="116" t="n">
         <f aca="false">_xlfn.MAXIFS(OPdate,OPcompte,$A6,OPdevise,$B6,OPcatégorie,Solde)</f>
         <v>0</v>
       </c>
@@ -17402,11 +17430,11 @@
       <c r="B7" s="55" t="s">
         <v>95</v>
       </c>
-      <c r="C7" s="117" t="n">
+      <c r="C7" s="116" t="n">
         <f aca="false">IF(COUNTIFS(OPcompte,$A7,OPdevise,$B7,OPcatégorie,Solde)&gt;=2,_xlfn.MINIFS(OPdate,OPcompte,$A7,OPdevise,$B7,OPcatégorie,Solde),0)</f>
         <v>0</v>
       </c>
-      <c r="D7" s="117" t="n">
+      <c r="D7" s="116" t="n">
         <f aca="false">_xlfn.MAXIFS(OPdate,OPcompte,$A7,OPdevise,$B7,OPcatégorie,Solde)</f>
         <v>0</v>
       </c>
@@ -17438,27 +17466,27 @@
       <c r="B8" s="55" t="s">
         <v>100</v>
       </c>
-      <c r="C8" s="117" t="n">
+      <c r="C8" s="116" t="n">
         <f aca="false">IF(COUNTIFS(OPcompte,$A8,OPdevise,$B8,OPcatégorie,Solde)&gt;=2,_xlfn.MINIFS(OPdate,OPcompte,$A8,OPdevise,$B8,OPcatégorie,Solde),0)</f>
         <v>0</v>
       </c>
-      <c r="D8" s="117" t="n">
+      <c r="D8" s="116" t="n">
         <f aca="false">_xlfn.MAXIFS(OPdate,OPcompte,$A8,OPdevise,$B8,OPcatégorie,Solde)</f>
         <v>46050</v>
       </c>
-      <c r="E8" s="142" t="n">
+      <c r="E8" s="141" t="n">
         <f aca="false">IF($C8=0,0,_xlfn.XLOOKUP(1,(OPcompte=$A8)*(OPdevise=$B8)*(OPcatégorie=Solde)*(OPdate=$C8),OPmontant,0,0,1))</f>
         <v>0</v>
       </c>
-      <c r="F8" s="142" t="n">
+      <c r="F8" s="141" t="n">
         <f aca="false">$E8+SUMIFS(OPmontant,OPcompte,$A8,OPdevise,$B8,OPdate,"&gt;"&amp;$C8,OPdate,"&lt;="&amp;$D8,OPcatégorie,"&lt;&gt;Solde",OPcatégorie,"&lt;&gt;"&amp;Spéciale)</f>
         <v>3732.02</v>
       </c>
-      <c r="G8" s="142" t="n">
+      <c r="G8" s="141" t="n">
         <f aca="false">_xlfn.XLOOKUP(1,(OPcompte=$A8)*(OPdevise=$B8)*(OPcatégorie=Solde)*(OPdate=$D8),OPmontant,0,0,-1)</f>
         <v>3549.43</v>
       </c>
-      <c r="H8" s="142" t="n">
+      <c r="H8" s="141" t="n">
         <f aca="false">IF(ABS($G8-$F8)&lt;0.015,0,ROUND($G8-$F8,2))</f>
         <v>-182.59</v>
       </c>
@@ -17474,11 +17502,11 @@
       <c r="B9" s="55" t="s">
         <v>95</v>
       </c>
-      <c r="C9" s="117" t="n">
+      <c r="C9" s="116" t="n">
         <f aca="false">IF(COUNTIFS(OPcompte,$A9,OPdevise,$B9,OPcatégorie,Solde)&gt;=2,_xlfn.MINIFS(OPdate,OPcompte,$A9,OPdevise,$B9,OPcatégorie,Solde),0)</f>
         <v>0</v>
       </c>
-      <c r="D9" s="117" t="n">
+      <c r="D9" s="116" t="n">
         <f aca="false">_xlfn.MAXIFS(OPdate,OPcompte,$A9,OPdevise,$B9,OPcatégorie,Solde)</f>
         <v>45657</v>
       </c>
@@ -17510,11 +17538,11 @@
       <c r="B10" s="55" t="s">
         <v>95</v>
       </c>
-      <c r="C10" s="117" t="n">
+      <c r="C10" s="116" t="n">
         <f aca="false">IF(COUNTIFS(OPcompte,$A10,OPdevise,$B10,OPcatégorie,Solde)&gt;=2,_xlfn.MINIFS(OPdate,OPcompte,$A10,OPdevise,$B10,OPcatégorie,Solde),0)</f>
         <v>0</v>
       </c>
-      <c r="D10" s="117" t="n">
+      <c r="D10" s="116" t="n">
         <f aca="false">_xlfn.MAXIFS(OPdate,OPcompte,$A10,OPdevise,$B10,OPcatégorie,Solde)</f>
         <v>0</v>
       </c>
@@ -17546,11 +17574,11 @@
       <c r="B11" s="55" t="s">
         <v>95</v>
       </c>
-      <c r="C11" s="117" t="n">
+      <c r="C11" s="116" t="n">
         <f aca="false">IF(COUNTIFS(OPcompte,$A11,OPdevise,$B11,OPcatégorie,Solde)&gt;=2,_xlfn.MINIFS(OPdate,OPcompte,$A11,OPdevise,$B11,OPcatégorie,Solde),0)</f>
         <v>44927</v>
       </c>
-      <c r="D11" s="117" t="n">
+      <c r="D11" s="116" t="n">
         <f aca="false">_xlfn.MAXIFS(OPdate,OPcompte,$A11,OPdevise,$B11,OPcatégorie,Solde)</f>
         <v>46092</v>
       </c>
@@ -17582,11 +17610,11 @@
       <c r="B12" s="55" t="s">
         <v>95</v>
       </c>
-      <c r="C12" s="117" t="n">
+      <c r="C12" s="116" t="n">
         <f aca="false">IF(COUNTIFS(OPcompte,$A12,OPdevise,$B12,OPcatégorie,Solde)&gt;=2,_xlfn.MINIFS(OPdate,OPcompte,$A12,OPdevise,$B12,OPcatégorie,Solde),0)</f>
         <v>45657</v>
       </c>
-      <c r="D12" s="117" t="n">
+      <c r="D12" s="116" t="n">
         <f aca="false">_xlfn.MAXIFS(OPdate,OPcompte,$A12,OPdevise,$B12,OPcatégorie,Solde)</f>
         <v>46084</v>
       </c>
@@ -17618,11 +17646,11 @@
       <c r="B13" s="55" t="s">
         <v>95</v>
       </c>
-      <c r="C13" s="117" t="n">
+      <c r="C13" s="116" t="n">
         <f aca="false">IF(COUNTIFS(OPcompte,$A13,OPdevise,$B13,OPcatégorie,Solde)&gt;=2,_xlfn.MINIFS(OPdate,OPcompte,$A13,OPdevise,$B13,OPcatégorie,Solde),0)</f>
         <v>0</v>
       </c>
-      <c r="D13" s="117" t="n">
+      <c r="D13" s="116" t="n">
         <f aca="false">_xlfn.MAXIFS(OPdate,OPcompte,$A13,OPdevise,$B13,OPcatégorie,Solde)</f>
         <v>0</v>
       </c>
@@ -17654,11 +17682,11 @@
       <c r="B14" s="55" t="s">
         <v>95</v>
       </c>
-      <c r="C14" s="117" t="n">
+      <c r="C14" s="116" t="n">
         <f aca="false">IF(COUNTIFS(OPcompte,$A14,OPdevise,$B14,OPcatégorie,Solde)&gt;=2,_xlfn.MINIFS(OPdate,OPcompte,$A14,OPdevise,$B14,OPcatégorie,Solde),0)</f>
         <v>0</v>
       </c>
-      <c r="D14" s="117" t="n">
+      <c r="D14" s="116" t="n">
         <f aca="false">_xlfn.MAXIFS(OPdate,OPcompte,$A14,OPdevise,$B14,OPcatégorie,Solde)</f>
         <v>46091</v>
       </c>
@@ -17690,11 +17718,11 @@
       <c r="B15" s="55" t="s">
         <v>95</v>
       </c>
-      <c r="C15" s="117" t="n">
+      <c r="C15" s="116" t="n">
         <f aca="false">IF(COUNTIFS(OPcompte,$A15,OPdevise,$B15,OPcatégorie,Solde)&gt;=2,_xlfn.MINIFS(OPdate,OPcompte,$A15,OPdevise,$B15,OPcatégorie,Solde),0)</f>
         <v>0</v>
       </c>
-      <c r="D15" s="117" t="n">
+      <c r="D15" s="116" t="n">
         <f aca="false">_xlfn.MAXIFS(OPdate,OPcompte,$A15,OPdevise,$B15,OPcatégorie,Solde)</f>
         <v>0</v>
       </c>
@@ -17726,11 +17754,11 @@
       <c r="B16" s="55" t="s">
         <v>95</v>
       </c>
-      <c r="C16" s="117" t="n">
+      <c r="C16" s="116" t="n">
         <f aca="false">IF(COUNTIFS(OPcompte,$A16,OPdevise,$B16,OPcatégorie,Solde)&gt;=2,_xlfn.MINIFS(OPdate,OPcompte,$A16,OPdevise,$B16,OPcatégorie,Solde),0)</f>
         <v>0</v>
       </c>
-      <c r="D16" s="117" t="n">
+      <c r="D16" s="116" t="n">
         <f aca="false">_xlfn.MAXIFS(OPdate,OPcompte,$A16,OPdevise,$B16,OPcatégorie,Solde)</f>
         <v>0</v>
       </c>
@@ -17762,11 +17790,11 @@
       <c r="B17" s="55" t="s">
         <v>95</v>
       </c>
-      <c r="C17" s="117" t="n">
+      <c r="C17" s="116" t="n">
         <f aca="false">IF(COUNTIFS(OPcompte,$A17,OPdevise,$B17,OPcatégorie,Solde)&gt;=2,_xlfn.MINIFS(OPdate,OPcompte,$A17,OPdevise,$B17,OPcatégorie,Solde),0)</f>
         <v>0</v>
       </c>
-      <c r="D17" s="117" t="n">
+      <c r="D17" s="116" t="n">
         <f aca="false">_xlfn.MAXIFS(OPdate,OPcompte,$A17,OPdevise,$B17,OPcatégorie,Solde)</f>
         <v>0</v>
       </c>
@@ -17798,27 +17826,27 @@
       <c r="B18" s="55" t="s">
         <v>100</v>
       </c>
-      <c r="C18" s="117" t="n">
+      <c r="C18" s="116" t="n">
         <f aca="false">IF(COUNTIFS(OPcompte,$A18,OPdevise,$B18,OPcatégorie,Solde)&gt;=2,_xlfn.MINIFS(OPdate,OPcompte,$A18,OPdevise,$B18,OPcatégorie,Solde),0)</f>
         <v>0</v>
       </c>
-      <c r="D18" s="117" t="n">
+      <c r="D18" s="116" t="n">
         <f aca="false">_xlfn.MAXIFS(OPdate,OPcompte,$A18,OPdevise,$B18,OPcatégorie,Solde)</f>
         <v>0</v>
       </c>
-      <c r="E18" s="142" t="n">
+      <c r="E18" s="141" t="n">
         <f aca="false">IF($C18=0,0,_xlfn.XLOOKUP(1,(OPcompte=$A18)*(OPdevise=$B18)*(OPcatégorie=Solde)*(OPdate=$C18),OPmontant,0,0,1))</f>
         <v>0</v>
       </c>
-      <c r="F18" s="142" t="n">
+      <c r="F18" s="141" t="n">
         <f aca="false">$E18+SUMIFS(OPmontant,OPcompte,$A18,OPdevise,$B18,OPdate,"&gt;"&amp;$C18,OPdate,"&lt;="&amp;$D18,OPcatégorie,"&lt;&gt;Solde",OPcatégorie,"&lt;&gt;"&amp;Spéciale)</f>
         <v>0</v>
       </c>
-      <c r="G18" s="142" t="n">
+      <c r="G18" s="141" t="n">
         <f aca="false">_xlfn.XLOOKUP(1,(OPcompte=$A18)*(OPdevise=$B18)*(OPcatégorie=Solde)*(OPdate=$D18),OPmontant,0,0,-1)</f>
         <v>0</v>
       </c>
-      <c r="H18" s="142" t="n">
+      <c r="H18" s="141" t="n">
         <f aca="false">IF(ABS($G18-$F18)&lt;0.015,0,ROUND($G18-$F18,2))</f>
         <v>0</v>
       </c>
@@ -17834,27 +17862,27 @@
       <c r="B19" s="55" t="s">
         <v>112</v>
       </c>
-      <c r="C19" s="117" t="n">
+      <c r="C19" s="116" t="n">
         <f aca="false">IF(COUNTIFS(OPcompte,$A19,OPdevise,$B19,OPcatégorie,Solde)&gt;=2,_xlfn.MINIFS(OPdate,OPcompte,$A19,OPdevise,$B19,OPcatégorie,Solde),0)</f>
         <v>0</v>
       </c>
-      <c r="D19" s="117" t="n">
+      <c r="D19" s="116" t="n">
         <f aca="false">_xlfn.MAXIFS(OPdate,OPcompte,$A19,OPdevise,$B19,OPcatégorie,Solde)</f>
         <v>0</v>
       </c>
-      <c r="E19" s="143" t="n">
+      <c r="E19" s="142" t="n">
         <f aca="false">IF($C19=0,0,_xlfn.XLOOKUP(1,(OPcompte=$A19)*(OPdevise=$B19)*(OPcatégorie=Solde)*(OPdate=$C19),OPmontant,0,0,1))</f>
         <v>0</v>
       </c>
-      <c r="F19" s="143" t="n">
+      <c r="F19" s="142" t="n">
         <f aca="false">$E19+SUMIFS(OPmontant,OPcompte,$A19,OPdevise,$B19,OPdate,"&gt;"&amp;$C19,OPdate,"&lt;="&amp;$D19,OPcatégorie,"&lt;&gt;Solde",OPcatégorie,"&lt;&gt;"&amp;Spéciale)</f>
         <v>0</v>
       </c>
-      <c r="G19" s="143" t="n">
+      <c r="G19" s="142" t="n">
         <f aca="false">_xlfn.XLOOKUP(1,(OPcompte=$A19)*(OPdevise=$B19)*(OPcatégorie=Solde)*(OPdate=$D19),OPmontant,0,0,-1)</f>
         <v>0</v>
       </c>
-      <c r="H19" s="143" t="n">
+      <c r="H19" s="142" t="n">
         <f aca="false">IF(ABS($G19-$F19)&lt;0.015,0,ROUND($G19-$F19,2))</f>
         <v>0</v>
       </c>
@@ -17870,27 +17898,27 @@
       <c r="B20" s="55" t="s">
         <v>100</v>
       </c>
-      <c r="C20" s="117" t="n">
+      <c r="C20" s="116" t="n">
         <f aca="false">IF(COUNTIFS(OPcompte,$A20,OPdevise,$B20,OPcatégorie,Solde)&gt;=2,_xlfn.MINIFS(OPdate,OPcompte,$A20,OPdevise,$B20,OPcatégorie,Solde),0)</f>
         <v>45621</v>
       </c>
-      <c r="D20" s="117" t="n">
+      <c r="D20" s="116" t="n">
         <f aca="false">_xlfn.MAXIFS(OPdate,OPcompte,$A20,OPdevise,$B20,OPcatégorie,Solde)</f>
         <v>46050</v>
       </c>
-      <c r="E20" s="142" t="n">
+      <c r="E20" s="141" t="n">
         <f aca="false">IF($C20=0,0,_xlfn.XLOOKUP(1,(OPcompte=$A20)*(OPdevise=$B20)*(OPcatégorie=Solde)*(OPdate=$C20),OPmontant,0,0,1))</f>
         <v>2500</v>
       </c>
-      <c r="F20" s="142" t="n">
+      <c r="F20" s="141" t="n">
         <f aca="false">$E20+SUMIFS(OPmontant,OPcompte,$A20,OPdevise,$B20,OPdate,"&gt;"&amp;$C20,OPdate,"&lt;="&amp;$D20,OPcatégorie,"&lt;&gt;Solde",OPcatégorie,"&lt;&gt;"&amp;Spéciale)</f>
         <v>487.59</v>
       </c>
-      <c r="G20" s="142" t="n">
+      <c r="G20" s="141" t="n">
         <f aca="false">_xlfn.XLOOKUP(1,(OPcompte=$A20)*(OPdevise=$B20)*(OPcatégorie=Solde)*(OPdate=$D20),OPmontant,0,0,-1)</f>
         <v>487.59</v>
       </c>
-      <c r="H20" s="142" t="n">
+      <c r="H20" s="141" t="n">
         <f aca="false">IF(ABS($G20-$F20)&lt;0.015,0,ROUND($G20-$F20,2))</f>
         <v>0</v>
       </c>
@@ -17906,11 +17934,11 @@
       <c r="B21" s="55" t="s">
         <v>95</v>
       </c>
-      <c r="C21" s="117" t="n">
+      <c r="C21" s="116" t="n">
         <f aca="false">IF(COUNTIFS(OPcompte,$A21,OPdevise,$B21,OPcatégorie,Solde)&gt;=2,_xlfn.MINIFS(OPdate,OPcompte,$A21,OPdevise,$B21,OPcatégorie,Solde),0)</f>
         <v>45657</v>
       </c>
-      <c r="D21" s="117" t="n">
+      <c r="D21" s="116" t="n">
         <f aca="false">_xlfn.MAXIFS(OPdate,OPcompte,$A21,OPdevise,$B21,OPcatégorie,Solde)</f>
         <v>46058</v>
       </c>
@@ -17942,27 +17970,27 @@
       <c r="B22" s="55" t="s">
         <v>116</v>
       </c>
-      <c r="C22" s="117" t="n">
+      <c r="C22" s="116" t="n">
         <f aca="false">IF(COUNTIFS(OPcompte,$A22,OPdevise,$B22,OPcatégorie,Solde)&gt;=2,_xlfn.MINIFS(OPdate,OPcompte,$A22,OPdevise,$B22,OPcatégorie,Solde),0)</f>
         <v>44927</v>
       </c>
-      <c r="D22" s="117" t="n">
+      <c r="D22" s="116" t="n">
         <f aca="false">_xlfn.MAXIFS(OPdate,OPcompte,$A22,OPdevise,$B22,OPcatégorie,Solde)</f>
         <v>45292</v>
       </c>
-      <c r="E22" s="144" t="n">
+      <c r="E22" s="143" t="n">
         <f aca="false">IF($C22=0,0,_xlfn.XLOOKUP(1,(OPcompte=$A22)*(OPdevise=$B22)*(OPcatégorie=Solde)*(OPdate=$C22),OPmontant,0,0,1))</f>
         <v>503110</v>
       </c>
-      <c r="F22" s="144" t="n">
+      <c r="F22" s="143" t="n">
         <f aca="false">$E22+SUMIFS(OPmontant,OPcompte,$A22,OPdevise,$B22,OPdate,"&gt;"&amp;$C22,OPdate,"&lt;="&amp;$D22,OPcatégorie,"&lt;&gt;Solde",OPcatégorie,"&lt;&gt;"&amp;Spéciale)</f>
         <v>0</v>
       </c>
-      <c r="G22" s="144" t="n">
+      <c r="G22" s="143" t="n">
         <f aca="false">_xlfn.XLOOKUP(1,(OPcompte=$A22)*(OPdevise=$B22)*(OPcatégorie=Solde)*(OPdate=$D22),OPmontant,0,0,-1)</f>
         <v>0</v>
       </c>
-      <c r="H22" s="144" t="n">
+      <c r="H22" s="143" t="n">
         <f aca="false">IF(ABS($G22-$F22)&lt;0.015,0,ROUND($G22-$F22,2))</f>
         <v>0</v>
       </c>
@@ -17978,27 +18006,27 @@
       <c r="B23" s="55" t="s">
         <v>116</v>
       </c>
-      <c r="C23" s="117" t="n">
+      <c r="C23" s="116" t="n">
         <f aca="false">IF(COUNTIFS(OPcompte,$A23,OPdevise,$B23,OPcatégorie,Solde)&gt;=2,_xlfn.MINIFS(OPdate,OPcompte,$A23,OPdevise,$B23,OPcatégorie,Solde),0)</f>
         <v>0</v>
       </c>
-      <c r="D23" s="117" t="n">
+      <c r="D23" s="116" t="n">
         <f aca="false">_xlfn.MAXIFS(OPdate,OPcompte,$A23,OPdevise,$B23,OPcatégorie,Solde)</f>
         <v>45292</v>
       </c>
-      <c r="E23" s="144" t="n">
+      <c r="E23" s="143" t="n">
         <f aca="false">IF($C23=0,0,_xlfn.XLOOKUP(1,(OPcompte=$A23)*(OPdevise=$B23)*(OPcatégorie=Solde)*(OPdate=$C23),OPmontant,0,0,1))</f>
         <v>0</v>
       </c>
-      <c r="F23" s="144" t="n">
+      <c r="F23" s="143" t="n">
         <f aca="false">$E23+SUMIFS(OPmontant,OPcompte,$A23,OPdevise,$B23,OPdate,"&gt;"&amp;$C23,OPdate,"&lt;="&amp;$D23,OPcatégorie,"&lt;&gt;Solde",OPcatégorie,"&lt;&gt;"&amp;Spéciale)</f>
         <v>278800</v>
       </c>
-      <c r="G23" s="144" t="n">
+      <c r="G23" s="143" t="n">
         <f aca="false">_xlfn.XLOOKUP(1,(OPcompte=$A23)*(OPdevise=$B23)*(OPcatégorie=Solde)*(OPdate=$D23),OPmontant,0,0,-1)</f>
         <v>278800</v>
       </c>
-      <c r="H23" s="144" t="n">
+      <c r="H23" s="143" t="n">
         <f aca="false">IF(ABS($G23-$F23)&lt;0.015,0,ROUND($G23-$F23,2))</f>
         <v>0</v>
       </c>
@@ -18014,27 +18042,27 @@
       <c r="B24" s="55" t="s">
         <v>116</v>
       </c>
-      <c r="C24" s="117" t="n">
+      <c r="C24" s="116" t="n">
         <f aca="false">IF(COUNTIFS(OPcompte,$A24,OPdevise,$B24,OPcatégorie,Solde)&gt;=2,_xlfn.MINIFS(OPdate,OPcompte,$A24,OPdevise,$B24,OPcatégorie,Solde),0)</f>
         <v>45923</v>
       </c>
-      <c r="D24" s="117" t="n">
+      <c r="D24" s="116" t="n">
         <f aca="false">_xlfn.MAXIFS(OPdate,OPcompte,$A24,OPdevise,$B24,OPcatégorie,Solde)</f>
         <v>45967</v>
       </c>
-      <c r="E24" s="144" t="n">
+      <c r="E24" s="143" t="n">
         <f aca="false">IF($C24=0,0,_xlfn.XLOOKUP(1,(OPcompte=$A24)*(OPdevise=$B24)*(OPcatégorie=Solde)*(OPdate=$C24),OPmontant,0,0,1))</f>
         <v>51277</v>
       </c>
-      <c r="F24" s="144" t="n">
+      <c r="F24" s="143" t="n">
         <f aca="false">$E24+SUMIFS(OPmontant,OPcompte,$A24,OPdevise,$B24,OPdate,"&gt;"&amp;$C24,OPdate,"&lt;="&amp;$D24,OPcatégorie,"&lt;&gt;Solde",OPcatégorie,"&lt;&gt;"&amp;Spéciale)</f>
         <v>51277</v>
       </c>
-      <c r="G24" s="144" t="n">
+      <c r="G24" s="143" t="n">
         <f aca="false">_xlfn.XLOOKUP(1,(OPcompte=$A24)*(OPdevise=$B24)*(OPcatégorie=Solde)*(OPdate=$D24),OPmontant,0,0,-1)</f>
         <v>51277</v>
       </c>
-      <c r="H24" s="144" t="n">
+      <c r="H24" s="143" t="n">
         <f aca="false">IF(ABS($G24-$F24)&lt;0.015,0,ROUND($G24-$F24,2))</f>
         <v>0</v>
       </c>
@@ -18050,27 +18078,27 @@
       <c r="B25" s="55" t="s">
         <v>120</v>
       </c>
-      <c r="C25" s="117" t="n">
+      <c r="C25" s="116" t="n">
         <f aca="false">IF(COUNTIFS(OPcompte,$A25,OPdevise,$B25,OPcatégorie,Solde)&gt;=2,_xlfn.MINIFS(OPdate,OPcompte,$A25,OPdevise,$B25,OPcatégorie,Solde),0)</f>
         <v>0</v>
       </c>
-      <c r="D25" s="117" t="n">
+      <c r="D25" s="116" t="n">
         <f aca="false">_xlfn.MAXIFS(OPdate,OPcompte,$A25,OPdevise,$B25,OPcatégorie,Solde)</f>
         <v>0</v>
       </c>
-      <c r="E25" s="145" t="n">
+      <c r="E25" s="144" t="n">
         <f aca="false">IF($C25=0,0,_xlfn.XLOOKUP(1,(OPcompte=$A25)*(OPdevise=$B25)*(OPcatégorie=Solde)*(OPdate=$C25),OPmontant,0,0,1))</f>
         <v>0</v>
       </c>
-      <c r="F25" s="145" t="n">
+      <c r="F25" s="144" t="n">
         <f aca="false">$E25+SUMIFS(OPmontant,OPcompte,$A25,OPdevise,$B25,OPdate,"&gt;"&amp;$C25,OPdate,"&lt;="&amp;$D25,OPcatégorie,"&lt;&gt;Solde",OPcatégorie,"&lt;&gt;"&amp;Spéciale)</f>
         <v>0</v>
       </c>
-      <c r="G25" s="145" t="n">
+      <c r="G25" s="144" t="n">
         <f aca="false">_xlfn.XLOOKUP(1,(OPcompte=$A25)*(OPdevise=$B25)*(OPcatégorie=Solde)*(OPdate=$D25),OPmontant,0,0,-1)</f>
         <v>0</v>
       </c>
-      <c r="H25" s="145" t="n">
+      <c r="H25" s="144" t="n">
         <f aca="false">IF(ABS($G25-$F25)&lt;0.015,0,ROUND($G25-$F25,2))</f>
         <v>0</v>
       </c>
@@ -18079,17 +18107,17 @@
       </c>
     </row>
     <row r="26" customFormat="false" ht="16.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A26" s="146" t="s">
+      <c r="A26" s="145" t="s">
         <v>4</v>
       </c>
-      <c r="B26" s="147"/>
-      <c r="C26" s="147"/>
-      <c r="D26" s="147"/>
-      <c r="E26" s="147"/>
-      <c r="F26" s="148"/>
-      <c r="G26" s="149"/>
-      <c r="H26" s="149"/>
-      <c r="I26" s="147"/>
+      <c r="B26" s="146"/>
+      <c r="C26" s="146"/>
+      <c r="D26" s="146"/>
+      <c r="E26" s="146"/>
+      <c r="F26" s="147"/>
+      <c r="G26" s="148"/>
+      <c r="H26" s="148"/>
+      <c r="I26" s="146"/>
     </row>
     <row r="27" customFormat="false" ht="17.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A27" s="69"/>
@@ -18097,7 +18125,7 @@
       <c r="C27" s="71"/>
       <c r="D27" s="71"/>
       <c r="E27" s="71"/>
-      <c r="F27" s="150"/>
+      <c r="F27" s="149"/>
       <c r="G27" s="69"/>
       <c r="H27" s="69"/>
       <c r="I27" s="69"/>
@@ -18129,252 +18157,282 @@
         <v>4</v>
       </c>
       <c r="K31" s="55"/>
-      <c r="L31" s="151"/>
-      <c r="M31" s="104"/>
+      <c r="L31" s="150"/>
+      <c r="M31" s="103"/>
     </row>
     <row r="32" customFormat="false" ht="16.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="J32" s="32" t="s">
         <v>254</v>
       </c>
-      <c r="K32" s="147" t="str">
+      <c r="K32" s="146" t="str">
         <f aca="false">IF(L32=0,"✓","✗")</f>
         <v>✓</v>
       </c>
-      <c r="L32" s="151" t="n">
+      <c r="L32" s="150" t="n">
         <f aca="false">COUNTIFS(CTRL1controle,"Oui")-COUNTIFS(CTRL1controle,"Oui",CTRL1ecart,0)</f>
         <v>0</v>
       </c>
-      <c r="M32" s="152" t="n">
+      <c r="M32" s="151" t="n">
         <f aca="false">COUNTIFS(CTRL1devise,M$8,CTRL1controle,"Oui")-COUNTIFS(CTRL1devise,M$8,CTRL1controle,"Oui",CTRL1ecart,0)</f>
         <v>0</v>
       </c>
     </row>
     <row r="33" customFormat="false" ht="16.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="J33" s="32" t="s">
-        <v>255</v>
-      </c>
-      <c r="K33" s="147" t="str">
-        <f aca="false">IF(ABS(L33)&lt;1,"✓","✗")</f>
+        <v>66</v>
+      </c>
+      <c r="K33" s="146" t="str">
+        <f aca="false">IF(L33&gt;0,"✗","✓")</f>
         <v>✓</v>
       </c>
-      <c r="L33" s="91" t="n">
-        <f aca="false">ABS(Budget!G$38)+ABS(Budget!I$39-Budget!G$39)+ABS(Budget!C$14)</f>
-        <v>0</v>
-      </c>
-      <c r="M33" s="104" t="n">
-        <f aca="false">ROUND(SUMPRODUCT(SUMIFS(OPmontant,OPdevise,M$30,OPcatégorie,CATnom,OPdate,"&gt;"&amp;Budget!$C$2-365))-SUMIFS(OPmontant,OPdevise,M$30,OPcatégorie,"&lt;&gt;"&amp;Spéciale,OPdate,"&gt;"&amp;Budget!$C$2-365),2)</f>
-        <v>0</v>
-      </c>
+      <c r="L33" s="34" t="n">
+        <f aca="false">IF(L34&gt;0,1,0)+IF(L35&gt;0,1,0)+IF(ABS(L36)&gt;=1,1,0)</f>
+        <v>0</v>
+      </c>
+      <c r="M33" s="91"/>
     </row>
     <row r="34" customFormat="false" ht="16.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="J34" s="32" t="s">
+        <v>255</v>
+      </c>
+      <c r="K34" s="146"/>
+      <c r="L34" s="34" t="n">
+        <f aca="false">SUMPRODUCT(ISNUMBER(OPdate)*(OPcatégorie=""))</f>
+        <v>0</v>
+      </c>
+      <c r="M34" s="151"/>
+    </row>
+    <row r="35" customFormat="false" ht="16.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="J35" s="32" t="s">
+        <v>256</v>
+      </c>
+      <c r="K35" s="146"/>
+      <c r="L35" s="34" t="n">
+        <f aca="false">SUMPRODUCT((COUNTIF(CATnom,OPcatégorie)=0)*(OPcatégorie&lt;&gt;"")*(LEFT(OPcatégorie,1)&lt;&gt;"#"))</f>
+        <v>0</v>
+      </c>
+      <c r="M35" s="151"/>
+    </row>
+    <row r="36" customFormat="false" ht="16.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="J36" s="32" t="s">
+        <v>257</v>
+      </c>
+      <c r="K36" s="146"/>
+      <c r="L36" s="91" t="n">
+        <f aca="false">ABS(Budget!G$38)+ABS(Budget!I$39-Budget!G$39)+ABS(Budget!C$14)</f>
+        <v>0</v>
+      </c>
+      <c r="M36" s="103" t="n">
+        <f aca="false">ROUND(SUMPRODUCT(SUMIFS(OPmontant,OPdevise,M$30,OPcatégorie,CATnom,OPdate,"&gt;"&amp;Budget!$C$2-365))-SUMIFS(OPmontant,OPdevise,M$30,OPcatégorie,"&lt;&gt;"&amp;Spéciale,OPdate,"&gt;"&amp;Budget!$C$2-365),2)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="37" customFormat="false" ht="16.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="J37" s="32" t="s">
         <v>70</v>
       </c>
-      <c r="K34" s="147" t="str">
-        <f aca="false">IF(L34&gt;0,"⚠","✓")</f>
+      <c r="K37" s="146" t="str">
+        <f aca="false">IF(L37&gt;0,"⚠","✓")</f>
         <v>✓</v>
       </c>
-      <c r="L34" s="34" t="n">
-        <f aca="false">SUM(L35:L37)</f>
-        <v>0</v>
-      </c>
-      <c r="M34" s="91"/>
-    </row>
-    <row r="35" customFormat="false" ht="16.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="J35" s="153" t="s">
-        <v>256</v>
-      </c>
-      <c r="K35" s="147"/>
-      <c r="L35" s="34" t="n">
+      <c r="L37" s="34" t="n">
+        <f aca="false">SUM(L38:L40)</f>
+        <v>0</v>
+      </c>
+      <c r="M37" s="91"/>
+    </row>
+    <row r="38" customFormat="false" ht="16.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="J38" s="152" t="s">
+        <v>258</v>
+      </c>
+      <c r="K38" s="146"/>
+      <c r="L38" s="34" t="n">
         <f aca="false">COUNTIF(OPdate,"&lt;"&amp;DATE(2020,1,1))+COUNTIF(OPdate,"&gt;"&amp;DATE(année_courante,12,31))</f>
         <v>0</v>
       </c>
-      <c r="M35" s="152"/>
-    </row>
-    <row r="36" customFormat="false" ht="16.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="J36" s="153" t="s">
-        <v>257</v>
-      </c>
-      <c r="K36" s="147"/>
-      <c r="L36" s="34" t="n">
+      <c r="M38" s="151"/>
+    </row>
+    <row r="39" customFormat="false" ht="16.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="J39" s="152" t="s">
+        <v>259</v>
+      </c>
+      <c r="K39" s="146"/>
+      <c r="L39" s="34" t="n">
         <f aca="false">Patrimoine!D54</f>
         <v>0</v>
       </c>
-      <c r="M36" s="152"/>
-    </row>
-    <row r="37" customFormat="false" ht="16.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="J37" s="153" t="s">
-        <v>258</v>
-      </c>
-      <c r="K37" s="147"/>
-      <c r="L37" s="34" t="n">
+      <c r="M39" s="151"/>
+    </row>
+    <row r="40" customFormat="false" ht="16.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="J40" s="152" t="s">
+        <v>260</v>
+      </c>
+      <c r="K40" s="146"/>
+      <c r="L40" s="34" t="n">
         <f aca="false">IF(Cotations!B27="⚠",1,0)</f>
         <v>0</v>
       </c>
-      <c r="M37" s="102"/>
-    </row>
-    <row r="38" customFormat="false" ht="16.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="J38" s="32" t="s">
-        <v>259</v>
-      </c>
-      <c r="K38" s="147" t="str">
-        <f aca="false">IF(L38=0,"✓","⚠")</f>
+      <c r="M40" s="101"/>
+    </row>
+    <row r="41" customFormat="false" ht="16.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="J41" s="32" t="s">
+        <v>261</v>
+      </c>
+      <c r="K41" s="146" t="str">
+        <f aca="false">IF(L41=0,"✓","⚠")</f>
         <v>✓</v>
       </c>
-      <c r="L38" s="151" t="n">
+      <c r="L41" s="150" t="n">
         <f aca="false">COUNTIFS(OPréf,"-")</f>
         <v>0</v>
       </c>
-      <c r="M38" s="104" t="n">
+      <c r="M41" s="103" t="n">
         <f aca="false">COUNTIFS(OPréf,"-",OPdevise,M$30)</f>
         <v>0</v>
       </c>
     </row>
-    <row r="39" customFormat="false" ht="16.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="J39" s="146" t="s">
-        <v>260</v>
-      </c>
-      <c r="K39" s="147" t="str">
-        <f aca="false">IF(L39=0,"✓","⚠")</f>
+    <row r="42" customFormat="false" ht="16.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="J42" s="145" t="s">
+        <v>262</v>
+      </c>
+      <c r="K42" s="146" t="str">
+        <f aca="false">IF(L42=0,"✓","⚠")</f>
         <v>✓</v>
       </c>
-      <c r="L39" s="151" t="n">
-        <f aca="false">3-COUNTIFS(L40:L42,0)</f>
-        <v>0</v>
-      </c>
-      <c r="M39" s="104" t="n">
-        <f aca="false">COUNTA($J40:$J42)-COUNTIFS(M40:M42,0)</f>
+      <c r="L42" s="150" t="n">
+        <f aca="false">3-COUNTIFS(L43:L45,0)</f>
+        <v>0</v>
+      </c>
+      <c r="M42" s="103" t="n">
+        <f aca="false">COUNTA($J43:$J45)-COUNTIFS(M43:M45,0)</f>
         <v>1</v>
       </c>
     </row>
-    <row r="40" customFormat="false" ht="16.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="J40" s="154" t="s">
-        <v>261</v>
-      </c>
-      <c r="K40" s="55"/>
-      <c r="L40" s="91" t="n">
+    <row r="43" customFormat="false" ht="16.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="J43" s="153" t="s">
+        <v>263</v>
+      </c>
+      <c r="K43" s="55"/>
+      <c r="L43" s="91" t="n">
         <f aca="false">ROUND(SUMIFS(OPequiv_euro,OPcatégorie,"@Virement"),0)</f>
         <v>0</v>
       </c>
-      <c r="M40" s="104" t="n">
+      <c r="M43" s="103" t="n">
         <f aca="false">SUMIFS(OPequiv_euro,OPdevise,M$30,OPcatégorie,"@Virement")</f>
         <v>0</v>
       </c>
     </row>
-    <row r="41" customFormat="false" ht="16.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="J41" s="154" t="s">
-        <v>262</v>
-      </c>
-      <c r="K41" s="55"/>
-      <c r="L41" s="91" t="n">
+    <row r="44" customFormat="false" ht="16.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="J44" s="153" t="s">
+        <v>264</v>
+      </c>
+      <c r="K44" s="55"/>
+      <c r="L44" s="91" t="n">
         <f aca="false">ROUND(SUMIFS(OPequiv_euro,OPcatégorie,"*titres"),0)</f>
         <v>0</v>
       </c>
-      <c r="M41" s="104" t="n">
+      <c r="M44" s="103" t="n">
         <f aca="false">SUMIFS(OPequiv_euro,OPdevise,M$30,OPcatégorie,"*titres")</f>
         <v>0</v>
       </c>
     </row>
-    <row r="42" customFormat="false" ht="16.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="J42" s="154" t="s">
-        <v>263</v>
-      </c>
-      <c r="K42" s="55"/>
-      <c r="L42" s="91" t="n">
+    <row r="45" customFormat="false" ht="16.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="J45" s="153" t="s">
+        <v>265</v>
+      </c>
+      <c r="K45" s="55"/>
+      <c r="L45" s="91" t="n">
         <f aca="false">ROUND(SUMIFS(OPequiv_euro,OPcatégorie,"@Change") + SUMIFS(OPequiv_euro,OPcatégorie,"@Achat métaux"),0)</f>
         <v>0</v>
       </c>
-      <c r="M42" s="104" t="n">
+      <c r="M45" s="103" t="n">
         <f aca="false">SUMIFS(OPequiv_euro,OPdevise,M$30,OPcatégorie,"@Change")+SUMIFS(OPequiv_euro,OPdevise,M$30,OPcatégorie,"@Achat métaux")</f>
         <v>-2458.08</v>
       </c>
     </row>
-    <row r="43" customFormat="false" ht="16.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="J43" s="155" t="s">
-        <v>264</v>
-      </c>
-      <c r="K43" s="55"/>
-      <c r="L43" s="91" t="n">
-        <f aca="false">L40+L41+L42</f>
-        <v>0</v>
-      </c>
-      <c r="M43" s="91" t="n">
-        <f aca="false">M40+M41+M42</f>
-        <v>-2458.08</v>
-      </c>
-    </row>
-    <row r="44" customFormat="false" ht="16.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="J44" s="146" t="s">
-        <v>265</v>
-      </c>
-      <c r="K44" s="147" t="str">
-        <f aca="false">IF(L44=0,"✓","✗")</f>
-        <v>✓</v>
-      </c>
-      <c r="L44" s="151" t="n">
-        <f aca="false">SUMPRODUCT((COUNTIF(AVRintitulé,OPcompte)=0)*(OPcompte&lt;&gt;""))</f>
-        <v>0</v>
-      </c>
-      <c r="M44" s="91"/>
-    </row>
-    <row r="45" customFormat="false" ht="16.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="J45" s="146" t="s">
-        <v>266</v>
-      </c>
-      <c r="K45" s="147" t="str">
-        <f aca="false">IF(L45&gt;0,"✗","✓")</f>
-        <v>✓</v>
-      </c>
-      <c r="L45" s="151" t="n">
-        <f aca="false">SUM(L46:L47)</f>
-        <v>0</v>
-      </c>
-      <c r="M45" s="91"/>
-    </row>
     <row r="46" customFormat="false" ht="16.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="J46" s="154" t="s">
+        <v>266</v>
+      </c>
+      <c r="K46" s="55"/>
+      <c r="L46" s="91" t="n">
+        <f aca="false">L43+L44+L45</f>
+        <v>0</v>
+      </c>
+      <c r="M46" s="91" t="n">
+        <f aca="false">M43+M44+M45</f>
+        <v>-2458.08</v>
+      </c>
+    </row>
+    <row r="47" customFormat="false" ht="16.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="J47" s="145" t="s">
         <v>267</v>
       </c>
-      <c r="K46" s="147"/>
-      <c r="L46" s="151" t="n">
+      <c r="K47" s="146" t="str">
+        <f aca="false">IF(L47=0,"✓","✗")</f>
+        <v>✓</v>
+      </c>
+      <c r="L47" s="150" t="n">
+        <f aca="false">SUMPRODUCT((COUNTIF(AVRintitulé,OPcompte)=0)*(OPcompte&lt;&gt;""))+SUMPRODUCT(ISNUMBER(OPdate)*(OPcompte="")*(LEFT(OPcatégorie,1)&lt;&gt;"#"))+SUMPRODUCT((COUNTIF(COTcode,OPdevise)=0)*(OPdevise&lt;&gt;""))+SUMPRODUCT(ISNUMBER(OPdate)*(OPdevise="")*(LEFT(OPcatégorie,1)&lt;&gt;"#"))</f>
+        <v>0</v>
+      </c>
+      <c r="M47" s="91"/>
+    </row>
+    <row r="48" customFormat="false" ht="16.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="J48" s="145" t="s">
+        <v>268</v>
+      </c>
+      <c r="K48" s="146" t="str">
+        <f aca="false">IF(L48&gt;0,"✗","✓")</f>
+        <v>✓</v>
+      </c>
+      <c r="L48" s="150" t="n">
+        <f aca="false">SUM(L49:L50)</f>
+        <v>0</v>
+      </c>
+      <c r="M48" s="91"/>
+    </row>
+    <row r="49" customFormat="false" ht="16.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="J49" s="153" t="s">
+        <v>269</v>
+      </c>
+      <c r="K49" s="146"/>
+      <c r="L49" s="150" t="n">
         <f aca="false">IF(Avoirs!L1="✗",1,0)</f>
         <v>0</v>
       </c>
-      <c r="M46" s="91"/>
-    </row>
-    <row r="47" customFormat="false" ht="16.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="J47" s="154" t="s">
-        <v>268</v>
-      </c>
-      <c r="K47" s="147"/>
-      <c r="L47" s="151" t="n">
+      <c r="M49" s="91"/>
+    </row>
+    <row r="50" customFormat="false" ht="16.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="J50" s="153" t="s">
+        <v>270</v>
+      </c>
+      <c r="K50" s="146"/>
+      <c r="L50" s="150" t="n">
         <f aca="false">IF(Plus_value!B3="✗",1,0)</f>
         <v>0</v>
       </c>
-      <c r="M47" s="91"/>
-    </row>
-    <row r="48" customFormat="false" ht="16.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="J48" s="14" t="s">
+      <c r="M50" s="91"/>
+    </row>
+    <row r="51" customFormat="false" ht="16.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="J51" s="14" t="s">
         <v>4</v>
       </c>
-      <c r="K48" s="55"/>
-      <c r="L48" s="151"/>
-      <c r="M48" s="91"/>
-    </row>
-    <row r="49" customFormat="false" ht="17.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="J49" s="69" t="s">
-        <v>269</v>
-      </c>
-      <c r="K49" s="71" t="str">
-        <f aca="false">IF(ISNUMBER(FIND("✗",IFERROR(K32,"⚠")&amp;IFERROR(K33,"⚠")&amp;IFERROR(K34,"⚠")&amp;IFERROR(K38,"⚠")&amp;IFERROR(K39,"⚠")&amp;IFERROR(K44,"⚠")&amp;IFERROR(K45,"⚠"))),"✗",IF(ISNUMBER(FIND("⚠",IFERROR(K32,"⚠")&amp;IFERROR(K33,"⚠")&amp;IFERROR(K34,"⚠")&amp;IFERROR(K38,"⚠")&amp;IFERROR(K39,"⚠")&amp;IFERROR(K44,"⚠")&amp;IFERROR(K45,"⚠"))),"⚠","✓"))</f>
+      <c r="K51" s="55"/>
+      <c r="L51" s="150"/>
+      <c r="M51" s="91"/>
+    </row>
+    <row r="52" customFormat="false" ht="17.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="J52" s="69" t="s">
+        <v>271</v>
+      </c>
+      <c r="K52" s="71" t="str">
+        <f aca="false">IF(ISNUMBER(FIND("✗",IFERROR(K32,"⚠")&amp;IFERROR(K33,"⚠")&amp;IFERROR(K37,"⚠")&amp;IFERROR(K41,"⚠")&amp;IFERROR(K42,"⚠")&amp;IFERROR(K47,"⚠")&amp;IFERROR(K48,"⚠"))),"✗",IF(ISNUMBER(FIND("⚠",IFERROR(K32,"⚠")&amp;IFERROR(K33,"⚠")&amp;IFERROR(K37,"⚠")&amp;IFERROR(K41,"⚠")&amp;IFERROR(K42,"⚠")&amp;IFERROR(K47,"⚠")&amp;IFERROR(K48,"⚠"))),"⚠","✓"))</f>
         <v>✓</v>
       </c>
-      <c r="L49" s="156"/>
-      <c r="M49" s="69"/>
-    </row>
-    <row r="1048541" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="1048542" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="1048543" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+      <c r="L52" s="155"/>
+      <c r="M52" s="69"/>
+    </row>
     <row r="1048544" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
     <row r="1048545" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
     <row r="1048546" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
@@ -18412,12 +18470,12 @@
   <mergeCells count="1">
     <mergeCell ref="J29:M29"/>
   </mergeCells>
-  <conditionalFormatting sqref="L33 L40:L43">
+  <conditionalFormatting sqref="L33 L43:L46">
     <cfRule type="cellIs" priority="2" operator="notEqual" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="0">
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="L31:L32 L34:L39 L44:L48">
+  <conditionalFormatting sqref="L31:L32 L37:L42 L47:L51">
     <cfRule type="cellIs" priority="3" operator="notEqual" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="0">
       <formula>0</formula>
     </cfRule>
@@ -18430,7 +18488,7 @@
       <formula>NOT(ISERROR(FIND("⚠",INDIRECT("RC",0))))</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="K33">
+  <conditionalFormatting sqref="K41">
     <cfRule type="expression" priority="6" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="1">
       <formula>NOT(ISERROR(FIND("✗",INDIRECT("RC",0))))</formula>
     </cfRule>
@@ -18438,7 +18496,7 @@
       <formula>NOT(ISERROR(FIND("⚠",INDIRECT("RC",0))))</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="K38">
+  <conditionalFormatting sqref="A1">
     <cfRule type="expression" priority="8" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="1">
       <formula>NOT(ISERROR(FIND("✗",INDIRECT("RC",0))))</formula>
     </cfRule>
@@ -18446,7 +18504,7 @@
       <formula>NOT(ISERROR(FIND("⚠",INDIRECT("RC",0))))</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="A1">
+  <conditionalFormatting sqref="C1">
     <cfRule type="expression" priority="10" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="1">
       <formula>NOT(ISERROR(FIND("✗",INDIRECT("RC",0))))</formula>
     </cfRule>
@@ -18454,7 +18512,7 @@
       <formula>NOT(ISERROR(FIND("⚠",INDIRECT("RC",0))))</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="C1">
+  <conditionalFormatting sqref="K42">
     <cfRule type="expression" priority="12" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="1">
       <formula>NOT(ISERROR(FIND("✗",INDIRECT("RC",0))))</formula>
     </cfRule>
@@ -18462,7 +18520,7 @@
       <formula>NOT(ISERROR(FIND("⚠",INDIRECT("RC",0))))</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="K39">
+  <conditionalFormatting sqref="K52">
     <cfRule type="expression" priority="14" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="1">
       <formula>NOT(ISERROR(FIND("✗",INDIRECT("RC",0))))</formula>
     </cfRule>
@@ -18470,7 +18528,7 @@
       <formula>NOT(ISERROR(FIND("⚠",INDIRECT("RC",0))))</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="K49">
+  <conditionalFormatting sqref="K37">
     <cfRule type="expression" priority="16" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="1">
       <formula>NOT(ISERROR(FIND("✗",INDIRECT("RC",0))))</formula>
     </cfRule>
@@ -18478,7 +18536,7 @@
       <formula>NOT(ISERROR(FIND("⚠",INDIRECT("RC",0))))</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="K34">
+  <conditionalFormatting sqref="K47">
     <cfRule type="expression" priority="18" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="1">
       <formula>NOT(ISERROR(FIND("✗",INDIRECT("RC",0))))</formula>
     </cfRule>
@@ -18486,7 +18544,7 @@
       <formula>NOT(ISERROR(FIND("⚠",INDIRECT("RC",0))))</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="K44">
+  <conditionalFormatting sqref="K48">
     <cfRule type="expression" priority="20" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="1">
       <formula>NOT(ISERROR(FIND("✗",INDIRECT("RC",0))))</formula>
     </cfRule>
@@ -18494,38 +18552,79 @@
       <formula>NOT(ISERROR(FIND("⚠",INDIRECT("RC",0))))</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="K45">
-    <cfRule type="expression" priority="22" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="1">
+  <conditionalFormatting sqref="M34:M35">
+    <cfRule type="expression" priority="22" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="6">
+      <formula>$M$30="EUR"</formula>
+    </cfRule>
+    <cfRule type="expression" priority="23" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="7">
+      <formula>$M$30="XAU"</formula>
+    </cfRule>
+    <cfRule type="expression" priority="24" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="8">
+      <formula>$M$30="OrPr"</formula>
+    </cfRule>
+    <cfRule type="expression" priority="25" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="9">
+      <formula>$M$30="BTC"</formula>
+    </cfRule>
+    <cfRule type="expression" priority="26" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="10">
+      <formula>$M$30="SAT"</formula>
+    </cfRule>
+    <cfRule type="expression" priority="27" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="11">
+      <formula>$M$30="XMR"</formula>
+    </cfRule>
+    <cfRule type="expression" priority="28" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="12">
+      <formula>$M$30="USD"</formula>
+    </cfRule>
+    <cfRule type="expression" priority="29" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="13">
+      <formula>$M$30="SGD"</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="L34">
+    <cfRule type="cellIs" priority="30" operator="notEqual" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="0">
+      <formula>0</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="L35">
+    <cfRule type="cellIs" priority="31" operator="notEqual" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="0">
+      <formula>0</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="L36">
+    <cfRule type="cellIs" priority="32" operator="notEqual" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="0">
+      <formula>0</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="M36">
+    <cfRule type="expression" priority="33" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="6">
+      <formula>$M$30="EUR"</formula>
+    </cfRule>
+    <cfRule type="expression" priority="34" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="7">
+      <formula>$M$30="XAU"</formula>
+    </cfRule>
+    <cfRule type="expression" priority="35" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="8">
+      <formula>$M$30="OrPr"</formula>
+    </cfRule>
+    <cfRule type="expression" priority="36" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="9">
+      <formula>$M$30="BTC"</formula>
+    </cfRule>
+    <cfRule type="expression" priority="37" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="10">
+      <formula>$M$30="SAT"</formula>
+    </cfRule>
+    <cfRule type="expression" priority="38" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="11">
+      <formula>$M$30="XMR"</formula>
+    </cfRule>
+    <cfRule type="expression" priority="39" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="12">
+      <formula>$M$30="USD"</formula>
+    </cfRule>
+    <cfRule type="expression" priority="40" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="13">
+      <formula>$M$30="SGD"</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="K33">
+    <cfRule type="expression" priority="41" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="1">
       <formula>NOT(ISERROR(FIND("✗",INDIRECT("RC",0))))</formula>
     </cfRule>
-    <cfRule type="expression" priority="23" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="2">
+    <cfRule type="expression" priority="42" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="2">
       <formula>NOT(ISERROR(FIND("⚠",INDIRECT("RC",0))))</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="M33">
-    <cfRule type="expression" priority="24" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="6">
-      <formula>$M$30="EUR"</formula>
-    </cfRule>
-    <cfRule type="expression" priority="25" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="7">
-      <formula>$M$30="XAU"</formula>
-    </cfRule>
-    <cfRule type="expression" priority="26" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="8">
-      <formula>$M$30="OrPr"</formula>
-    </cfRule>
-    <cfRule type="expression" priority="27" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="9">
-      <formula>$M$30="BTC"</formula>
-    </cfRule>
-    <cfRule type="expression" priority="28" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="10">
-      <formula>$M$30="SAT"</formula>
-    </cfRule>
-    <cfRule type="expression" priority="29" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="11">
-      <formula>$M$30="XMR"</formula>
-    </cfRule>
-    <cfRule type="expression" priority="30" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="12">
-      <formula>$M$30="USD"</formula>
-    </cfRule>
-    <cfRule type="expression" priority="31" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="13">
-      <formula>$M$30="SGD"</formula>
     </cfRule>
   </conditionalFormatting>
   <dataValidations count="2">
@@ -18559,7 +18658,7 @@
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="74" width="45.77"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="2" style="74" width="9"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="74" width="10.66"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="96" width="9"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="95" width="9"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="74" width="14.47"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="7" style="74" width="13.44"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="8" min="8" style="74" width="27.36"/>
@@ -18573,7 +18672,7 @@
   <sheetData>
     <row r="1" customFormat="false" ht="16.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A1" s="85" t="str">
-        <f aca="false">Contrôles!$K$49</f>
+        <f aca="false">Contrôles!$K$52</f>
         <v>✓</v>
       </c>
       <c r="B1" s="85"/>
@@ -18589,258 +18688,258 @@
     </row>
     <row r="2" customFormat="false" ht="21" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A2" s="26" t="s">
-        <v>270</v>
+        <v>272</v>
       </c>
       <c r="B2" s="26" t="s">
-        <v>271</v>
+        <v>273</v>
       </c>
       <c r="C2" s="26" t="s">
-        <v>272</v>
+        <v>274</v>
       </c>
       <c r="D2" s="26" t="s">
-        <v>273</v>
+        <v>275</v>
       </c>
       <c r="E2" s="51" t="s">
-        <v>274</v>
+        <v>276</v>
       </c>
       <c r="F2" s="51" t="s">
-        <v>275</v>
+        <v>277</v>
       </c>
       <c r="G2" s="51" t="s">
         <v>91</v>
       </c>
       <c r="H2" s="51" t="s">
-        <v>276</v>
+        <v>278</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A3" s="157" t="s">
+      <c r="A3" s="156" t="s">
         <v>4</v>
       </c>
-      <c r="B3" s="158"/>
-      <c r="C3" s="158"/>
-      <c r="D3" s="158"/>
+      <c r="B3" s="157"/>
+      <c r="C3" s="157"/>
+      <c r="D3" s="157"/>
       <c r="E3" s="55"/>
       <c r="F3" s="16"/>
       <c r="G3" s="16"/>
       <c r="H3" s="16"/>
     </row>
     <row r="4" customFormat="false" ht="16.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A4" s="157" t="s">
+      <c r="A4" s="156" t="s">
         <v>17</v>
       </c>
-      <c r="B4" s="158" t="s">
-        <v>277</v>
-      </c>
-      <c r="C4" s="158" t="s">
-        <v>278</v>
-      </c>
-      <c r="D4" s="158" t="n">
+      <c r="B4" s="157" t="s">
+        <v>279</v>
+      </c>
+      <c r="C4" s="157" t="s">
+        <v>280</v>
+      </c>
+      <c r="D4" s="157" t="n">
         <v>2</v>
       </c>
       <c r="E4" s="55" t="s">
         <v>95</v>
       </c>
-      <c r="F4" s="134" t="n">
+      <c r="F4" s="133" t="n">
         <v>1</v>
       </c>
-      <c r="G4" s="134"/>
-      <c r="H4" s="159"/>
+      <c r="G4" s="133"/>
+      <c r="H4" s="158"/>
     </row>
     <row r="5" customFormat="false" ht="16.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A5" s="157" t="s">
+      <c r="A5" s="156" t="s">
+        <v>281</v>
+      </c>
+      <c r="B5" s="157" t="s">
         <v>279</v>
       </c>
-      <c r="B5" s="158" t="s">
-        <v>277</v>
-      </c>
-      <c r="C5" s="158" t="s">
-        <v>280</v>
-      </c>
-      <c r="D5" s="158" t="n">
+      <c r="C5" s="157" t="s">
+        <v>282</v>
+      </c>
+      <c r="D5" s="157" t="n">
         <v>2</v>
       </c>
       <c r="E5" s="55" t="s">
-        <v>281</v>
-      </c>
-      <c r="F5" s="134" t="n">
+        <v>283</v>
+      </c>
+      <c r="F5" s="133" t="n">
         <v>144.12</v>
       </c>
-      <c r="G5" s="160" t="s">
-        <v>282</v>
-      </c>
-      <c r="H5" s="161" t="n">
+      <c r="G5" s="159" t="s">
+        <v>284</v>
+      </c>
+      <c r="H5" s="160" t="n">
         <f aca="false">1/F5</f>
         <v>0.00693866222592284</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="16.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A6" s="157" t="s">
-        <v>283</v>
-      </c>
-      <c r="B6" s="158" t="s">
-        <v>284</v>
-      </c>
-      <c r="C6" s="158" t="s">
-        <v>280</v>
-      </c>
-      <c r="D6" s="158" t="n">
+      <c r="A6" s="156" t="s">
+        <v>285</v>
+      </c>
+      <c r="B6" s="157" t="s">
+        <v>286</v>
+      </c>
+      <c r="C6" s="157" t="s">
+        <v>282</v>
+      </c>
+      <c r="D6" s="157" t="n">
         <v>5</v>
       </c>
       <c r="E6" s="55" t="s">
         <v>122</v>
       </c>
-      <c r="F6" s="162" t="n">
+      <c r="F6" s="161" t="n">
         <f aca="false">F$5*1.043</f>
         <v>150.31716</v>
       </c>
-      <c r="G6" s="160"/>
-      <c r="H6" s="163" t="n">
+      <c r="G6" s="159"/>
+      <c r="H6" s="162" t="n">
         <f aca="false">1/F6</f>
         <v>0.00665260040836322</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="16.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A7" s="157" t="s">
+      <c r="A7" s="156" t="s">
         <v>18</v>
       </c>
-      <c r="B7" s="158" t="s">
-        <v>277</v>
-      </c>
-      <c r="C7" s="158" t="s">
+      <c r="B7" s="157" t="s">
+        <v>279</v>
+      </c>
+      <c r="C7" s="157" t="s">
         <v>178</v>
       </c>
-      <c r="D7" s="158" t="n">
+      <c r="D7" s="157" t="n">
         <v>2</v>
       </c>
       <c r="E7" s="55" t="s">
-        <v>285</v>
-      </c>
-      <c r="F7" s="134" t="n">
+        <v>287</v>
+      </c>
+      <c r="F7" s="133" t="n">
         <v>61009</v>
       </c>
-      <c r="G7" s="160" t="s">
-        <v>282</v>
-      </c>
-      <c r="H7" s="164" t="n">
+      <c r="G7" s="159" t="s">
+        <v>284</v>
+      </c>
+      <c r="H7" s="163" t="n">
         <f aca="false">1/F7</f>
         <v>1.6391024275107E-005</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="16.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A8" s="157" t="s">
+      <c r="A8" s="156" t="s">
+        <v>288</v>
+      </c>
+      <c r="B8" s="157" t="s">
         <v>286</v>
       </c>
-      <c r="B8" s="158" t="s">
-        <v>284</v>
-      </c>
-      <c r="C8" s="158" t="s">
+      <c r="C8" s="157" t="s">
         <v>178</v>
       </c>
-      <c r="D8" s="158" t="n">
+      <c r="D8" s="157" t="n">
         <v>0</v>
       </c>
       <c r="E8" s="55" t="s">
         <v>116</v>
       </c>
-      <c r="F8" s="162" t="n">
+      <c r="F8" s="161" t="n">
         <f aca="false">F$7/100000000</f>
         <v>0.00061009</v>
       </c>
-      <c r="G8" s="160"/>
-      <c r="H8" s="165" t="n">
+      <c r="G8" s="159"/>
+      <c r="H8" s="164" t="n">
         <f aca="false">1/F8</f>
         <v>1639.1024275107</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="16.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A9" s="157" t="s">
+      <c r="A9" s="156" t="s">
         <v>21</v>
       </c>
-      <c r="B9" s="158" t="s">
-        <v>277</v>
-      </c>
-      <c r="C9" s="158" t="s">
+      <c r="B9" s="157" t="s">
+        <v>279</v>
+      </c>
+      <c r="C9" s="157" t="s">
         <v>178</v>
       </c>
-      <c r="D9" s="158" t="n">
+      <c r="D9" s="157" t="n">
         <v>5</v>
       </c>
       <c r="E9" s="55" t="s">
         <v>120</v>
       </c>
-      <c r="F9" s="162" t="n">
+      <c r="F9" s="161" t="n">
         <v>305.02</v>
       </c>
-      <c r="G9" s="160" t="s">
-        <v>282</v>
-      </c>
-      <c r="H9" s="166" t="n">
+      <c r="G9" s="159" t="s">
+        <v>284</v>
+      </c>
+      <c r="H9" s="165" t="n">
         <f aca="false">1/F9</f>
         <v>0.00327847354271851</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="16.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A10" s="157" t="s">
+      <c r="A10" s="156" t="s">
         <v>20</v>
       </c>
-      <c r="B10" s="158" t="s">
-        <v>277</v>
-      </c>
-      <c r="C10" s="158" t="s">
-        <v>278</v>
-      </c>
-      <c r="D10" s="158" t="n">
+      <c r="B10" s="157" t="s">
+        <v>279</v>
+      </c>
+      <c r="C10" s="157" t="s">
+        <v>280</v>
+      </c>
+      <c r="D10" s="157" t="n">
         <v>2</v>
       </c>
       <c r="E10" s="55" t="s">
         <v>100</v>
       </c>
-      <c r="F10" s="134" t="n">
+      <c r="F10" s="133" t="n">
         <v>0.8635</v>
       </c>
-      <c r="G10" s="160" t="s">
-        <v>282</v>
-      </c>
-      <c r="H10" s="167" t="n">
+      <c r="G10" s="159" t="s">
+        <v>284</v>
+      </c>
+      <c r="H10" s="166" t="n">
         <f aca="false">1/F10</f>
         <v>1.15807759119861</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="16.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A11" s="157" t="s">
+      <c r="A11" s="156" t="s">
         <v>19</v>
       </c>
-      <c r="B11" s="158" t="s">
-        <v>277</v>
-      </c>
-      <c r="C11" s="158" t="s">
-        <v>278</v>
-      </c>
-      <c r="D11" s="158" t="n">
+      <c r="B11" s="157" t="s">
+        <v>279</v>
+      </c>
+      <c r="C11" s="157" t="s">
+        <v>280</v>
+      </c>
+      <c r="D11" s="157" t="n">
         <v>2</v>
       </c>
       <c r="E11" s="55" t="s">
         <v>112</v>
       </c>
-      <c r="F11" s="134" t="n">
+      <c r="F11" s="133" t="n">
         <v>0.6776</v>
       </c>
-      <c r="G11" s="160" t="s">
-        <v>282</v>
-      </c>
-      <c r="H11" s="168" t="n">
+      <c r="G11" s="159" t="s">
+        <v>284</v>
+      </c>
+      <c r="H11" s="167" t="n">
         <f aca="false">1/F11</f>
         <v>1.47579693034239</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="16.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A12" s="157" t="s">
+      <c r="A12" s="156" t="s">
         <v>4</v>
       </c>
-      <c r="B12" s="158"/>
-      <c r="C12" s="158"/>
-      <c r="D12" s="158"/>
+      <c r="B12" s="157"/>
+      <c r="C12" s="157"/>
+      <c r="D12" s="157"/>
       <c r="E12" s="55"/>
       <c r="F12" s="16"/>
       <c r="G12" s="16"/>
@@ -18848,7 +18947,7 @@
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A13" s="69" t="s">
-        <v>287</v>
+        <v>289</v>
       </c>
       <c r="B13" s="69" t="str">
         <f aca="false">IF(SUMPRODUCT((COUNTIF(COTcode,PVLdevise)=0)*(PVLdevise&lt;&gt;""))+SUMPRODUCT((COUNTIF(COTcode,AVRdevise)=0)*(AVRdevise&lt;&gt;""))+IFERROR(SUMPRODUCT((COTcode&lt;&gt;"")*(COTcours="")),1)&gt;0,"⚠","✓")</f>
@@ -18862,24 +18961,24 @@
       <c r="H13" s="69"/>
     </row>
     <row r="14" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="F14" s="169"/>
-      <c r="G14" s="169"/>
+      <c r="F14" s="168"/>
+      <c r="G14" s="168"/>
     </row>
     <row r="15" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="F15" s="169"/>
-      <c r="G15" s="169"/>
+      <c r="F15" s="168"/>
+      <c r="G15" s="168"/>
     </row>
     <row r="16" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="F16" s="169"/>
-      <c r="G16" s="169"/>
+      <c r="F16" s="168"/>
+      <c r="G16" s="168"/>
     </row>
     <row r="17" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="F17" s="169"/>
-      <c r="G17" s="169"/>
+      <c r="F17" s="168"/>
+      <c r="G17" s="168"/>
     </row>
     <row r="18" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="F18" s="169"/>
-      <c r="G18" s="169"/>
+      <c r="F18" s="168"/>
+      <c r="G18" s="168"/>
     </row>
     <row r="1048563" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
     <row r="1048564" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
